--- a/extraction/providence-worcester.xlsx
+++ b/extraction/providence-worcester.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal facts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rounds'!$A$1:$J$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deal facts'!$A$1:$B$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deal facts'!$A$1:$B$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="MM/DD/YYYY"/>
   </numFmts>
   <fonts count="2">
@@ -439,14 +439,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V54"/>
+  <dimension ref="A1:V53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
@@ -455,11 +455,11 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="50" customWidth="1" min="16" max="16"/>
-    <col width="55" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="60" customWidth="1" min="16" max="16"/>
+    <col width="60" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
@@ -620,17 +620,17 @@
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Class I rail partner; at a commercial meeting suggested joint ventures and interest in acquiring equity in the Company (no price; not a whole-company offer). Prompted Board to have a subcommittee interview bankers.</t>
+          <t>First contact. At a meeting on joint commercial opportunities with CEO Eder and CCO Rogers, Party A (a Class I rail partner) suggested joint ventures and some interest in acquiring equity; no price, scope unresolved. Board responded by forming a subcommittee to interview bankers.</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>“Party A suggested possible joint venture arrangements and expressed some interest in acquiring equity in the Company” (p. 27)</t>
+          <t>Party A suggested possible joint venture arrangements and expressed some interest in acquiring equity in the Company to further develop strategic opportunities (p. 27)</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S2" s="2" t="n"/>
@@ -655,7 +655,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Greene Holcomb &amp; Fisher LLC (GHF), later BMO Capital Markets</t>
+          <t>Greene Holcomb &amp; Fisher LLC (GHF; later BMO Capital Markets Corp.)</t>
         </is>
       </c>
       <c r="D3" s="2" t="n"/>
@@ -680,12 +680,12 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Target's financial adviser (only one named), engaged by Board on subcommittee recommendation. BMO acquired GHF's business 08/01/2016 and continued the mandate; BMO gave the 08/12/2016 fairness opinion.</t>
+          <t>Target's financial adviser (sole). Recommended by subcommittee (Barrett, Anderson) after interviewing several banks; Board approved and engaged it 01/27/2016. BMO acquired GHF's business 08/01/2016 (same adviser, no new row); BMO gave the fairness opinion 08/12/2016; fee about $2.52 million (p. 41).</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>“Following this presentation, the Board approved the subcommittee’s recommendation and the Company engaged GHF.” (p. 27)</t>
+          <t>Following this presentation, the Board approved the subcommittee’s recommendation and the Company engaged GHF. (p. 27)</t>
         </is>
       </c>
       <c r="R3" s="2" t="n"/>
@@ -736,15 +736,19 @@
       <c r="O4" s="2" t="n"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Board adopted GHF's proposed 'exploratory transaction strategy': continue talks with Party A and solicit other change-in-control interest. Formed Transaction Committee (Barrett, Anderson, Garvey), which could not approve a deal.</t>
+          <t>Board adopted GHF's proposed process: continue discussions with Party A and solicit interest from other third parties in a change-in-control deal. Formed Transaction Committee (Barrett, Anderson, Garvey); approval reserved to full Board. Management met Party A 03/22–23.</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>“Representatives of GHF then proposed a process pursuant to which the Company would proceed with discussions with Party A and also solicit interest from other potential third parties” (p. 27)</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="n"/>
+          <t>Representatives of GHF then proposed a process pursuant to which the Company would proceed with discussions with Party A and also solicit interest from other potential third parties (p. 27)</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S4" s="2" t="n"/>
       <c r="T4" s="3" t="n">
         <v>42443</v>
@@ -792,12 +796,12 @@
       <c r="O5" s="2" t="n"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Target's legal counsel; first seen acting 03/24/2016, attending Transaction Committee meetings.</t>
+          <t>Target's legal counsel; first seen acting 03/24/2016, attending all Transaction Committee meetings. Negotiated the merger agreement drafts with both finalists' counsel.</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>“representatives of each of GHF and the Company’s legal counsel, Hinckley, Allen &amp; Snyder LLP (which we refer to as “Hinckley Allen”), participated in all meetings of the Transaction Committee” (p. 28)</t>
+          <t>representatives of each of GHF and the Company’s legal counsel, Hinckley, Allen &amp; Snyder LLP (which we refer to as “Hinckley Allen”), participated in all meetings of the Transaction Committee (p. 28)</t>
         </is>
       </c>
       <c r="R5" s="2" t="n"/>
@@ -848,12 +852,12 @@
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>GHF outreach wave began, executing the Committee's 03/24 authorization to contact Party A and other buyers (management had told Party A of GHF's engagement on 03/22-23).</t>
+          <t>GHF began outreach under the Transaction Committee's 03/24/2016 authorization to contact Party A and other potential buyers: 11 strategic and 18 financial buyers contacted (#6–7). Confidentiality agreements had no standstill.</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>“The Transaction Committee authorized GHF to contact Party A as well as other potential buyers to determine their level of interest in a change in control transaction.” (p. 28)</t>
+          <t>During the week of March 28, 2016, in accordance with the Transaction Committee’s directives, representatives of GHF contacted 11 potential strategic buyers (including Party A) and 18 potential financial buyers. (p. 28)</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
@@ -863,7 +867,7 @@
       </c>
       <c r="S6" s="2" t="n"/>
       <c r="T6" s="3" t="n">
-        <v>42457</v>
+        <v>42460</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>42457</v>
@@ -883,7 +887,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10 strategic buyers contacted</t>
+          <t>11 potential strategic buyers (incl. Party A; G&amp;W, Parties B, E, F assumed)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -908,28 +912,28 @@
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>GHF contacted 11 potential strategic buyers; Party A (#1) is the eleventh. All 11 later signed NDAs.</t>
+          <t>Target-initiated (GHF). Stated total 11 includes Party A, first contacted Q4 2015 (#1); kept in Count so the row reconciles to the total. G&amp;W, Party B, Party E and Party F assumed members (no other strategic outreach reported besides #10 and Party C).</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>“representatives of GHF contacted 11 potential strategic buyers (including Party A) and 18 potential financial buyers” (p. 28)</t>
+          <t>representatives of GHF contacted 11 potential strategic buyers (including Party A) and 18 potential financial buyers (p. 28)</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S7" s="2" t="n"/>
       <c r="T7" s="3" t="n">
-        <v>42457</v>
+        <v>42460</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>42457</v>
@@ -949,7 +953,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>18 financial buyers contacted</t>
+          <t>18 potential financial buyers (incl. Party D, assumed)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -980,22 +984,22 @@
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>GHF contacted 18 potential financial buyers; 14 later signed NDAs, 4 did not.</t>
+          <t>Target-initiated (GHF). Party D assumed a member (only financial outreach reported). 4 of the 18 did not sign (#9) and never entered.</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>“representatives of GHF contacted 11 potential strategic buyers (including Party A) and 18 potential financial buyers” (p. 28)</t>
+          <t>representatives of GHF contacted 11 potential strategic buyers (including Party A) and 18 potential financial buyers (p. 28)</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S8" s="2" t="n"/>
       <c r="T8" s="3" t="n">
-        <v>42457</v>
+        <v>42460</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>42457</v>
@@ -1015,7 +1019,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11 strategic NDA signers</t>
+          <t>11 strategic NDA signers (incl. Party A, G&amp;W; Parties B, E, F assumed)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1046,22 +1050,22 @@
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>All 11 contacted strategic buyers; no standstills. Includes Party A and G&amp;W (NDA dated 04/03/2016). Parties E and F, and probably B, are members but the filing does not say so. Memorandum later sent to signers.</t>
+          <t>Entry. All 11 contacted strategic buyers signed; no standstill. Stated wave total 25 = 11 + 14 (#9); p. 33 also cites 25 signers. Party B first named 04/21/2016 (introductory meeting); assumed a member. All signers later got the memorandum. Signing dates not reported.</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>“Each of the potential strategic buyers and 14 potential financial buyers subsequently executed confidentiality agreements.” (p. 28)</t>
+          <t>Each of the potential strategic buyers and 14 potential financial buyers subsequently executed confidentiality agreements. (p. 28)</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S9" s="2" t="n"/>
       <c r="T9" s="3" t="n">
-        <v>42457</v>
+        <v>42460</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>42457</v>
@@ -1079,7 +1083,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>14 financial NDA signers</t>
+          <t>14 financial NDA signers (incl. Party D, assumed)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1110,22 +1114,22 @@
       <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14 of the 18 contacted financial buyers; no standstills. Party D is presumably a member (only financial signers before July). Filing's total: 25 NDAs.</t>
+          <t>Entry. 14 of 18 contacted financial buyers signed; no standstill. Part of the stated 25 (#8). Signing dates not reported.</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>“Each of the potential strategic buyers and 14 potential financial buyers subsequently executed confidentiality agreements.” (p. 28)</t>
+          <t>Each of the potential strategic buyers and 14 potential financial buyers subsequently executed confidentiality agreements. (p. 28)</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S10" s="2" t="n"/>
       <c r="T10" s="3" t="n">
-        <v>42457</v>
+        <v>42460</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>42457</v>
@@ -1174,17 +1178,17 @@
       <c r="O11" s="2" t="n"/>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Company management approached them about a possible transaction; filing reports no response and no NDA.</t>
+          <t>Target-initiated by management, reported 04/07/2016. Assumed outside the 11 (#6) because the filing calls them “additional”; response and any NDA not reported, so no entry recorded. Contact date not reported.</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>“Mr. Noreck reported that the Company had also approached two additional Class I railroads to determine their interest in a possible transaction.” (p. 28)</t>
+          <t>Mr. Noreck reported that the Company had also approached two additional Class I railroads to determine their interest in a possible transaction. (p. 28)</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S11" s="2" t="n"/>
@@ -1232,24 +1236,26 @@
       <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Every potential buyer told to submit a non-binding IOI by 05/10/2016; memorandum already sent to NDA signers.</t>
+          <t>Each potential buyer told to submit a non-binding IOI by 05/10/2016; reported at 04/27/2016 Board meeting, communication date not reported. Memorandum prepared with GHF went to all NDA signers, incl. Party A, Party B, G&amp;W.</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>“each potential buyer had been advised to submit a non-binding indication of interest by May 10, 2016” (p. 29)</t>
+          <t>each potential buyer had been advised to submit a non-binding indication of interest by May 10, 2016 (p. 29)</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S12" s="2" t="n"/>
       <c r="T12" s="3" t="n">
-        <v>42487</v>
-      </c>
-      <c r="U12" s="2" t="n"/>
+        <v>42472</v>
+      </c>
+      <c r="U12" s="3" t="n">
+        <v>42457</v>
+      </c>
       <c r="V12" s="3" t="n">
         <v>42487</v>
       </c>
@@ -1260,7 +1266,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>after 04/27/2016</t>
+          <t>after due date set; before 05/19/2016</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1290,28 +1296,28 @@
       <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>IOI due date moved from 05/10 to 05/19/2016. Day not given; Date from assumes 05/10 was still operative at the 04/27 Board discussion.</t>
+          <t>IOI due date moved 05/10 → 05/19/2016 so buyers had time for their most compelling offers. Revision date not reported; treated as before 05/10 arrived (superseded before arrival).</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>“which deadline was subsequently postponed to May 19, 2016 to ensure the potential buyers had sufficient time to formulate their most compelling offers” (p. 29)</t>
+          <t>which deadline was subsequently postponed to May 19, 2016 to ensure the potential buyers had sufficient time to formulate their most compelling offers (p. 29)</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S13" s="2" t="n"/>
       <c r="T13" s="3" t="n">
-        <v>42498</v>
+        <v>42482</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>42487</v>
+        <v>42457</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>42509</v>
+        <v>42508</v>
       </c>
     </row>
     <row r="14">
@@ -1350,17 +1356,17 @@
       <c r="O14" s="2" t="n"/>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>IOI due date reached. IOIs arrived 05/19 to 06/01.</t>
+          <t>IOI due date reached. Nine IOIs arrived between 05/19 and 06/01 (#14); the filing does not say whether any came after 05/19. Outcome Unclear.</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>“which deadline was subsequently postponed to May 19, 2016” (p. 29)</t>
+          <t>Between May 19, 2016 and June 1, 2016, the Company received nine written indications of interest (“IOIs”) from potential buyers (p. 29)</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S14" s="2" t="n"/>
@@ -1380,12 +1386,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/19/2016 - 06/01/2016</t>
+          <t>05/19/2016–06/01/2016</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9 IOI bidders</t>
+          <t>9 IOI bidders (incl. G&amp;W, Parties B, D, E, F; 4 unnamed)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1422,7 +1428,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Heavy</t>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
@@ -1432,17 +1438,17 @@
       <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Range for the group; $/share assumes preferred converts; equity $90M-$134M. Made before data-site access. By later events includes B, G&amp;W, D, E, F and the two LOI non-submitters (#29-30): 5 strategic, 2 financial, 2 unknown.</t>
+          <t>Conditions not reported. Written non-binding IOIs; group range (preferred converted) implying equity values $90M–$134M; individual prices undisclosed. Members G&amp;W, B, D, E, F established by their later advancement (#17); mixed types, split not given.</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>“the Company received nine written indications of interest (“IOIs”) from potential buyers, with offer prices per share ranging from $17.93 to $26.50” (p. 29)</t>
+          <t>the Company received nine written indications of interest (“IOIs”) from potential buyers, with offer prices per share ranging from $17.93 to $26.50 (p. 29)</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S15" s="2" t="n"/>
@@ -1467,7 +1473,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>16 NDA signers without IOI</t>
+          <t>16 NDA signers without an IOI</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1506,22 +1512,22 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25 NDA signers (#8-9) − 9 IOI bidders (#14) = 16. None reappears. May include Party A, which the filing never mentions after March.</t>
+          <t>Inferred: 25 wave signers (#8–9) − 9 IOI bidders (#14) = 16, all of whom had been asked for IOIs (#11). Identities and types unknown; may include Party A, whose IOI status is not reported.</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>“Between May 19, 2016 and June 1, 2016, the Company received nine written indications of interest (“IOIs”) from potential buyers” (p. 29)</t>
+          <t>Between May 19, 2016 and June 1, 2016, the Company received nine written indications of interest (“IOIs”) from potential buyers (p. 29)</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>Q3; Q7</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S16" s="2" t="n"/>
       <c r="T16" s="3" t="n">
-        <v>42509</v>
+        <v>42517</v>
       </c>
       <c r="U16" s="2" t="n"/>
       <c r="V16" s="3" t="n">
@@ -1534,12 +1540,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>05/23/2016 - 06/01/2016</t>
+          <t>05/23/2016–06/01/2016</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2 low IOI bidders</t>
+          <t>2 lowest IOI bidders (unnamed)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1574,19 +1580,15 @@
       <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Transaction Committee excluded the two lowest IOIs from management presentations to save management time. Identities and types not disclosed; may include Party A.</t>
+          <t>Transaction Committee excluded the two low bidders from management presentations to save management time (decided across its 05/23 and 06/01 meetings). Identities, types and prices not disclosed; may include Party A.</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>“the Transaction Committee concluded that the two low bidders should be excluded from that process” (p. 29)</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>Q7</t>
-        </is>
-      </c>
+          <t>the Transaction Committee concluded that the two low bidders should be excluded from that process (p. 29)</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="n"/>
       <c r="S17" s="2" t="n"/>
       <c r="T17" s="3" t="n">
         <v>42517</v>
@@ -1604,7 +1606,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>05/23/2016 - 06/01/2016</t>
+          <t>05/23/2016–06/01/2016</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1634,12 +1636,12 @@
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Committee advanced the other seven IOI bidders to in-person management presentations and further diligence; all seven got internet data-site access.</t>
+          <t>Committee advanced 7 of 9 IOI bidders (G&amp;W, Parties B, D, E, F, one unnamed strategic, one unnamed financial) to in-person management presentations and further diligence; all seven got data-room access. LOI request followed (#18).</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>“The Transaction Committee authorized representatives of GHF to schedule in-person management presentations with the remaining seven potential buyers and allow these parties to conduct additional due diligence.” (p. 29)</t>
+          <t>The Transaction Committee authorized representatives of GHF to schedule in-person management presentations with the remaining seven potential buyers and allow these parties to conduct additional due diligence. (p. 29)</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
@@ -1694,17 +1696,17 @@
       <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Non-binding LOIs due 07/20/2016 with mark-ups of the merger agreement, disclosure letter and voting agreement; price per share for 100% of common. Drafts posted 06/29, 06/30, 07/11.</t>
+          <t>At Committee direction, GHF told all potential buyers to submit non-binding LOIs by 07/20/2016 with mark-ups of the merger agreement, disclosure letter and voting agreement, pricing 100% of common per share. Company drafts posted 06/29, 06/30, 07/11.</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>“representatives of GHF instructed all potential buyers to submit non-binding letters of intent (“LOIs”) by July 20, 2016, together with mark-ups of the forms of merger agreement” (p. 29)</t>
+          <t>representatives of GHF instructed all potential buyers to submit non-binding letters of intent (“LOIs”) by July 20, 2016, together with mark-ups of the forms of merger agreement (p. 29)</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1; Q3</t>
         </is>
       </c>
       <c r="S19" s="2" t="n"/>
@@ -1760,12 +1762,12 @@
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>New strategic buyer approached management unsolicited, expressing interest in acquiring the Company; late entrant during the LOI stage.</t>
+          <t>First contact: a strategic buyer new to the process approached management and expressed interest in acquiring the Company; no price.</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>“a potential strategic buyer that had not previously been part of the process (“Party C”) approached the Company’s management and expressed interest in acquiring the Company” (p. 29)</t>
+          <t>a potential strategic buyer that had not previously been part of the process (“Party C”) approached the Company’s management and expressed interest in acquiring the Company (p. 29)</t>
         </is>
       </c>
       <c r="R20" s="2" t="n"/>
@@ -1786,7 +1788,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>early July 2016</t>
+          <t>early July 2016 (before 07/12/2016)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1822,17 +1824,17 @@
       <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Signed after its approach and before its 07/12 IOI; then received the memorandum. It may not be counted in the filing's 25-NDA total.</t>
+          <t>Entry (late entrant). Received the memorandum given to the other buyers. Outside the 25-signer wave total (#8–9).</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>“After executing a confidentiality agreement, Party C was provided the memorandum concerning the Company provided to the other potential buyers.” (p. 29)</t>
+          <t>After executing a confidentiality agreement, Party C was provided the memorandum concerning the Company provided to the other potential buyers. (p. 29)</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S21" s="2" t="n"/>
@@ -1894,7 +1896,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Heavy</t>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
@@ -1904,12 +1906,12 @@
       <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>IOI; equity value $108M. Made before data-site access (Heavy by context).</t>
+          <t>Diligence open per narrative: no data room or management presentation until after this IOI (07/14). Unsolicited entry IOI while round 2 was open; implies equity value $108M.</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>“On July 12, 2016, Party C submitted an IOI with an offer price per share of $21.00 (implying an equity value of $108 million).” (p. 29)</t>
+          <t>On July 12, 2016, Party C submitted an IOI with an offer price per share of $21.00 (implying an equity value of $108 million). (p. 29)</t>
         </is>
       </c>
       <c r="R22" s="2" t="n"/>
@@ -1930,7 +1932,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>after 07/12/2016; call 07/14/2016</t>
+          <t>07/12/2016–07/14/2016</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1966,23 +1968,25 @@
       <c r="O23" s="2" t="n"/>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>Catch-up access for late entrant: Party C got data-site access and a telephone management presentation (07/14); the seven others had in-person presentations.</t>
+          <t>Catch-up access: after its IOI, Party C was admitted to the data room and given a management presentation by telephone on 07/14 (the other seven had in-person presentations).</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>“Subsequently, Party C was provided access to the internet data site and the Company’s management held a management presentation with Party C by telephone on July 14, 2016.” (p. 29)</t>
+          <t>Subsequently, Party C was provided access to the internet data site and the Company’s management held a management presentation with Party C by telephone on July 14, 2016. (p. 29)</t>
         </is>
       </c>
       <c r="R23" s="2" t="n"/>
       <c r="S23" s="2" t="n"/>
       <c r="T23" s="3" t="n">
-        <v>42565</v>
+        <v>42564</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>42563</v>
       </c>
-      <c r="V23" s="2" t="n"/>
+      <c r="V23" s="3" t="n">
+        <v>42565</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -2020,17 +2024,17 @@
       <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>LOI due date reached; six LOIs arrived in late July, G&amp;W's on 07/21.</t>
+          <t>LOI due date reached. G&amp;W's LOI dated 07/21 (#31) was a late bid and was considered. Other five LOIs came “late July” (by the 07/27 review), arrival days not reported. Six LOIs ranged $19.20–$24.00.</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>“submit non-binding letters of intent (“LOIs”) by July 20, 2016” (p. 29)</t>
+          <t>In late July 2016, the Company received six LOIs with offer prices per share ranging from $19.20 to $24.00 (implying equity values of $96 million to $121 million). (p. 29)</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S24" s="2" t="n"/>
@@ -2102,15 +2106,19 @@
       <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>Non-binding LOI with mark-ups of the merger and voting agreements (Formal by markup); subject to expedited diligence review. Highest LOI.</t>
+          <t>Subject to expedited diligence review. Non-binding LOI delivered with mark-ups of the draft merger agreement and voting agreement, hence Formal. Highest LOI.</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>“Party B submitted an LOI to acquire the Company for a price of $24.00 per share (subject to an expedited diligence review).” (p. 29)</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="n"/>
+          <t>Party B submitted an LOI to acquire the Company for a price of $24.00 per share (subject to an expedited diligence review). (p. 29)</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
       <c r="S25" s="2" t="n"/>
       <c r="T25" s="3" t="n">
         <v>42571</v>
@@ -2180,12 +2188,12 @@
       <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>LOI asking for a 60-day exclusivity period for diligence and documentation. Sent an issues list on the merger and voting agreements, not a markup, so recorded Informal.</t>
+          <t>60-day exclusivity period for diligence and definitive documentation requested. Sent a summary of material issues and proposed changes to the merger and voting agreements, not a mark-up, so Informal.</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>“Party E (a strategic buyer) submitted an LOI to acquire the Company for a price of $21.26 per share (subject to a 60-day exclusivity period for due diligence” (p. 30)</t>
+          <t>Party E (a strategic buyer) submitted an LOI to acquire the Company for a price of $21.26 per share (subject to a 60-day exclusivity period (p. 30)</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
@@ -2262,12 +2270,12 @@
       <c r="O27" s="2" t="n"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>LOI with mark-ups of the merger and voting agreements; four-week diligence period.</t>
+          <t>Four-week diligence period. LOI delivered with mark-ups of the draft merger agreement and voting agreement (p. 29), hence Formal.</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>“Party D (a financial buyer) submitted an LOI to acquire the Company for a price of $21.00 per share (subject to a four-week diligence period).” (p. 30)</t>
+          <t>Party D (a financial buyer) submitted an LOI to acquire the Company for a price of $21.00 per share (subject to a four-week diligence period). (p. 30)</t>
         </is>
       </c>
       <c r="R27" s="2" t="n"/>
@@ -2340,12 +2348,12 @@
       <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>LOI; 30-day diligence period; no markup reported. Below its $21.00 IOI (#21).</t>
+          <t>30-day diligence period. LOI; no mark-up reported. Revises #21.</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>“Party C submitted an LOI to acquire the Company for a price of $19.30 per share (subject to a 30-day diligence period).” (p. 30)</t>
+          <t>Party C submitted an LOI to acquire the Company for a price of $19.30 per share (subject to a 30-day diligence period). (p. 30)</t>
         </is>
       </c>
       <c r="R28" s="2" t="n"/>
@@ -2418,12 +2426,12 @@
       <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>LOI; 30-day due diligence period; no markup reported.</t>
+          <t>30-day due diligence period. LOI; no mark-up reported. Lowest LOI.</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>“Party F (a strategic buyer) submitted an LOI to acquire the Company for a price of $19.20 per share (subject to a 30-day due diligence period).” (p. 30)</t>
+          <t>Party F (a strategic buyer) submitted an LOI to acquire the Company for a price of $19.20 per share (subject to a 30-day due diligence period). (p. 30)</t>
         </is>
       </c>
       <c r="R29" s="2" t="n"/>
@@ -2449,7 +2457,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Unnamed strategic LOI non-submitter</t>
+          <t>Unnamed strategic buyer 1</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2484,12 +2492,12 @@
       <c r="O30" s="2" t="n"/>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>One of the seven IOI bidders advanced in #17; chose not to submit an LOI; never mentioned again.</t>
+          <t>One of the seven round-2 participants (#17); elected not to submit an LOI. Not identified; could be Party A.</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>“One strategic buyer and one financial buyer elected not to submit an LOI.” (p. 30)</t>
+          <t>One strategic buyer and one financial buyer elected not to submit an LOI. (p. 30)</t>
         </is>
       </c>
       <c r="R30" s="2" t="n"/>
@@ -2513,7 +2521,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Unnamed financial LOI non-submitter</t>
+          <t>Unnamed financial buyer 1</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2548,12 +2556,12 @@
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>One of the seven IOI bidders advanced in #17; chose not to submit an LOI; never mentioned again.</t>
+          <t>One of the seven round-2 participants (#17); elected not to submit an LOI.</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>“One strategic buyer and one financial buyer elected not to submit an LOI.” (p. 30)</t>
+          <t>One strategic buyer and one financial buyer elected not to submit an LOI. (p. 30)</t>
         </is>
       </c>
       <c r="R31" s="2" t="n"/>
@@ -2577,7 +2585,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>G&amp;W</t>
+          <t>G&amp;W (Genesee &amp; Wyoming Inc.)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2624,17 +2632,17 @@
       <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>$20.02 cash + $1.13 CVR tied to sale of South Quay property (payment form not stated). Asked for a three-week exclusive diligence period. Marked up merger agreement, voting agreement and disclosure letter. Arrived after 07/20 due date.</t>
+          <t>Three-week exclusive diligence period. $20.02 cash at closing plus $1.13 CVR tied to later sale of the South Quay property; CVR payment form not stated. With mark-ups of merger, voting and disclosure documents, hence Formal. Late: due 07/20.</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>“G&amp;W submitted an LOI on July 21, 2016 to acquire the Company for a price of $21.15 per share (subject to a three-week exclusive diligence period).” (p. 29)</t>
+          <t>G&amp;W submitted an LOI on July 21, 2016 to acquire the Company for a price of $21.15 per share (subject to a three-week exclusive diligence period). (p. 29)</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S32" s="2" t="n"/>
@@ -2659,7 +2667,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>G&amp;W</t>
+          <t>G&amp;W (Genesee &amp; Wyoming Inc.)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2696,7 +2704,7 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Heavy</t>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
@@ -2706,12 +2714,12 @@
       <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Revised after GHF said its price and CVR structure were not competitive: $21.02 cash + $1.13 CVR. Diligence terms not restated; assumed unchanged from #31.</t>
+          <t>Diligence open per narrative: on-site diligence ran 07/27–08/11. Raised after GHF said price and CVR structure were not competitive: $21.02 cash plus $1.13 CVR. Revises #31; stays Formal.</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>“G&amp;W submitted a revised LOI, which increased its offer to $22.15 per share (including $21.02 in cash and $1.13 CVR).” (p. 29)</t>
+          <t>On July 26, 2016, in response to feedback from representatives of GHF indicating its price and CVR structure were not competitive, G&amp;W submitted a revised LOI (p. 29)</t>
         </is>
       </c>
       <c r="R33" s="2" t="n"/>
@@ -2732,47 +2740,57 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>07/27/2016</t>
+          <t>07/27/2016 (told subsequently)</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Target (Transaction Committee)</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n"/>
+          <t>Party C; Party E; Party F</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H34" s="2" t="n"/>
       <c r="I34" s="2" t="n"/>
       <c r="J34" s="2" t="n"/>
       <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="n"/>
-      <c r="M34" s="2" t="n"/>
-      <c r="N34" s="2" t="n"/>
+      <c r="M34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Lower offer than rivals</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Committee chose confirmatory diligence and negotiations with G&amp;W and Party B for their higher offers. Dated 07/27: meetings were 07/22 and 07/27, and the choice relied on G&amp;W's 07/26 revision (#32).</t>
+          <t>Committee chose G&amp;W and Party B for their higher offers; GHF later told the remaining bidders they were out. Decision dated 07/27: it relied on G&amp;W's 07/26 $22.15, as G&amp;W's $21.15 was below E's $21.26. E returns (#37).</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>“The Transaction Committee concluded that the Company should proceed with confirmatory due diligence and negotiations with G&amp;W and Party B because of the higher offers” (p. 30)</t>
+          <t>representatives of GHF subsequently contacted the remaining bidders to inform them that they were no longer involved in the process. (p. 30)</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="S34" s="2" t="n"/>
@@ -2792,17 +2810,17 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>07/27/2016</t>
+          <t>07/27/2016 (told subsequently)</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2832,15 +2850,19 @@
       <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>GHF later told the remaining bidders they were out; sorted to the Committee's decision day. $19.30 LOI.</t>
+          <t>Same decision as #33: $21.00 LOI below G&amp;W and Party B. D returns (#36).</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>“representatives of GHF subsequently contacted the remaining bidders to inform them that they were no longer involved in the process” (p. 30)</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="n"/>
+          <t>representatives of GHF subsequently contacted the remaining bidders to inform them that they were no longer involved in the process. (p. 30)</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
       <c r="S35" s="2" t="n"/>
       <c r="T35" s="3" t="n">
         <v>42578</v>
@@ -2848,7 +2870,9 @@
       <c r="U35" s="3" t="n">
         <v>42578</v>
       </c>
-      <c r="V35" s="2" t="n"/>
+      <c r="V35" s="3" t="n">
+        <v>42578</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -2861,50 +2885,44 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Target (Transaction Committee)</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36" s="2" t="n"/>
       <c r="I36" s="2" t="n"/>
       <c r="J36" s="2" t="n"/>
       <c r="K36" s="2" t="n"/>
       <c r="L36" s="2" t="n"/>
-      <c r="M36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>Lower offer than rivals</t>
-        </is>
-      </c>
+      <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2" t="n"/>
       <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>GHF later told the remaining bidders they were out; sorted to the Committee's decision day. $21.00 LOI.</t>
+          <t>Committee selected G&amp;W and Party B for confirmatory diligence and merger-agreement negotiations; both did on-site financial, legal and environmental diligence 07/27–08/11. No bid due date set.</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>“representatives of GHF subsequently contacted the remaining bidders to inform them that they were no longer involved in the process” (p. 30)</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="n"/>
+          <t>The Transaction Committee concluded that the Company should proceed with confirmatory due diligence and negotiations with G&amp;W and Party B because of the higher offers (p. 30)</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S36" s="2" t="n"/>
       <c r="T36" s="3" t="n">
         <v>42578</v>
@@ -2912,7 +2930,9 @@
       <c r="U36" s="3" t="n">
         <v>42578</v>
       </c>
-      <c r="V36" s="2" t="n"/>
+      <c r="V36" s="3" t="n">
+        <v>42578</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -2920,29 +2940,29 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>07/27/2016</t>
+          <t>07/29/2016</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Party E</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Re-entered</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" s="2" t="n"/>
       <c r="I37" s="2" t="n"/>
@@ -2952,31 +2972,33 @@
       <c r="M37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>Lower offer than rivals</t>
-        </is>
-      </c>
+      <c r="N37" s="2" t="n"/>
       <c r="O37" s="2" t="n"/>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>GHF later told the remaining bidders they were out; sorted to the Committee's decision day. $21.26 LOI.</t>
+          <t>Returned after exit #34: on calls with GHF, expressed interest in re-engaging and enhancing its offer; resumed with revised LOI (#38). Company considered it but did not admit it to the finalist stage.</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>“representatives of GHF subsequently contacted the remaining bidders to inform them that they were no longer involved in the process” (p. 30)</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="n"/>
+          <t>During those calls, Party D and Party E both expressed interest in reengaging and enhancing their offers. (p. 30)</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
       <c r="S37" s="2" t="n"/>
       <c r="T37" s="3" t="n">
-        <v>42578</v>
+        <v>42580</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>42578</v>
-      </c>
-      <c r="V37" s="2" t="n"/>
+        <v>42580</v>
+      </c>
+      <c r="V37" s="3" t="n">
+        <v>42580</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -2984,12 +3006,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>07/27/2016</t>
+          <t>07/29/2016</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Party F</t>
+          <t>Party E</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2999,14 +3021,14 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Re-entered</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H38" s="2" t="n"/>
       <c r="I38" s="2" t="n"/>
@@ -3016,31 +3038,33 @@
       <c r="M38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>Lower offer than rivals</t>
-        </is>
-      </c>
+      <c r="N38" s="2" t="n"/>
       <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>GHF later told the remaining bidders they were out; sorted to the Committee's decision day. $19.20 LOI. F later gave Party E financing support (#41) but did not bid again.</t>
+          <t>Returned after exit #33: on calls with GHF, expressed interest in re-engaging and enhancing its offer; resumed with revised LOI (#39).</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>“representatives of GHF subsequently contacted the remaining bidders to inform them that they were no longer involved in the process” (p. 30)</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="n"/>
+          <t>During those calls, Party D and Party E both expressed interest in reengaging and enhancing their offers. (p. 30)</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
       <c r="S38" s="2" t="n"/>
       <c r="T38" s="3" t="n">
-        <v>42578</v>
+        <v>42580</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>42578</v>
-      </c>
-      <c r="V38" s="2" t="n"/>
+        <v>42580</v>
+      </c>
+      <c r="V38" s="3" t="n">
+        <v>42580</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -3048,7 +3072,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/29/2016</t>
+          <t>08/01/2016</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3063,7 +3087,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Re-entered</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
@@ -3072,11 +3096,27 @@
       <c r="G39" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H39" s="2" t="n"/>
-      <c r="I39" s="2" t="n"/>
-      <c r="J39" s="2" t="n"/>
-      <c r="K39" s="2" t="n"/>
-      <c r="L39" s="2" t="n"/>
+      <c r="H39" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="M39" s="2" t="n">
         <v>1</v>
       </c>
@@ -3084,28 +3124,28 @@
       <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Returned after exit #35: on calls with GHF, said it wanted to re-engage and improve its offer. Filing does not say who started the calls.</t>
+          <t>30-day due diligence period. Revised LOI raising #26; stays Formal (earlier mark-up). Committee had BMO clarify its terms and diligence needs.</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>“During those calls, Party D and Party E both expressed interest in reengaging and enhancing their offers.” (p. 30)</t>
+          <t>On August 1, 2016, Party D submitted a revised LOI at a price of $24.00 per share (p. 30)</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="S39" s="2" t="n"/>
       <c r="T39" s="3" t="n">
-        <v>42580</v>
+        <v>42583</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>42580</v>
+        <v>42583</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>42580</v>
+        <v>42583</v>
       </c>
     </row>
     <row r="40">
@@ -3114,7 +3154,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>07/29/2016</t>
+          <t>08/01/2016</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3129,7 +3169,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Re-entered</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
@@ -3138,11 +3178,27 @@
       <c r="G40" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="n"/>
-      <c r="J40" s="2" t="n"/>
-      <c r="K40" s="2" t="n"/>
-      <c r="L40" s="2" t="n"/>
+      <c r="H40" s="4" t="n">
+        <v>23.81</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>23.81</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="M40" s="2" t="n">
         <v>1</v>
       </c>
@@ -3150,28 +3206,28 @@
       <c r="O40" s="2" t="n"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Returned after exit #36: on calls with GHF, said it wanted to re-engage and improve its offer. Filing does not say who started the calls.</t>
+          <t>30-day due diligence period. Revised LOI raising #25, with financing support from Party F (already out, #33; not a group). Committee had BMO clarify its terms.</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>“During those calls, Party D and Party E both expressed interest in reengaging and enhancing their offers.” (p. 30)</t>
+          <t>Party E submitted a revised LOI, along with financing support, from Party F, at a price of $23.81 per share. (p. 30)</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q5; Q6</t>
         </is>
       </c>
       <c r="S40" s="2" t="n"/>
       <c r="T40" s="3" t="n">
-        <v>42580</v>
+        <v>42583</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>42580</v>
+        <v>42583</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>42580</v>
+        <v>42583</v>
       </c>
     </row>
     <row r="41">
@@ -3180,7 +3236,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>08/01/2016</t>
+          <t>on or after 08/01/2016</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3195,7 +3251,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Exclusivity changed</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
@@ -3204,27 +3260,11 @@
       <c r="G41" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H41" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="I41" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="n"/>
       <c r="M41" s="2" t="n">
         <v>1</v>
       </c>
@@ -3232,17 +3272,17 @@
       <c r="O41" s="2" t="n"/>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Revised LOI; 30-day due diligence period. Formal because its July LOI came with a markup (#26); no new markup reported.</t>
+          <t>Requested and refused: D would not shorten its 30-day diligence and asked the Company to commit not to sign with another bidder during it; Company declined, citing active interest of Party B and G&amp;W. Date not reported.</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>“On August 1, 2016, Party D submitted a revised LOI at a price of $24.00 per share” (p. 30)</t>
+          <t>Party D declined to shorten its due diligence period and requested that the Company commit that it would not enter into an agreement with another bidder (p. 30)</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="S41" s="2" t="n"/>
@@ -3252,9 +3292,7 @@
       <c r="U41" s="3" t="n">
         <v>42583</v>
       </c>
-      <c r="V41" s="3" t="n">
-        <v>42583</v>
-      </c>
+      <c r="V41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -3262,22 +3300,22 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>08/01/2016</t>
+          <t>on or after 08/01/2016</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Party E</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Withdrew</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
@@ -3286,45 +3324,33 @@
       <c r="G42" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H42" s="4" t="n">
-        <v>23.81</v>
-      </c>
-      <c r="I42" s="4" t="n">
-        <v>23.81</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
+      <c r="H42" s="2" t="n"/>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="2" t="n"/>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="n"/>
       <c r="M42" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N42" s="2" t="n"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Terms or process</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Revised LOI with financing support from Party F (out since #37); 30-day due diligence period. Board had BMO clarify terms and diligence needs.</t>
+          <t>After refusal of #40, D said it would not continue due diligence “at that time” (stopping for now); not heard from again. Date not reported.</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>“Party E submitted a revised LOI, along with financing support, from Party F, at a price of $23.81 per share” (p. 30)</t>
+          <t>the Company declined to make such a commitment, at which point Party D indicated that it would not proceed with further due diligence at that time. (p. 30)</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="S42" s="2" t="n"/>
@@ -3334,9 +3360,7 @@
       <c r="U42" s="3" t="n">
         <v>42583</v>
       </c>
-      <c r="V42" s="3" t="n">
-        <v>42583</v>
-      </c>
+      <c r="V42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -3396,17 +3420,17 @@
       <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>Reversion: withdrew its $23.81 proposal (#41) but confirmed its original $21.26 LOI (#25), which asked for 60-day exclusivity.</t>
+          <t>Reverted to original proposal (#25), with its 60-day exclusivity for diligence: withdrew $23.81 (#39) after BMO's clarification request and confirmed $21.26. A new Bid under the reversion rule, not an exit.</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>“Party E withdrew its revised proposal on August 2, 2016 (but confirmed its original proposal of $21.26 per share)” (p. 30)</t>
+          <t>Party E withdrew its revised proposal on August 2, 2016 (but confirmed its original proposal of $21.26 per share) (p. 30)</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>Q5; Q6</t>
         </is>
       </c>
       <c r="S43" s="2" t="n"/>
@@ -3426,22 +3450,18 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>08/01/2016 - 08/04/2016</t>
+          <t>08/04/2016</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Target (Transaction Committee)</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Withdrew</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
@@ -3455,32 +3475,30 @@
       <c r="J44" s="2" t="n"/>
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="n"/>
-      <c r="M44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>Terms or process</t>
-        </is>
-      </c>
+      <c r="M44" s="2" t="n"/>
+      <c r="N44" s="2" t="n"/>
       <c r="O44" s="2" t="n"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Would not shorten its 30-day diligence period and asked the Company not to sign with anyone else meanwhile. The Company refused because B and G&amp;W were active. D stopped diligence 'at that time'. Both sides contributed.</t>
+          <t>Preferred bidder: Committee told advisers to keep up diligence and negotiations with both G&amp;W and Party B but, given B's higher price, to prioritize B and complete the merger agreement with B.</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>“the Company declined to make such a commitment, at which point Party D indicated that it would not proceed with further due diligence at that time” (p. 30)</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="n"/>
+          <t>given the higher price offered by Party B, to prioritize Party B and proceed to complete the negotiation of the merger agreement with Party B. (p. 31)</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
       <c r="S44" s="2" t="n"/>
       <c r="T44" s="3" t="n">
-        <v>42584</v>
+        <v>42586</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>42583</v>
+        <v>42586</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>42586</v>
@@ -3497,13 +3515,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Target (Transaction Committee)</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="n"/>
+          <t>Party B</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bid reaffirmed</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
@@ -3512,22 +3534,40 @@
       <c r="G45" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H45" s="2" t="n"/>
-      <c r="I45" s="2" t="n"/>
-      <c r="J45" s="2" t="n"/>
-      <c r="K45" s="2" t="n"/>
-      <c r="L45" s="2" t="n"/>
-      <c r="M45" s="2" t="n"/>
+      <c r="H45" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N45" s="2" t="n"/>
       <c r="O45" s="2" t="n"/>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>Preferred bidder named: continue diligence and talks with G&amp;W and B, but prioritize B for its higher price and finish the merger agreement with B.</t>
+          <t>Expedited diligence still open (on-site to 08/11). Reaffirmed by returned draft: B's counsel returned a revised merger agreement after the Company's 08/01 draft, with Company moving to finalize with B (#43). Price carried from #24.</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>“given the higher price offered by Party B, to prioritize Party B and proceed to complete the negotiation of the merger agreement with Party B” (p. 31)</t>
+          <t>On August 4, 2016, legal counsel for Party B provided a revised draft of the merger agreement (p. 31)</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
@@ -3552,12 +3592,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>by 08/04/2016</t>
+          <t>08/09/2016</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Party E</t>
+          <t>G&amp;W (Genesee &amp; Wyoming Inc.)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -3567,7 +3607,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
@@ -3584,38 +3624,28 @@
       <c r="M46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="N46" s="2" t="n"/>
+      <c r="O46" s="2" t="n"/>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>Out by 08/04: the Committee named only G&amp;W and B as continuing, and E's confirmed $21.26 offer is never mentioned again.</t>
+          <t>Status change: Committee had BMO tell G&amp;W the Company intended to sign with another bidder. G&amp;W's request to keep doing diligence (physical diligence 08/10–08/11) to support a better offer was granted.</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>“the Transaction Committee directed the management team and representatives of each of BMO and Hinckley Allen to continue diligence and negotiations with both G&amp;W and Party B” (p. 31)</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
+          <t>the Transaction Committee directed representatives of BMO to inform G&amp;W that the Company intended to enter into a merger agreement with another bidder. (p. 31)</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="n"/>
       <c r="S46" s="2" t="n"/>
       <c r="T46" s="3" t="n">
-        <v>42586</v>
-      </c>
-      <c r="U46" s="2" t="n"/>
+        <v>42591</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>42591</v>
+      </c>
       <c r="V46" s="3" t="n">
-        <v>42586</v>
+        <v>42591</v>
       </c>
     </row>
     <row r="47">
@@ -3624,22 +3654,18 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>08/04/2016</t>
+          <t>08/10/2016</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Bid reaffirmed</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
@@ -3648,56 +3674,34 @@
       <c r="G47" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H47" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="I47" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H47" s="2" t="n"/>
+      <c r="I47" s="2" t="n"/>
+      <c r="J47" s="2" t="n"/>
+      <c r="K47" s="2" t="n"/>
+      <c r="L47" s="2" t="n"/>
+      <c r="M47" s="2" t="n"/>
       <c r="N47" s="2" t="n"/>
       <c r="O47" s="2" t="n"/>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>Carried from #24; reaffirmed by returned draft: B's counsel sent a revised merger agreement as the Company moved to complete the agreement with B (#44). On-site diligence continued to 08/11.</t>
+          <t>G&amp;W's legal counsel; first seen acting 08/10/2016 in draft-agreement discussions with Hinckley Allen; finalized documents at signing.</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>“On August 4, 2016, legal counsel for Party B provided a revised draft of the merger agreement” (p. 31)</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
+          <t>Simpson Thacher &amp; Bartlett LLP (which we refer to as “Simpson Thacher”), G&amp;W’s legal counsel (p. 31)</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="n"/>
       <c r="S47" s="2" t="n"/>
       <c r="T47" s="3" t="n">
-        <v>42586</v>
+        <v>42592</v>
       </c>
       <c r="U47" s="3" t="n">
-        <v>42586</v>
+        <v>42592</v>
       </c>
       <c r="V47" s="3" t="n">
-        <v>42586</v>
+        <v>42592</v>
       </c>
     </row>
     <row r="48">
@@ -3706,12 +3710,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>08/09/2016</t>
+          <t>08/12/2016 (morning)</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>G&amp;W</t>
+          <t>G&amp;W (Genesee &amp; Wyoming Inc.)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3721,7 +3725,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
@@ -3730,11 +3734,27 @@
       <c r="G48" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H48" s="2" t="n"/>
-      <c r="I48" s="2" t="n"/>
-      <c r="J48" s="2" t="n"/>
-      <c r="K48" s="2" t="n"/>
-      <c r="L48" s="2" t="n"/>
+      <c r="H48" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="M48" s="2" t="n">
         <v>1</v>
       </c>
@@ -3742,24 +3762,24 @@
       <c r="O48" s="2" t="n"/>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>Target told G&amp;W it intended to sign with another bidder. G&amp;W asked to continue diligence (on-site 08/10-11) toward a better offer; granted. On 08/11 G&amp;W signalled a revised LOI.</t>
+          <t>Physical diligence completed 08/11; no financing condition in the agreement signed that day (p. 34). All cash, CVR dropped; with merger and voting agreement mark-ups; expiring 6:00 p.m. next day. Ref: $16.30 close 08/12/2016; 53% premium (p. 33).</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>“the Transaction Committee directed representatives of BMO to inform G&amp;W that the Company intended to enter into a merger agreement with another bidder” (p. 31)</t>
+          <t>G&amp;W submitted a revised LOI to acquire the Company for a price of $25.00 per share in cash, which excluded the previously proposed CVR (p. 31)</t>
         </is>
       </c>
       <c r="R48" s="2" t="n"/>
       <c r="S48" s="2" t="n"/>
       <c r="T48" s="3" t="n">
-        <v>42591</v>
+        <v>42594</v>
       </c>
       <c r="U48" s="3" t="n">
-        <v>42591</v>
+        <v>42594</v>
       </c>
       <c r="V48" s="3" t="n">
-        <v>42591</v>
+        <v>42594</v>
       </c>
     </row>
     <row r="49">
@@ -3768,18 +3788,22 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>08/10/2016</t>
+          <t>08/12/2016</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="n"/>
+          <t>Party B</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Bid reaffirmed</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
@@ -3788,34 +3812,56 @@
       <c r="G49" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H49" s="2" t="n"/>
-      <c r="I49" s="2" t="n"/>
-      <c r="J49" s="2" t="n"/>
-      <c r="K49" s="2" t="n"/>
-      <c r="L49" s="2" t="n"/>
-      <c r="M49" s="2" t="n"/>
+      <c r="H49" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N49" s="2" t="n"/>
       <c r="O49" s="2" t="n"/>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>G&amp;W's legal counsel; first seen acting 08/10/2016.</t>
+          <t>Only final documentation left: diligence done 08/11; meetings set to approve a deal with B. By price confirmation: told a rival bid higher, then asked by BMO at the Board's request to raise, B would not; $24.00 carried from #24.</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>“Simpson Thacher &amp; Bartlett LLP (which we refer to as “Simpson Thacher”), G&amp;W’s legal counsel” (p. 31)</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="n"/>
+          <t>representatives of BMO then contacted Party B to determine if it would increase its offer price. Party B indicated that it would not increase its price. (p. 32)</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
       <c r="S49" s="2" t="n"/>
       <c r="T49" s="3" t="n">
-        <v>42592</v>
+        <v>42594</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>42592</v>
+        <v>42594</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>42592</v>
+        <v>42594</v>
       </c>
     </row>
     <row r="50">
@@ -3824,22 +3870,18 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>08/12/2016 (morning)</t>
+          <t>08/12/2016</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>G&amp;W</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Target; G&amp;W</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Merger agreement signed</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
@@ -3848,40 +3890,22 @@
       <c r="G50" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H50" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="I50" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H50" s="2" t="n"/>
+      <c r="I50" s="2" t="n"/>
+      <c r="J50" s="2" t="n"/>
+      <c r="K50" s="2" t="n"/>
+      <c r="L50" s="2" t="n"/>
+      <c r="M50" s="2" t="n"/>
       <c r="N50" s="2" t="n"/>
       <c r="O50" s="2" t="n"/>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>All-cash revised LOI; CVR dropped; mark-ups of merger and voting agreements; offer expiring 6 p.m. next day. Physical diligence done 08/11; agreement signed that day, without financing condition.</t>
+          <t>$25.00 per share in cash (preferred converted at 100 common each). Board (Smith recused) found G&amp;W superior: $1.00 more, lower break fee, similar STB risk; BMO fairness opinion. Eder Trusts voting agreement; $3.785M termination fee.</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>“G&amp;W submitted a revised LOI to acquire the Company for a price of $25.00 per share in cash, which excluded the previously proposed CVR” (p. 31)</t>
+          <t>the Company and G&amp;W executed the merger agreement, and the Company, G&amp;W and the Eder Trusts executed the voting agreement. (p. 32)</t>
         </is>
       </c>
       <c r="R50" s="2" t="n"/>
@@ -3917,7 +3941,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Not selected at signing</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
@@ -3934,19 +3958,27 @@
       <c r="M51" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N51" s="2" t="n"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>Would not improve earlier offer</t>
+        </is>
+      </c>
       <c r="O51" s="2" t="n"/>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>At its 10:30 a.m. meeting, the Committee had BMO tell B that a higher revised LOI had arrived. In the afternoon, the Board had BMO ask B to raise its price.</t>
+          <t>Reported: still bidding at $24.00 (#48) when the Board chose G&amp;W's $25.00; declined to improve when asked.</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>“the Transaction Committee directed representatives of BMO to inform Party B that another party had submitted a revised LOI at a higher price” (p. 31)</t>
-        </is>
-      </c>
-      <c r="R51" s="2" t="n"/>
+          <t>The Board determined that the G&amp;W offer represented the superior proposal. (p. 32)</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
       <c r="S51" s="2" t="n"/>
       <c r="T51" s="3" t="n">
         <v>42594</v>
@@ -3964,12 +3996,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>08/12/2016</t>
+          <t>by 08/12/2016</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>Party E</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3998,27 +4030,35 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Would not improve earlier offer</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="n"/>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>Declined to raise its $24.00 offer (#46). Board found G&amp;W's $25.00 superior; the drafts otherwise differed on the termination fee (lower for G&amp;W) and on the STB approval route.</t>
+          <t>Inferred: last seen 08/02 with $21.26 confirmed (#42), then never mentioned; closed at signing with G&amp;W under the fallback rule.</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>“representatives of BMO then contacted Party B to determine if it would increase its offer price. Party B indicated that it would not increase its price.” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="n"/>
+          <t>Party E withdrew its revised proposal on August 2, 2016 (but confirmed its original proposal of $21.26 per share) (p. 30)</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
       <c r="S52" s="2" t="n"/>
       <c r="T52" s="3" t="n">
         <v>42594</v>
       </c>
       <c r="U52" s="3" t="n">
-        <v>42594</v>
+        <v>42584</v>
       </c>
       <c r="V52" s="3" t="n">
         <v>42594</v>
@@ -4030,122 +4070,60 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>08/12/2016</t>
+          <t>08/15/2016</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>G&amp;W</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n"/>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Merger agreement signed</t>
+          <t>Merger announced</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G53" s="2" t="n">
-        <v>3</v>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
       </c>
       <c r="H53" s="2" t="n"/>
       <c r="I53" s="2" t="n"/>
       <c r="J53" s="2" t="n"/>
       <c r="K53" s="2" t="n"/>
       <c r="L53" s="2" t="n"/>
-      <c r="M53" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M53" s="2" t="n"/>
       <c r="N53" s="2" t="n"/>
       <c r="O53" s="2" t="n"/>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>$25.00 cash per common share (each preferred share converts into 100 common). Termination fee 3% ($3.785M). Eder Trusts signed voting agreement. Board approved 08/12 (Smith recused).</t>
+          <t>Press release before market open on Monday 08/15/2016.</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>“Shortly thereafter, Hinckley Allen and Simpson Thacher finalized the transaction documents and the Company and G&amp;W executed the merger agreement” (p. 32)</t>
+          <t>The Company issued a press release publicly announcing the transaction on Monday, August 15, 2016 prior to the opening of trading (p. 32)</t>
         </is>
       </c>
       <c r="R53" s="2" t="n"/>
       <c r="S53" s="2" t="n"/>
       <c r="T53" s="3" t="n">
-        <v>42594</v>
+        <v>42597</v>
       </c>
       <c r="U53" s="3" t="n">
-        <v>42594</v>
+        <v>42597</v>
       </c>
       <c r="V53" s="3" t="n">
-        <v>42594</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>08/15/2016</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Merger announced</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="n"/>
-      <c r="I54" s="2" t="n"/>
-      <c r="J54" s="2" t="n"/>
-      <c r="K54" s="2" t="n"/>
-      <c r="L54" s="2" t="n"/>
-      <c r="M54" s="2" t="n"/>
-      <c r="N54" s="2" t="n"/>
-      <c r="O54" s="2" t="n"/>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>Press release before NASDAQ open.</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>“The Company issued a press release publicly announcing the transaction on Monday, August 15, 2016 prior to the opening of trading” (p. 32)</t>
-        </is>
-      </c>
-      <c r="R54" s="2" t="n"/>
-      <c r="S54" s="2" t="n"/>
-      <c r="T54" s="3" t="n">
         <v>42597</v>
       </c>
-      <c r="U54" s="3" t="n">
-        <v>42597</v>
-      </c>
-      <c r="V54" s="3" t="n">
-        <v>42597</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V54"/>
+  <autoFilter ref="A1:V53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4163,11 +4141,11 @@
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -4231,26 +4209,26 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>42457</v>
+        <v>42460</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>GHF began outreach (week of 03/28): 11 strategic and 18 financial buyers contacted, after the Committee's 03/24 authorization (#5-7).</t>
+          <t>GHF outreach wave, week of 03/28/2016, on the Transaction Committee's 03/24 authorization: 11 strategic and 18 financial buyers contacted (#5–7).</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>25 NDA signers: 11 strategic (incl. Party A, G&amp;W; E, F and probably B) and 14 financial (incl. D). Two more Class I railroads approached; no NDA reported.</t>
+          <t>25 NDA signers (#8–9): 11 strategic (incl. Party A, G&amp;W; Parties B, E, F assumed) and 14 financial (incl. Party D, assumed).</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>05/10/2016 → 05/19/2016</t>
+          <t>05/10/2016 (superseded before arrival; revision date not reported) → 05/19/2016</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Enforced</t>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -4260,12 +4238,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>9 non-binding IOIs, $17.93-$26.50 (#14); by later events includes B, G&amp;W, D, E, F and two unnamed (one strategic, one financial).</t>
+          <t>9 IOIs, $17.93–$26.50 as a group (#14): G&amp;W, Parties B, D, E, F and 4 unnamed.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Seven advanced, two low bidders excluded (#16), 16 signers did not submit (#15).</t>
+          <t>seven advanced; two low bidders excluded; sixteen did not submit (#15–17)</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4259,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Committee advanced seven IOI bidders to management presentations and data-site diligence (#17); LOIs with markups requested mid-June (#18).</t>
+          <t>Committee advanced seven IOI bidders to management presentations, data room and further diligence; mid-June request for LOIs with document mark-ups (#17–18).</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>8: seven advanced (strategic B, G&amp;W, E, F, one unnamed; financial D, one unnamed) plus late entrant Party C (strategic, NDA early July).</t>
+          <t>7 admitted: 5 strategic (G&amp;W, Parties B, E, F, unnamed strategic buyer 1) and 2 financial (Party D, unnamed financial buyer 1); plus late entrant Party C (strategic), admitted to data room and management presentation 07/12–07/14 (#20–22).</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -4306,12 +4284,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>6 LOIs: B $24.00, G&amp;W $21.15 then $22.15, E $21.26, D $21.00, C $19.30, F $19.20 (C also IOI $21.00 on 07/12). Two did not submit.</t>
+          <t>6 LOIs: Party B $24.00; G&amp;W $21.15 → $22.15; Party E $21.26; Party D $21.00; Party C $19.30; Party F $19.20. Party C also bid $21.00 by IOI 07/12.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Two advanced (G&amp;W, B); C, D, E, F told they were out (#34-37); two did not submit (#29-30).</t>
+          <t>two advanced (G&amp;W, Party B); four dropped (Parties C, D, E, F); two did not submit (#29–30, #33–34)</t>
         </is>
       </c>
     </row>
@@ -4327,12 +4305,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Committee chose confirmatory diligence and negotiations with G&amp;W and Party B (#33); on 08/04 prioritized B (#44).</t>
+          <t>Committee chose G&amp;W and Party B for confirmatory diligence and merger-agreement negotiations (#35).</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2 strategic: G&amp;W, Party B; then D (financial) and E (strategic) re-entered 07/29 (#38-39).</t>
+          <t>2 strategic: G&amp;W, Party B. Parties D (financial) and E (strategic): still being received, not admitted (re-engaged 07/29, revised LOIs 08/01).</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -4352,12 +4330,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4: D $24.00; E $23.81, reverted to $21.26; B reaffirmed $24.00 (#46); G&amp;W $25.00 cash (#49).</t>
+          <t>4: G&amp;W $25.00 (#47); Party B $24.00 reaffirmed (#44, #48); Party D $24.00 (#38); Party E $23.81 then back to $21.26 (#39, #42).</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Signing with G&amp;W at $25.00 (#52); B would not raise (#51); D withdrew (#43); E out by 08/04 (inferred, #45).</t>
+          <t>signing with G&amp;W at $25.00; Party B would not raise and was not selected; Party E not selected; Party D withdrew</t>
         </is>
       </c>
     </row>
@@ -4373,16 +4351,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4430,27 +4408,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Process and round map: one process with rounds 1 (IOIs), 2 (LOIs) and 3 (negotiation with G&amp;W and B)?</t>
+          <t>Process and round map: one process with rounds 0–3?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Yes. Round 2 opens at the 05/23-06/01 selection of seven; round 3 opens 07/27; D and E's 08/01 bids are round 3; 08/04 prioritizing B stays inside round 3.</t>
+          <t>Yes. Process 1: round 0 (#1–4); round 1 opens with the 03/28-week outreach (#5); round 2 opens at the seven-bidder advancement (#17); round 3 (Inferred final) opens at the 07/27 G&amp;W/Party B selection (#35).</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Selection plus a new information stage opens round 2 (p. 29); the 07/27 move to confirmatory negotiation with two opens round 3 (p. 30). The LOI request was 'non-binding', so it was not a final round.</t>
+          <t>Party A's equity interest (Q4 2015) led directly to the banker hire and the 03/14 process, which kept Party A in view (pp. 27–28). Gaps of about two months or more: Q4 2015 Party A meeting (10/01–12/31/2015, uncertain) to 03/22/2016 Party A meetings, i.e. 2.7–5.7 months. C7: (a) fails, since Party A was carried forward; (b) uncertain; (c) met. So there is no new process. No other gap of two months or more.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>#5, #17, #33, #38-46</t>
+          <t>#1, #3, #5, #17, #18, #35</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>If round 2 opens at the mid-June LOI request, #17 moves to about 06/15. If 08/04 opens round 4, then #44-52 move to round 4 and round 3 ends with D and E out.</t>
+          <t>Most plausible alternative: round 2 opens at the mid-June LOI instruction (#18), not at the advancement decision, so #17 becomes a round-1 selection step. Another reading would open round 1 at the 03/24 authorization; nothing moves. Party A's interest in buying equity could instead be read as an other-scope approach; it has no row effect.</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -4463,27 +4441,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Deadline outcomes: round 1 Enforced (05/19); round 2 Late bids accepted (07/20)?</t>
+          <t>How many parties signed confidentiality agreements, and who is in the outreach cohorts?</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Yes. The 05/10 date was superseded before it arrived. Round 1 counts as Enforced because the IOI cohort's Date from is the due date. G&amp;W's 07/21 LOI arrived after the round-2 due date and was considered.</t>
+          <t>26 parties: 25 from the March wave (11 strategic, 14 financial) plus Party C. Assume Parties B, E, F and G&amp;W were among the 11 strategic buyers, Party D among the 14 financial buyers, and the two “additional” Class I railroads outside the 11 and not signing.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>IOIs arrived 05/19 to 06/01 and the Committee then selected seven (p. 29). G&amp;W's LOI is dated 07/21 against a 07/20 due date (p. 29).</t>
+          <t>p. 28 gives 11 + 14 = 25 signers from the wave; p. 29 adds Party C's agreement; p. 33 says “25 of whom entered into confidentiality agreements”, which leaves out Party C or counts differently. Party B was first met 04/21 as “another potential strategic buyer” (p. 28).</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>#11-14, #18, #23, #31</t>
+          <t>#6, #7, #8, #9, #10, #15, #20</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Round 1 could be Late bids accepted, since IOIs arrived up to 06/01. If the 05/10 date was postponed only after it passed, round 1 is 'Extended; Enforced'.</t>
+          <t>If Party B was outside the 11, it needs its own Contact/NDA row and the non-submitter residual (#15) becomes 17. If the two railroads signed, the totals rise. The auction screen stays Met under every reading.</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -4496,27 +4474,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>How many confidentiality agreements were signed, and is Party B among the 11 strategic signers?</t>
+          <t>Deadline outcomes for each round.</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Treat the March-April wave as 25 (11 strategic, 14 financial), with Party B inside it. Party C signed separately in July, giving 26. The auction screen is Met either way.</t>
+          <t>Round 1: 05/10 superseded before arrival, no outcome; 05/19 Unclear. Round 2: 07/20 Late bids accepted. Round 3: No deadline stated.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>The filing counts 11 plus 14 (p. 28) and '25 of whom entered into confidentiality agreements' in its Reasons section (p. 33), but Party C 'had not previously been part of the process' (p. 29). Party B first appears at an 04/21 meeting (p. 28).</t>
+          <t>The 05/10 date was “subsequently postponed” to 05/19; the revision date is not reported (p. 29). The IOIs arrived “between May 19, 2016 and June 1, 2016” (p. 29), with no per-bid days. G&amp;W's LOI was dated 07/21, a day after the 07/20 due date, and was considered (p. 29). G&amp;W's 08/12 offer expiry is not a bid deadline (p. 31).</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>#6-10, #15, #20</t>
+          <t>#11, #12, #13, #14, #18, #23, #31</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>If B is separate, it gets its own NDA row and #15 becomes 26 − 9 = 17. If the two approached Class I railroads signed, the residual grows too.</t>
+          <t>If 05/10 arrived before the postponement, it gets a Deadline row and the outcome Extended. If some IOIs are shown to have arrived after 05/19, round 1 becomes Late bids accepted; if all arrived on 05/19, Enforced.</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -4529,27 +4507,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Should Party B have a Bid reaffirmed row on 08/04 (returned draft) at $24.00?</t>
+          <t>Party B late-reconfirmation sequence: are #44 and #48 correct Bid reaffirmed rows?</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Yes, flagged. The Committee moved to complete the merger agreement with B on 08/04, and B's counsel returned a revised draft that day. B's standing LOI sat in a Not final round.</t>
+          <t>Yes. #44 is reaffirmed by returned draft (08/04): the Committee decided to complete the agreement with B (#43), B's latest priced row (#24) sits in round 2, which was Not final, and B's counsel returned a revised draft. #48 is by price confirmation (08/12).</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>p. 31: 'proceed to complete the negotiation of the merger agreement with Party B'; 'legal counsel for Party B provided a revised draft'. Same-day order is not stated.</t>
+          <t>p. 31: “legal counsel for Party B provided a revised draft of the merger agreement” on 08/04, after the prioritize-B decision. p. 32: B “indicated that it would not increase its price”. Conditions went from Light (expedited diligence still open) to Light (only final documentation left).</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>#24, #44, #46</t>
+          <t>#24, #43, #44, #48, #50</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Without it, B's last priced row is the round-2 LOI (already Formal by markup), so the loss is small. The 08/12 refusal (#51) confirms B stood at $24.00.</t>
+          <t>If “would not increase” is not an express confirmation, delete #48 and keep the fact in #50's Note. B's formality is unchanged either way (#24 is already Formal on its mark-up).</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -4562,27 +4540,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Formality of Party E's and Party D's bids.</t>
+          <t>Is Party E's LOI Informal although it came with an issues list on the agreements?</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>E stays Informal (#25, #41, #42): it sent an issues list, not a markup. D is Formal on 07/20 (markup) and on 08/01 by continuity.</t>
+          <t>Yes, Informal. It came with a summary of material issues, not a mark-up.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>p. 29: B, G&amp;W and D 'provided mark-ups'; E 'provided a summary of material issues and proposed changes'. D's 08/01 revision (p. 30) mentions no new markup.</t>
+          <t>p. 29: Parties B, G&amp;W and D “provided mark-ups”, while Party E “provided a summary of material issues and proposed changes”. Under C13 an issues list alone is not a returned mark-up. The 60-day exclusivity condition keeps it Heavy either way.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>#25, #26, #40, #41, #42</t>
+          <t>#25, #39, #42</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Treating E's issues list as engaging with definitive terms makes three E rows Formal. Treating D's re-entry after its exit as a break makes #40 Informal.</t>
+          <t>If Formal, round 2 has four Formal LOIs instead of three, and E's continuing proposals (#39, #42) become Formal.</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -4595,66 +4573,33 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Was Party E out by 08/04, or still live until signing?</t>
+          <t>Parties D and E after their 07/27 exclusion: were they live, in which round, and how did they leave?</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Out by 08/04 (inferred Dropped by target): the Committee named only G&amp;W and B as continuing.</t>
+          <t>Record Re-entered on 07/29, with their 08/01 bids in round 3 as “still being received, not admitted”. D Withdrew (“at that time”); E is Not selected at signing (inferred).</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>p. 31: 'continue diligence and negotiations with both G&amp;W and Party B'. E's confirmed $21.26 offer (p. 30) is never mentioned again.</t>
+          <t>p. 30: D and E “expressed interest in reengaging” after being told they were out; the Committee considered and clarified their 08/01 LOIs; D stopped diligence “at that time” when refused a no-other-agreement commitment; E is not mentioned after 08/02.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>#45</t>
+          <t>#33, #34, #36, #37, #38, #39, #40, #41, #42, #51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>As Not selected at signing on 08/12, three bidders were live from 08/04 to 08/12, not two.</t>
+          <t>If their approaches are not treated as re-entry, drop #36–37 and treat #38–42 as post-exit proposals; live units in round 3 would be 2, not up to 4. E could instead be read as dropped by the target by 08/04 (#43).</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Q7</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>What happened to Party A, the party whose interest set off the process?</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Keep it inside the anonymous residuals, with no exit row of its own: most likely a non-submitter (#15) or one of the two low IOI bidders (#16).</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Party A signed an NDA as one of the 11 strategic signers (p. 28). The filing never mentions it after March, and the named LOI bidders exclude it (pp. 29-30).</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>#1, #15, #16</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>If the reviewer knows Party A bid, one IOI in #14 is A's and it is one of the two excluded low bidders, which changes #15/#16 notes only.</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4665,7 +4610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4692,7 +4637,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Providence and Worcester Railroad Company (PWRR; NASDAQ: PWX)</t>
+          <t>Providence and Worcester Railroad Company (PWRR)</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4661,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Strategic: owns or leases 121 freight railroads worldwide (p. 1)</t>
+          <t>Strategic: G&amp;W owns or leases 121 freight railroads (p. 21)</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4673,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>$25.00 per common share in cash, without interest; each preferred share is deemed converted into 100 common shares</t>
+          <t>$25.00 per share in cash, without interest; each preferred share converts into 100 common shares first (p. 27). No CVR. Termination fee $3.785 million.</t>
         </is>
       </c>
     </row>
@@ -4738,8 +4683,10 @@
           <t>Merger agreement signed</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>42594</v>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>08/12/2016</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -4748,8 +4695,10 @@
           <t>Merger announced</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>42597</v>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>08/15/2016 (press release before market open)</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -4760,7 +4709,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DEFM14A; 09/20/2016 per supplied file name (letter to shareholders dated 09/19/2016)</t>
+          <t>DEFM14A definitive proxy statement dated 09/19/2016, filed 09/20/2016</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4721,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>27-32</t>
+          <t>pp. 27–32</t>
         </is>
       </c>
     </row>
@@ -4784,7 +4733,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Mixed: Party A's unsolicited interest in an equity stake (Q4 2015) led the Board to hire GHF; the sale process itself was target-led</t>
+          <t>Mixed: Party A's unsolicited interest in acquiring equity (Q4 2015) prompted the banker search; the Company then ran a target-led auction (pp. 27–28).</t>
         </is>
       </c>
     </row>
@@ -4803,77 +4752,89 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Auction screen</t>
+          <t>Earlier approaches</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Met: 25 NDAs per filing (11 strategic, 14 financial), plus Party C in July; 26 on the ledger (Q3)</t>
+          <t>None reported</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Whole-company bids</t>
+          <t>Auction screen</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Met (process 1): 26 parties: 25 confidentiality agreements from the March 2016 outreach (11 strategic, 14 financial, one per party) plus Party C (July 2016). Page 33 states a total of 25 parties. No post-signing additions.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Currency and units of bid prices</t>
+          <t>Whole-company bids</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>US dollars per common share, assuming conversion of preferred stock; G&amp;W's July offers included a $1.13 CVR</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Target financial advisers</t>
+          <t>Currency and units of bid prices</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Greene Holcomb &amp; Fisher LLC (GHF), whose business BMO Capital Markets Corp. acquired on 08/01/2016; sole financial adviser; BMO gave the fairness opinion</t>
+          <t>US dollars per share of common stock, assuming conversion of preferred into common; some bids also stated as implied equity value</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Target legal advisers</t>
+          <t>Target financial advisers</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Hinckley, Allen &amp; Snyder LLP; also an unnamed STB counsel</t>
+          <t>Greene Holcomb &amp; Fisher LLC (GHF), whose business BMO Capital Markets Corp. acquired on 08/01/2016; sole financial adviser; fairness opinion 08/12/2016. A BMO affiliate's roughly 5% participation in G&amp;W's credit facility was disclosed after signing and judged not material on 09/06/2016 (pp. 32, 41).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>Target legal advisers</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Hinckley, Allen &amp; Snyder LLP; also unnamed STB counsel. G&amp;W's counsel: Simpson Thacher &amp; Bartlett LLP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>Account</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>After Party A, a Class I rail partner, showed interest in an equity stake in late 2015, PWRR hired GHF and in March 2016 opened a broad auction. GHF contacted 29 buyers, 25 signed NDAs and nine gave IOIs of $17.93-$26.50. Seven advanced, late entrant Party C joined, and six LOIs came in during late July, led by Party B at $24.00. The Committee negotiated with B and G&amp;W; D and E briefly returned but fell away. B was about to sign when G&amp;W raised its offer to $25.00 in cash on 08/12. B would not match, and PWRR signed with G&amp;W that day.</t>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>After Party A, a Class I rail partner, showed interest in acquiring equity in late 2015, PWRR hired GHF and in March 2016 decided to solicit buyers broadly. GHF contacted 29 parties; 25 signed confidentiality agreements, and nine submitted IOIs of $17.93–$26.50 per share. Seven advanced to management presentations and diligence, late entrant Party C joined, and six LOIs arrived in late July at $19.20–$24.00. The Transaction Committee chose Party B ($24.00, with mark-ups) and G&amp;W ($22.15 with a CVR) for confirmatory diligence. Parties D and E briefly returned with higher bids but fell away. On 08/12/2016 G&amp;W raised to $25.00 all cash, Party B declined to improve, and PWRR signed with G&amp;W that day.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B17"/>
+  <autoFilter ref="A1:B18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/extraction/providence-worcester.xlsx
+++ b/extraction/providence-worcester.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal facts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rounds'!$A$1:$J$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deal facts'!$A$1:$B$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,14 +439,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V53"/>
+  <dimension ref="A1:V63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
@@ -455,12 +455,12 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
@@ -620,12 +620,12 @@
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>First contact. At a meeting on joint commercial opportunities with CEO Eder and CCO Rogers, Party A (a Class I rail partner) suggested joint ventures and some interest in acquiring equity; no price, scope unresolved. Board responded by forming a subcommittee to interview bankers.</t>
+          <t>First contact. At a meeting on joint commercial opportunities, Party A (a Class I rail partner) floated joint ventures and "some interest in acquiring equity"; no price, scope (stake or whole company) unstated. Board then formed a subcommittee to interview bankers for possible negotiations with Party A.</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Party A suggested possible joint venture arrangements and expressed some interest in acquiring equity in the Company to further develop strategic opportunities (p. 27)</t>
+          <t>Party A suggested possible joint venture arrangements and expressed some interest in acquiring equity in the Company to further develop strategic opportunities and enhance regional connectivity (p. 27)</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Greene Holcomb &amp; Fisher LLC (GHF; later BMO Capital Markets Corp.)</t>
+          <t>Greene Holcomb &amp; Fisher LLC (GHF), later BMO Capital Markets Corp.</t>
         </is>
       </c>
       <c r="D3" s="2" t="n"/>
@@ -680,7 +680,7 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Target's financial adviser (sole). Recommended by subcommittee (Barrett, Anderson) after interviewing several banks; Board approved and engaged it 01/27/2016. BMO acquired GHF's business 08/01/2016 (same adviser, no new row); BMO gave the fairness opinion 08/12/2016; fee about $2.52 million (p. 41).</t>
+          <t>Target's financial adviser, recommended by the board subcommittee after interviewing several banks; engaged at the 01/27/2016 meeting. BMO acquired GHF's business on 08/01/2016 and continued the mandate; BMO gave the 08/12/2016 fairness opinion.</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Target (Board)</t>
+          <t>Providence and Worcester Railroad (target)</t>
         </is>
       </c>
       <c r="D4" s="2" t="n"/>
@@ -736,19 +736,15 @@
       <c r="O4" s="2" t="n"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Board adopted GHF's proposed process: continue discussions with Party A and solicit interest from other third parties in a change-in-control deal. Formed Transaction Committee (Barrett, Anderson, Garvey); approval reserved to full Board. Management met Party A 03/22–23.</t>
+          <t>Board accepted GHF's proposed process: continue discussions with Party A and solicit other parties' interest in a change in control transaction. Appointed a Transaction Committee (Barrett, Anderson, Garvey) to oversee it; only the full Board could approve a deal. Management met Party A 03/22–03/23.</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Representatives of GHF then proposed a process pursuant to which the Company would proceed with discussions with Party A and also solicit interest from other potential third parties (p. 27)</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>the Company would proceed with discussions with Party A and also solicit interest from other potential third parties regarding a change in control transaction (p. 27)</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="n"/>
       <c r="S4" s="2" t="n"/>
       <c r="T4" s="3" t="n">
         <v>42443</v>
@@ -771,7 +767,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Hinckley, Allen &amp; Snyder LLP</t>
+          <t>Hinckley, Allen &amp; Snyder LLP (Hinckley Allen)</t>
         </is>
       </c>
       <c r="D5" s="2" t="n"/>
@@ -796,12 +792,12 @@
       <c r="O5" s="2" t="n"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Target's legal counsel; first seen acting 03/24/2016, attending all Transaction Committee meetings. Negotiated the merger agreement drafts with both finalists' counsel.</t>
+          <t>Target's legal counsel; first shown acting at the 03/24/2016 Transaction Committee meeting and attended all its meetings; negotiated the merger documents with Party B's counsel and Simpson Thacher.</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>representatives of each of GHF and the Company’s legal counsel, Hinckley, Allen &amp; Snyder LLP (which we refer to as “Hinckley Allen”), participated in all meetings of the Transaction Committee (p. 28)</t>
+          <t>the Company’s legal counsel, Hinckley, Allen &amp; Snyder LLP (which we refer to as “Hinckley Allen”), participated in all meetings of the Transaction Committee (p. 28)</t>
         </is>
       </c>
       <c r="R5" s="2" t="n"/>
@@ -822,12 +818,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>week of 03/28/2016</t>
+          <t>03/24/2016</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Target (GHF)</t>
+          <t>Providence and Worcester Railroad (target)</t>
         </is>
       </c>
       <c r="D6" s="2" t="n"/>
@@ -852,28 +848,28 @@
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>GHF began outreach under the Transaction Committee's 03/24/2016 authorization to contact Party A and other potential buyers: 11 strategic and 18 financial buyers contacted (#6–7). Confidentiality agreements had no standstill.</t>
+          <t>Transaction Committee authorized GHF to contact Party A and other potential buyers about a change in control transaction; GHF carried this out in the week of 03/28/2016 (#6–#7). Round opened at the authorizing decision (E6).</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>During the week of March 28, 2016, in accordance with the Transaction Committee’s directives, representatives of GHF contacted 11 potential strategic buyers (including Party A) and 18 potential financial buyers. (p. 28)</t>
+          <t>The Transaction Committee authorized GHF to contact Party A as well as other potential buyers to determine their level of interest in a change in control transaction. (p. 28)</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S6" s="2" t="n"/>
       <c r="T6" s="3" t="n">
-        <v>42460</v>
+        <v>42453</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>42457</v>
+        <v>42453</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>42463</v>
+        <v>42453</v>
       </c>
     </row>
     <row r="7">
@@ -887,7 +883,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11 potential strategic buyers (incl. Party A; G&amp;W, Parties B, E, F assumed)</t>
+          <t>10 potential strategic buyers (other than Party A)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -912,13 +908,13 @@
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated (GHF). Stated total 11 includes Party A, first contacted Q4 2015 (#1); kept in Count so the row reconciles to the total. G&amp;W, Party B, Party E and Party F assumed members (no other strategic outreach reported besides #10 and Party C).</t>
+          <t>Target-initiated outreach by GHF. Filing total: 11 strategic buyers contacted, including Party A (first contact at #1). Whether G&amp;W (#10, #14), Party B (#13, #15) or the two Class I railroads (#11) are among the 11 is not stated.</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -928,7 +924,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S7" s="2" t="n"/>
@@ -953,7 +949,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>18 potential financial buyers (incl. Party D, assumed)</t>
+          <t>18 potential financial buyers</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -984,7 +980,7 @@
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated (GHF). Party D assumed a member (only financial outreach reported). 4 of the 18 did not sign (#9) and never entered.</t>
+          <t>Target-initiated outreach by GHF. 14 of the 18 later signed confidentiality agreements (#9); the other 4 never entered.</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -992,11 +988,7 @@
           <t>representatives of GHF contacted 11 potential strategic buyers (including Party A) and 18 potential financial buyers (p. 28)</t>
         </is>
       </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
+      <c r="R8" s="2" t="n"/>
       <c r="S8" s="2" t="n"/>
       <c r="T8" s="3" t="n">
         <v>42460</v>
@@ -1014,12 +1006,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>after week of 03/28/2016</t>
+          <t>after week of 03/28/2016 (undated)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11 strategic NDA signers (incl. Party A, G&amp;W; Parties B, E, F assumed)</t>
+          <t>11 potential strategic buyers (incl. Party A)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1050,7 +1042,7 @@
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Entry. All 11 contacted strategic buyers signed; no standstill. Stated wave total 25 = 11 + 14 (#9); p. 33 also cites 25 signers. Party B first named 04/21/2016 (introductory meeting); assumed a member. All signers later got the memorandum. Signing dates not reported.</t>
+          <t>All 11 contacted strategic buyers, including Party A, signed; no standstill. Execution dates not given. G&amp;W and Party B (#14, #15) may be among the 11: not established. NDA signers received the Company memorandum.</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1060,7 +1052,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S9" s="2" t="n"/>
@@ -1078,12 +1070,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>after week of 03/28/2016</t>
+          <t>after week of 03/28/2016 (undated)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>14 financial NDA signers (incl. Party D, assumed)</t>
+          <t>14 potential financial buyers</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1114,7 +1106,7 @@
       <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Entry. 14 of 18 contacted financial buyers signed; no standstill. Part of the stated 25 (#8). Signing dates not reported.</t>
+          <t>No standstill; undated. The filing later says 25 parties signed confidentiality agreements (p. 33), which equals 11 + 14 and leaves no room for Party C (#24) or for G&amp;W and Party B outside #8.</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1124,7 +1116,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S10" s="2" t="n"/>
@@ -1142,12 +1134,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>by 04/07/2016</t>
+          <t>04/03/2016–04/06/2016</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2 additional Class I railroads</t>
+          <t>5 potential strategic buyers (incl. G&amp;W)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1172,32 +1164,34 @@
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
       <c r="M11" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N11" s="2" t="n"/>
       <c r="O11" s="2" t="n"/>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated by management, reported 04/07/2016. Assumed outside the 11 (#6) because the filing calls them “additional”; response and any NDA not reported, so no entry recorded. Contact date not reported.</t>
+          <t>Introductory meetings held by GHF and management at the 2016 Connections Convention. First contact for G&amp;W unless it was among the 11 contacted at #6; overlap with #6 not stated. On 04/07 GHF was told to confirm these five parties' continuing interest.</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Mr. Noreck reported that the Company had also approached two additional Class I railroads to determine their interest in a possible transaction. (p. 28)</t>
+          <t>held a series of introductory meetings with five potential strategic buyers (including G&amp;W) at the American Short Line and Regional Railroad Association’s 2016 Connections Convention (p. 28)</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S11" s="2" t="n"/>
       <c r="T11" s="3" t="n">
-        <v>42467</v>
-      </c>
-      <c r="U11" s="2" t="n"/>
+        <v>42464</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>42463</v>
+      </c>
       <c r="V11" s="3" t="n">
-        <v>42467</v>
+        <v>42466</v>
       </c>
     </row>
     <row r="12">
@@ -1206,18 +1200,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>by 04/27/2016</t>
+          <t>by 04/07/2016</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Target (GHF)</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n"/>
+          <t>2 additional Class I railroads</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Deadline set</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
@@ -1231,17 +1229,19 @@
       <c r="J12" s="2" t="n"/>
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="n"/>
+      <c r="M12" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="N12" s="2" t="n"/>
       <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Each potential buyer told to submit a non-binding IOI by 05/10/2016; reported at 04/27/2016 Board meeting, communication date not reported. Memorandum prepared with GHF went to all NDA signers, incl. Party A, Party B, G&amp;W.</t>
+          <t>Target-initiated: management approached two further Class I railroads about a possible transaction, reported 04/07/2016. Whether they are among the 11 at #6 or later signed NDAs is not stated; not mentioned again.</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>each potential buyer had been advised to submit a non-binding indication of interest by May 10, 2016 (p. 29)</t>
+          <t>the Company had also approached two additional Class I railroads to determine their interest in a possible transaction (p. 28)</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
@@ -1251,13 +1251,11 @@
       </c>
       <c r="S12" s="2" t="n"/>
       <c r="T12" s="3" t="n">
-        <v>42472</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>42457</v>
-      </c>
+        <v>42467</v>
+      </c>
+      <c r="U12" s="2" t="n"/>
       <c r="V12" s="3" t="n">
-        <v>42487</v>
+        <v>42467</v>
       </c>
     </row>
     <row r="13">
@@ -1266,18 +1264,18 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>after due date set; before 05/19/2016</t>
+          <t>by 04/27/2016</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Target (GHF)</t>
+          <t>Providence and Worcester Railroad (target)</t>
         </is>
       </c>
       <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Deadline revised</t>
+          <t>Deadline set</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -1296,28 +1294,28 @@
       <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>IOI due date moved 05/10 → 05/19/2016 so buyers had time for their most compelling offers. Revision date not reported; treated as before 05/10 arrived (superseded before arrival).</t>
+          <t>Each potential buyer told to submit a non-binding indication of interest by 05/10/2016. Communication date not stated; reported at the 04/27/2016 board executive session. Window starts at the outreach.</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>which deadline was subsequently postponed to May 19, 2016 to ensure the potential buyers had sufficient time to formulate their most compelling offers (p. 29)</t>
+          <t>each potential buyer had been advised to submit a non-binding indication of interest by May 10, 2016 (p. 29)</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S13" s="2" t="n"/>
       <c r="T13" s="3" t="n">
-        <v>42482</v>
+        <v>42472</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>42457</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>42508</v>
+        <v>42487</v>
       </c>
     </row>
     <row r="14">
@@ -1326,18 +1324,22 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>05/19/2016</t>
+          <t>04/21/2016</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n"/>
+          <t>Party B</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -1351,17 +1353,19 @@
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="n"/>
+      <c r="M14" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="n"/>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>IOI due date reached. Nine IOIs arrived between 05/19 and 06/01 (#14); the filing does not say whether any came after 05/19. Outcome Unclear.</t>
+          <t>Introductory meeting of the Company and GHF with "another potential strategic buyer". Whether Party B was among the 11 contacted at #6 is not stated.</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Between May 19, 2016 and June 1, 2016, the Company received nine written indications of interest (“IOIs”) from potential buyers (p. 29)</t>
+          <t>on April 21, 2016, the Company and representatives of GHF held an introductory meeting with another potential strategic buyer (“Party B”). (p. 28)</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
@@ -1371,13 +1375,13 @@
       </c>
       <c r="S14" s="2" t="n"/>
       <c r="T14" s="3" t="n">
-        <v>42509</v>
+        <v>42481</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>42509</v>
+        <v>42481</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>42509</v>
+        <v>42481</v>
       </c>
     </row>
     <row r="15">
@@ -1386,22 +1390,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/19/2016–06/01/2016</t>
+          <t>undated; by memorandum distribution</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9 IOI bidders (incl. G&amp;W, Parties B, D, E, F; 4 unnamed)</t>
+          <t>G&amp;W (Genesee &amp; Wyoming Inc.)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -1410,40 +1414,24 @@
       <c r="G15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="4" t="n">
-        <v>17.93</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Conditions not reported. Written non-binding IOIs; group range (preferred converted) implying equity values $90M–$134M; individual prices undisclosed. Members G&amp;W, B, D, E, F established by their later advancement (#17); mixed types, split not given.</t>
+          <t>G&amp;W had signed a confidentiality agreement and received the Company memorandum; execution date not given. Kept outside the 11 at #8 because membership is not established; if inside, the NDA total falls by one.</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>the Company received nine written indications of interest (“IOIs”) from potential buyers, with offer prices per share ranging from $17.93 to $26.50 (p. 29)</t>
+          <t>which was distributed to the potential buyers, including Party A, Party B and G&amp;W, that had executed confidentiality agreements (p. 28)</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
@@ -1453,14 +1441,12 @@
       </c>
       <c r="S15" s="2" t="n"/>
       <c r="T15" s="3" t="n">
-        <v>42509</v>
+        <v>42481</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>42509</v>
-      </c>
-      <c r="V15" s="3" t="n">
-        <v>42522</v>
-      </c>
+        <v>42457</v>
+      </c>
+      <c r="V15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1468,22 +1454,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>by 06/01/2016</t>
+          <t>undated; by memorandum distribution</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>16 NDA signers without an IOI</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Did not submit</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -1498,41 +1484,33 @@
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
       <c r="M16" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Inferred: 25 wave signers (#8–9) − 9 IOI bidders (#14) = 16, all of whom had been asked for IOIs (#11). Identities and types unknown; may include Party A, whose IOI status is not reported.</t>
+          <t>Party B had signed a confidentiality agreement and received the Company memorandum; execution date not given. Kept outside the 11 at #8 because membership is not established; if inside, the NDA total falls by one.</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Between May 19, 2016 and June 1, 2016, the Company received nine written indications of interest (“IOIs”) from potential buyers (p. 29)</t>
+          <t>which was distributed to the potential buyers, including Party A, Party B and G&amp;W, that had executed confidentiality agreements (p. 28)</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S16" s="2" t="n"/>
       <c r="T16" s="3" t="n">
-        <v>42517</v>
-      </c>
-      <c r="U16" s="2" t="n"/>
-      <c r="V16" s="3" t="n">
-        <v>42522</v>
-      </c>
+        <v>42481</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>42457</v>
+      </c>
+      <c r="V16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1540,22 +1518,18 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>05/23/2016–06/01/2016</t>
+          <t>after 05/10 due date set; before 05/19/2016</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2 lowest IOI bidders (unnamed)</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+          <t>Providence and Worcester Railroad (target)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Deadline revised</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -1569,35 +1543,33 @@
       <c r="J17" s="2" t="n"/>
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
-      <c r="M17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>Lower offer than rivals</t>
-        </is>
-      </c>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
       <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Transaction Committee excluded the two low bidders from management presentations to save management time (decided across its 05/23 and 06/01 meetings). Identities, types and prices not disclosed; may include Party A.</t>
+          <t>IOI due date postponed from 05/10 to 05/19/2016 so buyers had time "to formulate their most compelling offers". Revision date not stated; read as made before 05/10 arrived (inferred from the stated purpose).</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>the Transaction Committee concluded that the two low bidders should be excluded from that process (p. 29)</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="n"/>
+          <t>which deadline was subsequently postponed to May 19, 2016 to ensure the potential buyers had sufficient time to formulate their most compelling offers (p. 29)</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
       <c r="S17" s="2" t="n"/>
       <c r="T17" s="3" t="n">
-        <v>42517</v>
+        <v>42483</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>42513</v>
+        <v>42457</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>42522</v>
+        <v>42509</v>
       </c>
     </row>
     <row r="18">
@@ -1606,25 +1578,25 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>05/23/2016–06/01/2016</t>
+          <t>05/19/2016</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Target (Transaction Committee)</t>
+          <t>Providence and Worcester Railroad (target)</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" s="2" t="n"/>
       <c r="I18" s="2" t="n"/>
@@ -1636,28 +1608,28 @@
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Committee advanced 7 of 9 IOI bidders (G&amp;W, Parties B, D, E, F, one unnamed strategic, one unnamed financial) to in-person management presentations and further diligence; all seven got data-room access. LOI request followed (#18).</t>
+          <t>Operative IOI due date. IOIs arrived between 05/19 and 06/01/2016 and were considered by the Transaction Committee on 05/23 and 06/01 (#18).</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>The Transaction Committee authorized representatives of GHF to schedule in-person management presentations with the remaining seven potential buyers and allow these parties to conduct additional due diligence. (p. 29)</t>
+          <t>which deadline was subsequently postponed to May 19, 2016 (p. 29)</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S18" s="2" t="n"/>
       <c r="T18" s="3" t="n">
-        <v>42517</v>
+        <v>42509</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>42513</v>
+        <v>42509</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>42522</v>
+        <v>42509</v>
       </c>
     </row>
     <row r="19">
@@ -1666,58 +1638,80 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>mid-June 2016</t>
+          <t>05/19/2016–06/01/2016</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Target (GHF)</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n"/>
+          <t>9 IOI bidders</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Deadline set</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="M19" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="N19" s="2" t="n"/>
       <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>At Committee direction, GHF told all potential buyers to submit non-binding LOIs by 07/20/2016 with mark-ups of the merger agreement, disclosure letter and voting agreement, pricing 100% of common per share. Company drafts posted 06/29, 06/30, 07/11.</t>
+          <t>Conditions not reported (cohort). Non-binding written IOIs; per share assuming preferred converted to common; equity values $90m–$134m. Inferred members: G&amp;W and Parties B, D, E, F (all later LOI bidders except Party C), two later non-LOI bidders (#28–#29) and two low bidders (#20). Party A unknown.</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>representatives of GHF instructed all potential buyers to submit non-binding letters of intent (“LOIs”) by July 20, 2016, together with mark-ups of the forms of merger agreement (p. 29)</t>
+          <t>the Company received nine written indications of interest (“IOIs”) from potential buyers, with offer prices per share ranging from $17.93 to $26.50 (p. 29)</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q3</t>
+          <t>Q4; Q5</t>
         </is>
       </c>
       <c r="S19" s="2" t="n"/>
       <c r="T19" s="3" t="n">
-        <v>42536</v>
+        <v>42509</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>42532</v>
+        <v>42509</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>42540</v>
+        <v>42522</v>
       </c>
     </row>
     <row r="20">
@@ -1726,60 +1720,68 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>early July 2016</t>
+          <t>by 05/19/2016</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>NDA signers not submitting IOIs</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Bidder interest</t>
+          <t>Did not submit</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="n"/>
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" s="2" t="n"/>
-      <c r="O20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>First contact: a strategic buyer new to the process approached management and expressed interest in acquiring the Company; no price.</t>
+          <t>Count: 16–18. 25 signers (#8–#9) plus 0–2 for G&amp;W and Party B if outside #8, less 9 IOI bidders (#18). May include Party A. The filing's 25 total (p. 33) conflicts with Party C's later NDA (Q3).</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>a potential strategic buyer that had not previously been part of the process (“Party C”) approached the Company’s management and expressed interest in acquiring the Company (p. 29)</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="n"/>
+          <t>Between May 19, 2016 and June 1, 2016, the Company received nine written indications of interest (“IOIs”) from potential buyers (p. 29)</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S20" s="2" t="n"/>
       <c r="T20" s="3" t="n">
-        <v>42556</v>
-      </c>
-      <c r="U20" s="3" t="n">
-        <v>42552</v>
-      </c>
+        <v>42509</v>
+      </c>
+      <c r="U20" s="2" t="n"/>
       <c r="V20" s="3" t="n">
-        <v>42561</v>
+        <v>42509</v>
       </c>
     </row>
     <row r="21">
@@ -1788,29 +1790,29 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>early July 2016 (before 07/12/2016)</t>
+          <t>05/23/2016–06/01/2016</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>2 low IOI bidders</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="n"/>
@@ -1818,34 +1820,34 @@
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Lower offer than rivals</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Entry (late entrant). Received the memorandum given to the other buyers. Outside the 25-signer wave total (#8–9).</t>
+          <t>Transaction Committee excluded "the two low bidders" from management presentations, citing the management time presentations would take. Identities and prices not disclosed.</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>After executing a confidentiality agreement, Party C was provided the memorandum concerning the Company provided to the other potential buyers. (p. 29)</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
+          <t>the Transaction Committee concluded that the two low bidders should be excluded from that process (p. 29)</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="n"/>
       <c r="S21" s="2" t="n"/>
       <c r="T21" s="3" t="n">
-        <v>42557</v>
+        <v>42517</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>42552</v>
+        <v>42513</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>42563</v>
+        <v>42522</v>
       </c>
     </row>
     <row r="22">
@@ -1854,22 +1856,18 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>07/12/2016</t>
+          <t>05/23/2016–06/01/2016</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Providence and Worcester Railroad (target)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -1878,52 +1876,38 @@
       <c r="G22" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H22" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n"/>
       <c r="N22" s="2" t="n"/>
       <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: no data room or management presentation until after this IOI (07/14). Unsolicited entry IOI while round 2 was open; implies equity value $108M.</t>
+          <t>Transaction Committee advanced the remaining seven IOI bidders to in-person management presentations, further diligence and data-site access, given alike to all seven. Inferred members: G&amp;W, Parties B, D, E, F, one unnamed strategic, one unnamed financial.</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>On July 12, 2016, Party C submitted an IOI with an offer price per share of $21.00 (implying an equity value of $108 million). (p. 29)</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="n"/>
+          <t>The Transaction Committee authorized representatives of GHF to schedule in-person management presentations with the remaining seven potential buyers and allow these parties to conduct additional due diligence. (p. 29)</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>Q2; Q5</t>
+        </is>
+      </c>
       <c r="S22" s="2" t="n"/>
       <c r="T22" s="3" t="n">
-        <v>42563</v>
+        <v>42517</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>42563</v>
+        <v>42513</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>42563</v>
+        <v>42522</v>
       </c>
     </row>
     <row r="23">
@@ -1932,22 +1916,18 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>07/12/2016–07/14/2016</t>
+          <t>mid-June 2016</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Providence and Worcester Railroad (target)</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Deadline set</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -1961,31 +1941,33 @@
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
-      <c r="M23" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M23" s="2" t="n"/>
       <c r="N23" s="2" t="n"/>
       <c r="O23" s="2" t="n"/>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>Catch-up access: after its IOI, Party C was admitted to the data room and given a management presentation by telephone on 07/14 (the other seven had in-person presentations).</t>
+          <t>GHF told all potential buyers to submit non-binding LOIs by 07/20/2016 with mark-ups of the merger agreement, disclosure letter and voting agreement, pricing 100% of common per share (preferred converted). Drafts posted 06/29, 06/30 and 07/11/2016.</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>Subsequently, Party C was provided access to the internet data site and the Company’s management held a management presentation with Party C by telephone on July 14, 2016. (p. 29)</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="n"/>
+          <t>representatives of GHF instructed all potential buyers to submit non-binding letters of intent (“LOIs”) by July 20, 2016, together with mark-ups of the forms of merger agreement (p. 29)</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
       <c r="S23" s="2" t="n"/>
       <c r="T23" s="3" t="n">
-        <v>42564</v>
+        <v>42536</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>42563</v>
+        <v>42532</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>42565</v>
+        <v>42540</v>
       </c>
     </row>
     <row r="24">
@@ -1994,18 +1976,22 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/20/2016</t>
+          <t>early July 2016</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n"/>
+          <t>Party C</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Bidder interest</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -2019,33 +2005,31 @@
       <c r="J24" s="2" t="n"/>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
-      <c r="M24" s="2" t="n"/>
+      <c r="M24" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N24" s="2" t="n"/>
       <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>LOI due date reached. G&amp;W's LOI dated 07/21 (#31) was a late bid and was considered. Other five LOIs came “late July” (by the 07/27 review), arrival days not reported. Six LOIs ranged $19.20–$24.00.</t>
+          <t>First contact. A strategic buyer not previously part of the process approached management unprompted and expressed interest in acquiring the Company; no price.</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>In late July 2016, the Company received six LOIs with offer prices per share ranging from $19.20 to $24.00 (implying equity values of $96 million to $121 million). (p. 29)</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+          <t>a potential strategic buyer that had not previously been part of the process (“Party C”) approached the Company’s management and expressed interest in acquiring the Company (p. 29)</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="n"/>
       <c r="S24" s="2" t="n"/>
       <c r="T24" s="3" t="n">
-        <v>42571</v>
+        <v>42556</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>42571</v>
+        <v>42552</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>42571</v>
+        <v>42561</v>
       </c>
     </row>
     <row r="25">
@@ -2054,12 +2038,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>late July 2016</t>
+          <t>early July 2016 (before 07/12/2016)</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>Party C</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2069,7 +2053,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -2078,27 +2062,11 @@
       <c r="G25" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H25" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="I25" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="n"/>
       <c r="M25" s="2" t="n">
         <v>1</v>
       </c>
@@ -2106,28 +2074,28 @@
       <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>Subject to expedited diligence review. Non-binding LOI delivered with mark-ups of the draft merger agreement and voting agreement, hence Formal. Highest LOI.</t>
+          <t>Party C signed a confidentiality agreement, then received the Company memorandum given to other buyers. Not covered by the 25-party total implied by #8–#9 (Q3).</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>Party B submitted an LOI to acquire the Company for a price of $24.00 per share (subject to an expedited diligence review). (p. 29)</t>
+          <t>After executing a confidentiality agreement, Party C was provided the memorandum concerning the Company provided to the other potential buyers. (p. 29)</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S25" s="2" t="n"/>
       <c r="T25" s="3" t="n">
-        <v>42571</v>
+        <v>42557</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>42571</v>
+        <v>42552</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>42578</v>
+        <v>42563</v>
       </c>
     </row>
     <row r="26">
@@ -2136,12 +2104,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>late July 2016</t>
+          <t>07/12/2016</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Party E</t>
+          <t>Party C</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2161,10 +2129,10 @@
         <v>2</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>21.26</v>
+        <v>21</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>21.26</v>
+        <v>21</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2178,7 +2146,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Heavy</t>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
@@ -2188,28 +2156,28 @@
       <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60-day exclusivity period for diligence and definitive documentation requested. Sent a summary of material issues and proposed changes to the merger and voting agreements, not a mark-up, so Informal.</t>
+          <t>Conditions not reported. IOI, equity value $108m. A late entrant's catch-up IOI submitted while round-2 LOIs were pending; placed in round 2.</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>Party E (a strategic buyer) submitted an LOI to acquire the Company for a price of $21.26 per share (subject to a 60-day exclusivity period (p. 30)</t>
+          <t>On July 12, 2016, Party C submitted an IOI with an offer price per share of $21.00 (implying an equity value of $108 million). (p. 29)</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S26" s="2" t="n"/>
       <c r="T26" s="3" t="n">
-        <v>42571</v>
+        <v>42563</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>42571</v>
+        <v>42563</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>42578</v>
+        <v>42563</v>
       </c>
     </row>
     <row r="27">
@@ -2218,22 +2186,22 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>late July 2016</t>
+          <t>07/12/2016–07/14/2016</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>Party C</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -2242,27 +2210,11 @@
       <c r="G27" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H27" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n"/>
       <c r="M27" s="2" t="n">
         <v>1</v>
       </c>
@@ -2270,24 +2222,24 @@
       <c r="O27" s="2" t="n"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Four-week diligence period. LOI delivered with mark-ups of the draft merger agreement and voting agreement (p. 29), hence Formal.</t>
+          <t>Admitted with catch-up access: after its IOI, Party C got data-site access and a telephone management presentation on 07/14/2016, joining the other bidders' diligence six days before LOIs were due.</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>Party D (a financial buyer) submitted an LOI to acquire the Company for a price of $21.00 per share (subject to a four-week diligence period). (p. 30)</t>
+          <t>Subsequently, Party C was provided access to the internet data site and the Company’s management held a management presentation with Party C by telephone on July 14, 2016. (p. 29)</t>
         </is>
       </c>
       <c r="R27" s="2" t="n"/>
       <c r="S27" s="2" t="n"/>
       <c r="T27" s="3" t="n">
-        <v>42571</v>
+        <v>42564</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>42571</v>
+        <v>42563</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>42578</v>
+        <v>42565</v>
       </c>
     </row>
     <row r="28">
@@ -2296,22 +2248,18 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>late July 2016</t>
+          <t>07/20/2016</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Providence and Worcester Railroad (target)</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -2320,43 +2268,29 @@
       <c r="G28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H28" s="4" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="n"/>
       <c r="N28" s="2" t="n"/>
       <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30-day diligence period. LOI; no mark-up reported. Revises #21.</t>
+          <t>LOI due date. Six LOIs arrived in late July, G&amp;W's on 07/21 (#36); the Transaction Committee reviewed them on 07/22 and 07/27/2016.</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>Party C submitted an LOI to acquire the Company for a price of $19.30 per share (subject to a 30-day diligence period). (p. 30)</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="n"/>
+          <t>submit non-binding letters of intent (“LOIs”) by July 20, 2016 (p. 29)</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
       <c r="S28" s="2" t="n"/>
       <c r="T28" s="3" t="n">
         <v>42571</v>
@@ -2365,7 +2299,7 @@
         <v>42571</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>42578</v>
+        <v>42571</v>
       </c>
     </row>
     <row r="29">
@@ -2374,12 +2308,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>late July 2016</t>
+          <t>by 07/20/2016</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Party F</t>
+          <t>Unnamed strategic bidder (non-LOI)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2389,7 +2323,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Did not submit</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -2398,40 +2332,28 @@
       <c r="G29" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H29" s="4" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="I29" s="4" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" s="2" t="n"/>
       <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30-day due diligence period. LOI; no mark-up reported. Lowest LOI.</t>
+          <t>Reported: one strategic buyer among those invited "elected not to submit an LOI"; identity and IOI price not given. Could be Party A if Party A was among the seven advanced.</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>Party F (a strategic buyer) submitted an LOI to acquire the Company for a price of $19.20 per share (subject to a 30-day due diligence period). (p. 30)</t>
+          <t>One strategic buyer and one financial buyer elected not to submit an LOI. (p. 30)</t>
         </is>
       </c>
       <c r="R29" s="2" t="n"/>
@@ -2439,11 +2361,9 @@
       <c r="T29" s="3" t="n">
         <v>42571</v>
       </c>
-      <c r="U29" s="3" t="n">
+      <c r="U29" s="2" t="n"/>
+      <c r="V29" s="3" t="n">
         <v>42571</v>
-      </c>
-      <c r="V29" s="3" t="n">
-        <v>42578</v>
       </c>
     </row>
     <row r="30">
@@ -2452,17 +2372,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>by 07/27/2016</t>
+          <t>by 07/20/2016</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Unnamed strategic buyer 1</t>
+          <t>Unnamed financial bidder (non-LOI)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2492,7 +2412,7 @@
       <c r="O30" s="2" t="n"/>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>One of the seven round-2 participants (#17); elected not to submit an LOI. Not identified; could be Party A.</t>
+          <t>Reported: one financial buyer among those invited "elected not to submit an LOI"; identity and IOI price not given.</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -2507,7 +2427,7 @@
       </c>
       <c r="U30" s="2" t="n"/>
       <c r="V30" s="3" t="n">
-        <v>42578</v>
+        <v>42571</v>
       </c>
     </row>
     <row r="31">
@@ -2516,22 +2436,22 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>by 07/27/2016</t>
+          <t>late July 2016</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Unnamed financial buyer 1</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Did not submit</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -2540,28 +2460,40 @@
       <c r="G31" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="n"/>
+      <c r="H31" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
       <c r="M31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
+      <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>One of the seven round-2 participants (#17); elected not to submit an LOI.</t>
+          <t>Subject to an expedited diligence review. Non-binding LOI with mark-ups of the merger and voting agreements (Formal, E11). Highest LOI. Prices rested on differing assumptions about transaction expenses and change-in-control payments.</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>One strategic buyer and one financial buyer elected not to submit an LOI. (p. 30)</t>
+          <t>Party B submitted an LOI to acquire the Company for a price of $24.00 per share (subject to an expedited diligence review). (p. 29)</t>
         </is>
       </c>
       <c r="R31" s="2" t="n"/>
@@ -2569,7 +2501,9 @@
       <c r="T31" s="3" t="n">
         <v>42571</v>
       </c>
-      <c r="U31" s="2" t="n"/>
+      <c r="U31" s="3" t="n">
+        <v>42571</v>
+      </c>
       <c r="V31" s="3" t="n">
         <v>42578</v>
       </c>
@@ -2580,12 +2514,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>07/21/2016</t>
+          <t>late July 2016</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>G&amp;W (Genesee &amp; Wyoming Inc.)</t>
+          <t>Party E</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2605,10 +2539,10 @@
         <v>2</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>21.15</v>
+        <v>21.26</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>21.15</v>
+        <v>21.26</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2617,7 +2551,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Formal</t>
+          <t>Informal</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -2632,28 +2566,24 @@
       <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Three-week exclusive diligence period. $20.02 cash at closing plus $1.13 CVR tied to later sale of the South Quay property; CVR payment form not stated. With mark-ups of merger, voting and disclosure documents, hence Formal. Late: due 07/20.</t>
+          <t>Subject to a 60-day exclusivity period for diligence and documentation. Gave only a summary of material issues on the merger and voting agreements, not a mark-up (Informal).</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>G&amp;W submitted an LOI on July 21, 2016 to acquire the Company for a price of $21.15 per share (subject to a three-week exclusive diligence period). (p. 29)</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+          <t>Party E (a strategic buyer) submitted an LOI to acquire the Company for a price of $21.26 per share (subject to a 60-day exclusivity period for due diligence (p. 30)</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="n"/>
       <c r="S32" s="2" t="n"/>
       <c r="T32" s="3" t="n">
-        <v>42572</v>
+        <v>42571</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>42572</v>
+        <v>42571</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>42572</v>
+        <v>42578</v>
       </c>
     </row>
     <row r="33">
@@ -2662,12 +2592,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>07/26/2016</t>
+          <t>late July 2016</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>G&amp;W (Genesee &amp; Wyoming Inc.)</t>
+          <t>Party E</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2677,7 +2607,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Exclusivity changed</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -2686,27 +2616,11 @@
       <c r="G33" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H33" s="4" t="n">
-        <v>22.15</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>22.15</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
       <c r="M33" s="2" t="n">
         <v>1</v>
       </c>
@@ -2714,24 +2628,24 @@
       <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Diligence open per narrative: on-site diligence ran 07/27–08/11. Raised after GHF said price and CVR structure were not competitive: $21.02 cash plus $1.13 CVR. Revises #31; stays Formal.</t>
+          <t>Requested: Party E's LOI asked for a 60-day exclusivity period for due diligence and negotiation of definitive documentation. Not granted.</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>On July 26, 2016, in response to feedback from representatives of GHF indicating its price and CVR structure were not competitive, G&amp;W submitted a revised LOI (p. 29)</t>
+          <t>subject to a 60-day exclusivity period for due diligence and negotiation of definitive documentation (p. 30)</t>
         </is>
       </c>
       <c r="R33" s="2" t="n"/>
       <c r="S33" s="2" t="n"/>
       <c r="T33" s="3" t="n">
-        <v>42577</v>
+        <v>42571</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>42577</v>
+        <v>42571</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>42577</v>
+        <v>42578</v>
       </c>
     </row>
     <row r="34">
@@ -2740,22 +2654,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>07/27/2016 (told subsequently)</t>
+          <t>late July 2016</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Party C; Party E; Party F</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
@@ -2764,41 +2678,49 @@
       <c r="G34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
-      <c r="J34" s="2" t="n"/>
-      <c r="K34" s="2" t="n"/>
-      <c r="L34" s="2" t="n"/>
+      <c r="H34" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="M34" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>Lower offer than rivals</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N34" s="2" t="n"/>
       <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Committee chose G&amp;W and Party B for their higher offers; GHF later told the remaining bidders they were out. Decision dated 07/27: it relied on G&amp;W's 07/26 $22.15, as G&amp;W's $21.15 was below E's $21.26. E returns (#37).</t>
+          <t>Subject to a four-week diligence period. LOI with mark-ups of the draft merger and voting agreements (Formal, E11).</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>representatives of GHF subsequently contacted the remaining bidders to inform them that they were no longer involved in the process. (p. 30)</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
+          <t>Party D (a financial buyer) submitted an LOI to acquire the Company for a price of $21.00 per share (subject to a four-week diligence period). (p. 30)</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="n"/>
       <c r="S34" s="2" t="n"/>
       <c r="T34" s="3" t="n">
-        <v>42578</v>
+        <v>42571</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>42578</v>
+        <v>42571</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>42578</v>
@@ -2810,22 +2732,22 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>07/27/2016 (told subsequently)</t>
+          <t>late July 2016</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>Party C</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
@@ -2834,41 +2756,49 @@
       <c r="G35" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="n"/>
-      <c r="J35" s="2" t="n"/>
-      <c r="K35" s="2" t="n"/>
-      <c r="L35" s="2" t="n"/>
+      <c r="H35" s="4" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="M35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>Lower offer than rivals</t>
-        </is>
-      </c>
+      <c r="N35" s="2" t="n"/>
       <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>Same decision as #33: $21.00 LOI below G&amp;W and Party B. D returns (#36).</t>
+          <t>Subject to a 30-day diligence period. LOI; no mark-up reported. Down from its $21.00 IOI (#25).</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>representatives of GHF subsequently contacted the remaining bidders to inform them that they were no longer involved in the process. (p. 30)</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
+          <t>Party C submitted an LOI to acquire the Company for a price of $19.30 per share (subject to a 30-day diligence period). (p. 30)</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="n"/>
       <c r="S35" s="2" t="n"/>
       <c r="T35" s="3" t="n">
-        <v>42578</v>
+        <v>42571</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>42578</v>
+        <v>42571</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>42578</v>
@@ -2880,55 +2810,73 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>07/27/2016</t>
+          <t>late July 2016</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Target (Transaction Committee)</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="n"/>
+          <t>Party F</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="n"/>
-      <c r="J36" s="2" t="n"/>
-      <c r="K36" s="2" t="n"/>
-      <c r="L36" s="2" t="n"/>
-      <c r="M36" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N36" s="2" t="n"/>
       <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Committee selected G&amp;W and Party B for confirmatory diligence and merger-agreement negotiations; both did on-site financial, legal and environmental diligence 07/27–08/11. No bid due date set.</t>
+          <t>Subject to a 30-day due diligence period. LOI; no mark-up reported. Lowest LOI.</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>The Transaction Committee concluded that the Company should proceed with confirmatory due diligence and negotiations with G&amp;W and Party B because of the higher offers (p. 30)</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>Party F (a strategic buyer) submitted an LOI to acquire the Company for a price of $19.20 per share (subject to a 30-day due diligence period). (p. 30)</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="n"/>
       <c r="S36" s="2" t="n"/>
       <c r="T36" s="3" t="n">
-        <v>42578</v>
+        <v>42571</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>42578</v>
+        <v>42571</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>42578</v>
@@ -2940,35 +2888,51 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>07/29/2016</t>
+          <t>07/21/2016</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>G&amp;W</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Re-entered</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="n"/>
-      <c r="J37" s="2" t="n"/>
-      <c r="K37" s="2" t="n"/>
-      <c r="L37" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="M37" s="2" t="n">
         <v>1</v>
       </c>
@@ -2976,12 +2940,12 @@
       <c r="O37" s="2" t="n"/>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>Returned after exit #34: on calls with GHF, expressed interest in re-engaging and enhancing its offer; resumed with revised LOI (#38). Company considered it but did not admit it to the finalist stage.</t>
+          <t>Subject to a three-week exclusive diligence period. $20.02 cash at closing plus $1.13 CVR tied to a later sale of the South Quay property (CVR payment form not stated). Mark-ups of merger, voting agreement and disclosure letter (Formal). One day after the due date.</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>During those calls, Party D and Party E both expressed interest in reengaging and enhancing their offers. (p. 30)</t>
+          <t>G&amp;W submitted an LOI on July 21, 2016 to acquire the Company for a price of $21.15 per share (subject to a three-week exclusive diligence period). (p. 29)</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
@@ -2991,13 +2955,13 @@
       </c>
       <c r="S37" s="2" t="n"/>
       <c r="T37" s="3" t="n">
-        <v>42580</v>
+        <v>42572</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>42580</v>
+        <v>42572</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>42580</v>
+        <v>42572</v>
       </c>
     </row>
     <row r="38">
@@ -3006,12 +2970,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>07/29/2016</t>
+          <t>07/21/2016</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Party E</t>
+          <t>G&amp;W</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3021,14 +2985,14 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Re-entered</t>
+          <t>Exclusivity changed</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H38" s="2" t="n"/>
       <c r="I38" s="2" t="n"/>
@@ -3042,28 +3006,24 @@
       <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Returned after exit #33: on calls with GHF, expressed interest in re-engaging and enhancing its offer; resumed with revised LOI (#39).</t>
+          <t>Requested: G&amp;W's LOI was conditioned on a three-week exclusive diligence period. Not granted.</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>During those calls, Party D and Party E both expressed interest in reengaging and enhancing their offers. (p. 30)</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
+          <t>subject to a three-week exclusive diligence period (p. 29)</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="n"/>
       <c r="S38" s="2" t="n"/>
       <c r="T38" s="3" t="n">
-        <v>42580</v>
+        <v>42572</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>42580</v>
+        <v>42572</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>42580</v>
+        <v>42572</v>
       </c>
     </row>
     <row r="39">
@@ -3072,17 +3032,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>08/01/2016</t>
+          <t>07/26/2016</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>G&amp;W</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -3094,13 +3054,13 @@
         <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>24</v>
+        <v>22.15</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>24</v>
+        <v>22.15</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3114,7 +3074,7 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Heavy</t>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
@@ -3124,28 +3084,28 @@
       <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>30-day due diligence period. Revised LOI raising #26; stays Formal (earlier mark-up). Committee had BMO clarify its terms and diligence needs.</t>
+          <t>Conditions not restated; whether #36's exclusive-diligence condition still applied is not said. Raised after GHF said its price and CVR structure were not competitive: $21.02 cash plus $1.13 CVR. Formal via #36's mark-ups (Q7).</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>On August 1, 2016, Party D submitted a revised LOI at a price of $24.00 per share (p. 30)</t>
+          <t>G&amp;W submitted a revised LOI, which increased its offer to $22.15 per share (including $21.02 in cash and $1.13 CVR). (p. 29)</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="S39" s="2" t="n"/>
       <c r="T39" s="3" t="n">
-        <v>42583</v>
+        <v>42577</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>42583</v>
+        <v>42577</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>42583</v>
+        <v>42577</v>
       </c>
     </row>
     <row r="40">
@@ -3154,12 +3114,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>08/01/2016</t>
+          <t>07/27/2016 (decision; told subsequently)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Party E</t>
+          <t>Party C</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3169,65 +3129,49 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>23.81</v>
-      </c>
-      <c r="I40" s="4" t="n">
-        <v>23.81</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="n"/>
       <c r="M40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="2" t="n"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Lower offer than rivals</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="n"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>30-day due diligence period. Revised LOI raising #25, with financing support from Party F (already out, #33; not a group). Committee had BMO clarify its terms.</t>
+          <t>Transaction Committee kept only G&amp;W and Party B "because of the higher offers"; GHF then told the other bidders they were out. Party C's LOI: $19.30. Decision dated 07/27: it relies on G&amp;W's 07/26 revision (#38).</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>Party E submitted a revised LOI, along with financing support, from Party F, at a price of $23.81 per share. (p. 30)</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>Q5; Q6</t>
-        </is>
-      </c>
+          <t>representatives of GHF subsequently contacted the remaining bidders to inform them that they were no longer involved in the process (p. 30)</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="n"/>
       <c r="S40" s="2" t="n"/>
       <c r="T40" s="3" t="n">
-        <v>42583</v>
+        <v>42578</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>42583</v>
+        <v>42578</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>42583</v>
+        <v>42578</v>
       </c>
     </row>
     <row r="41">
@@ -3236,7 +3180,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>on or after 08/01/2016</t>
+          <t>07/27/2016 (decision; told subsequently)</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3251,14 +3195,14 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Exclusivity changed</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H41" s="2" t="n"/>
       <c r="I41" s="2" t="n"/>
@@ -3268,31 +3212,33 @@
       <c r="M41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N41" s="2" t="n"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Lower offer than rivals</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="n"/>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Requested and refused: D would not shorten its 30-day diligence and asked the Company to commit not to sign with another bidder during it; Company declined, citing active interest of Party B and G&amp;W. Date not reported.</t>
+          <t>Transaction Committee kept only G&amp;W and Party B "because of the higher offers"; GHF then told the other bidders they were out. Party D's LOI: $21.00. Decision dated 07/27: it relies on G&amp;W's 07/26 revision (#38).</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>Party D declined to shorten its due diligence period and requested that the Company commit that it would not enter into an agreement with another bidder (p. 30)</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
+          <t>representatives of GHF subsequently contacted the remaining bidders to inform them that they were no longer involved in the process (p. 30)</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="n"/>
       <c r="S41" s="2" t="n"/>
       <c r="T41" s="3" t="n">
-        <v>42583</v>
+        <v>42578</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>42583</v>
-      </c>
-      <c r="V41" s="2" t="n"/>
+        <v>42578</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>42578</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -3300,29 +3246,29 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>on or after 08/01/2016</t>
+          <t>07/27/2016 (decision; told subsequently)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>Party E</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Withdrew</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H42" s="2" t="n"/>
       <c r="I42" s="2" t="n"/>
@@ -3334,33 +3280,31 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Terms or process</t>
+          <t>Lower offer than rivals</t>
         </is>
       </c>
       <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>After refusal of #40, D said it would not continue due diligence “at that time” (stopping for now); not heard from again. Date not reported.</t>
+          <t>Transaction Committee kept only G&amp;W and Party B "because of the higher offers"; GHF then told the other bidders they were out. Party E's LOI: $21.26. Decision dated 07/27: it relies on G&amp;W's 07/26 revision (#38).</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>the Company declined to make such a commitment, at which point Party D indicated that it would not proceed with further due diligence at that time. (p. 30)</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
+          <t>representatives of GHF subsequently contacted the remaining bidders to inform them that they were no longer involved in the process (p. 30)</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="n"/>
       <c r="S42" s="2" t="n"/>
       <c r="T42" s="3" t="n">
-        <v>42583</v>
+        <v>42578</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>42583</v>
-      </c>
-      <c r="V42" s="2" t="n"/>
+        <v>42578</v>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v>42578</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -3368,12 +3312,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>08/02/2016</t>
+          <t>07/27/2016 (decision; told subsequently)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Party E</t>
+          <t>Party F</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -3383,65 +3327,49 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>21.26</v>
-      </c>
-      <c r="I43" s="4" t="n">
-        <v>21.26</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2" t="n"/>
+      <c r="J43" s="2" t="n"/>
+      <c r="K43" s="2" t="n"/>
+      <c r="L43" s="2" t="n"/>
       <c r="M43" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N43" s="2" t="n"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>Lower offer than rivals</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>Reverted to original proposal (#25), with its 60-day exclusivity for diligence: withdrew $23.81 (#39) after BMO's clarification request and confirmed $21.26. A new Bid under the reversion rule, not an exit.</t>
+          <t>Transaction Committee kept only G&amp;W and Party B "because of the higher offers"; GHF then told the other bidders they were out. Party F's LOI: $19.20. Decision dated 07/27: it relies on G&amp;W's 07/26 revision (#38).</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>Party E withdrew its revised proposal on August 2, 2016 (but confirmed its original proposal of $21.26 per share) (p. 30)</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>Q5; Q6</t>
-        </is>
-      </c>
+          <t>representatives of GHF subsequently contacted the remaining bidders to inform them that they were no longer involved in the process (p. 30)</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="n"/>
       <c r="S43" s="2" t="n"/>
       <c r="T43" s="3" t="n">
-        <v>42584</v>
+        <v>42578</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>42584</v>
+        <v>42578</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>42584</v>
+        <v>42578</v>
       </c>
     </row>
     <row r="44">
@@ -3450,18 +3378,18 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>08/04/2016</t>
+          <t>07/27/2016</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Target (Transaction Committee)</t>
+          <t>Providence and Worcester Railroad (target)</t>
         </is>
       </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
@@ -3480,28 +3408,28 @@
       <c r="O44" s="2" t="n"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Preferred bidder: Committee told advisers to keep up diligence and negotiations with both G&amp;W and Party B but, given B's higher price, to prioritize B and complete the merger agreement with B.</t>
+          <t>Transaction Committee moved to confirmatory diligence and negotiations with G&amp;W and Party B only (definitive negotiation with selected bidders, no final-bid request). Both did on-site diligence 07/27–08/11. Dated 07/27, the meeting after G&amp;W's 07/26 revision.</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>given the higher price offered by Party B, to prioritize Party B and proceed to complete the negotiation of the merger agreement with Party B. (p. 31)</t>
+          <t>The Transaction Committee concluded that the Company should proceed with confirmatory due diligence and negotiations with G&amp;W and Party B because of the higher offers (p. 30)</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S44" s="2" t="n"/>
       <c r="T44" s="3" t="n">
-        <v>42586</v>
+        <v>42578</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>42586</v>
+        <v>42578</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>42586</v>
+        <v>42578</v>
       </c>
     </row>
     <row r="45">
@@ -3510,22 +3438,22 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>08/04/2016</t>
+          <t>07/29/2016</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Bid reaffirmed</t>
+          <t>Re-entered</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
@@ -3534,27 +3462,11 @@
       <c r="G45" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H45" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="I45" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
+      <c r="H45" s="2" t="n"/>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="n"/>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
       <c r="M45" s="2" t="n">
         <v>1</v>
       </c>
@@ -3562,28 +3474,28 @@
       <c r="O45" s="2" t="n"/>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>Expedited diligence still open (on-site to 08/11). Reaffirmed by returned draft: B's counsel returned a revised merger agreement after the Company's 08/01 draft, with Company moving to finalize with B (#43). Price carried from #24.</t>
+          <t>On calls with GHF, Party D expressed interest in reengaging and enhancing its offer after being told it was out (#40). Not admitted to round 3; its revised proposal was still received.</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>On August 4, 2016, legal counsel for Party B provided a revised draft of the merger agreement (p. 31)</t>
+          <t>During those calls, Party D and Party E both expressed interest in reengaging and enhancing their offers. (p. 30)</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S45" s="2" t="n"/>
       <c r="T45" s="3" t="n">
-        <v>42586</v>
+        <v>42580</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>42586</v>
+        <v>42580</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>42586</v>
+        <v>42580</v>
       </c>
     </row>
     <row r="46">
@@ -3592,12 +3504,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>08/09/2016</t>
+          <t>07/29/2016</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>G&amp;W (Genesee &amp; Wyoming Inc.)</t>
+          <t>Party E</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -3607,7 +3519,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Re-entered</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
@@ -3628,24 +3540,28 @@
       <c r="O46" s="2" t="n"/>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>Status change: Committee had BMO tell G&amp;W the Company intended to sign with another bidder. G&amp;W's request to keep doing diligence (physical diligence 08/10–08/11) to support a better offer was granted.</t>
+          <t>On calls with GHF, Party E expressed interest in reengaging and enhancing its offer after being told it was out (#41). Not admitted to round 3; its revised proposal was still received.</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>the Transaction Committee directed representatives of BMO to inform G&amp;W that the Company intended to enter into a merger agreement with another bidder. (p. 31)</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="n"/>
+          <t>During those calls, Party D and Party E both expressed interest in reengaging and enhancing their offers. (p. 30)</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
       <c r="S46" s="2" t="n"/>
       <c r="T46" s="3" t="n">
-        <v>42591</v>
+        <v>42580</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>42591</v>
+        <v>42580</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>42591</v>
+        <v>42580</v>
       </c>
     </row>
     <row r="47">
@@ -3654,18 +3570,22 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>08/10/2016</t>
+          <t>08/01/2016</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="n"/>
+          <t>Party D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
@@ -3674,34 +3594,56 @@
       <c r="G47" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H47" s="2" t="n"/>
-      <c r="I47" s="2" t="n"/>
-      <c r="J47" s="2" t="n"/>
-      <c r="K47" s="2" t="n"/>
-      <c r="L47" s="2" t="n"/>
-      <c r="M47" s="2" t="n"/>
+      <c r="H47" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N47" s="2" t="n"/>
       <c r="O47" s="2" t="n"/>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>G&amp;W's legal counsel; first seen acting 08/10/2016 in draft-agreement discussions with Hinckley Allen; finalized documents at signing.</t>
+          <t>Subject to a 30-day due diligence period. Revised LOI up from $21.00 (#33); matched Party B's $24.00. No new mark-up reported; Formal via its July mark-ups (Q7).</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP (which we refer to as “Simpson Thacher”), G&amp;W’s legal counsel (p. 31)</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="n"/>
+          <t>On August 1, 2016, Party D submitted a revised LOI at a price of $24.00 per share (p. 30)</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>Q2; Q7</t>
+        </is>
+      </c>
       <c r="S47" s="2" t="n"/>
       <c r="T47" s="3" t="n">
-        <v>42592</v>
+        <v>42583</v>
       </c>
       <c r="U47" s="3" t="n">
-        <v>42592</v>
+        <v>42583</v>
       </c>
       <c r="V47" s="3" t="n">
-        <v>42592</v>
+        <v>42583</v>
       </c>
     </row>
     <row r="48">
@@ -3710,12 +3652,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>08/12/2016 (morning)</t>
+          <t>08/01/2016</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>G&amp;W (Genesee &amp; Wyoming Inc.)</t>
+          <t>Party E</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3735,24 +3677,24 @@
         <v>3</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Formal</t>
+          <t>Informal</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Heavy</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
@@ -3762,24 +3704,28 @@
       <c r="O48" s="2" t="n"/>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>Physical diligence completed 08/11; no financing condition in the agreement signed that day (p. 34). All cash, CVR dropped; with merger and voting agreement mark-ups; expiring 6:00 p.m. next day. Ref: $16.30 close 08/12/2016; 53% premium (p. 33).</t>
+          <t>Subject to a 30-day due diligence period. Revised LOI up from $21.26 (#31), with financing support from Party F (#48). Committee had BMO clarify terms and diligence needs.</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>G&amp;W submitted a revised LOI to acquire the Company for a price of $25.00 per share in cash, which excluded the previously proposed CVR (p. 31)</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="n"/>
+          <t>Party E submitted a revised LOI, along with financing support, from Party F, at a price of $23.81 per share. (p. 30)</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
       <c r="S48" s="2" t="n"/>
       <c r="T48" s="3" t="n">
-        <v>42594</v>
+        <v>42583</v>
       </c>
       <c r="U48" s="3" t="n">
-        <v>42594</v>
+        <v>42583</v>
       </c>
       <c r="V48" s="3" t="n">
-        <v>42594</v>
+        <v>42583</v>
       </c>
     </row>
     <row r="49">
@@ -3788,12 +3734,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>08/12/2016</t>
+          <t>08/01/2016</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>Party F (supporting Party E)</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3803,7 +3749,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Bid reaffirmed</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
@@ -3812,56 +3758,34 @@
       <c r="G49" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H49" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="I49" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H49" s="2" t="n"/>
+      <c r="I49" s="2" t="n"/>
+      <c r="J49" s="2" t="n"/>
+      <c r="K49" s="2" t="n"/>
+      <c r="L49" s="2" t="n"/>
+      <c r="M49" s="2" t="n"/>
       <c r="N49" s="2" t="n"/>
       <c r="O49" s="2" t="n"/>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>Only final documentation left: diligence done 08/11; meetings set to approve a deal with B. By price confirmation: told a rival bid higher, then asked by BMO at the Board's request to raise, B would not; $24.00 carried from #24.</t>
+          <t>Financing support: Party F, dropped at #42, backed Party E's revised LOI. Not a bidding group (E4); Party F does not re-enter.</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>representatives of BMO then contacted Party B to determine if it would increase its offer price. Party B indicated that it would not increase its price. (p. 32)</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
+          <t>Party E submitted a revised LOI, along with financing support, from Party F (p. 30)</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="n"/>
       <c r="S49" s="2" t="n"/>
       <c r="T49" s="3" t="n">
-        <v>42594</v>
+        <v>42583</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>42594</v>
+        <v>42583</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>42594</v>
+        <v>42583</v>
       </c>
     </row>
     <row r="50">
@@ -3870,18 +3794,22 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>08/12/2016</t>
+          <t>08/02/2016</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Target; G&amp;W</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="n"/>
+          <t>Party E</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Merger agreement signed</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
@@ -3890,34 +3818,56 @@
       <c r="G50" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H50" s="2" t="n"/>
-      <c r="I50" s="2" t="n"/>
-      <c r="J50" s="2" t="n"/>
-      <c r="K50" s="2" t="n"/>
-      <c r="L50" s="2" t="n"/>
-      <c r="M50" s="2" t="n"/>
+      <c r="H50" s="4" t="n">
+        <v>21.26</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>21.26</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N50" s="2" t="n"/>
       <c r="O50" s="2" t="n"/>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>$25.00 per share in cash (preferred converted at 100 common each). Board (Smith recused) found G&amp;W superior: $1.00 more, lower break fee, similar STB risk; BMO fairness opinion. Eder Trusts voting agreement; $3.785M termination fee.</t>
+          <t>Reversion: withdrew the 08/01 $23.81 proposal but confirmed its original $21.26 LOI (#31), whose terms included a 60-day exclusivity for diligence and documentation.</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>the Company and G&amp;W executed the merger agreement, and the Company, G&amp;W and the Eder Trusts executed the voting agreement. (p. 32)</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="n"/>
+          <t>Party E withdrew its revised proposal on August 2, 2016 (but confirmed its original proposal of $21.26 per share) (p. 30)</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
       <c r="S50" s="2" t="n"/>
       <c r="T50" s="3" t="n">
-        <v>42594</v>
+        <v>42584</v>
       </c>
       <c r="U50" s="3" t="n">
-        <v>42594</v>
+        <v>42584</v>
       </c>
       <c r="V50" s="3" t="n">
-        <v>42594</v>
+        <v>42584</v>
       </c>
     </row>
     <row r="51">
@@ -3926,22 +3876,22 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>08/12/2016</t>
+          <t>after 08/01/2016 (reported with 08/02 events)</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Not selected at signing</t>
+          <t>Exclusivity changed</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
@@ -3958,37 +3908,27 @@
       <c r="M51" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>Would not improve earlier offer</t>
-        </is>
-      </c>
+      <c r="N51" s="2" t="n"/>
       <c r="O51" s="2" t="n"/>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>Reported: still bidding at $24.00 (#48) when the Board chose G&amp;W's $25.00; declined to improve when asked.</t>
+          <t>Requested: Party D refused to shorten its 30-day diligence and asked the Company to commit not to sign with another bidder during it. The Company declined, citing Party B's and G&amp;W's active interest.</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>The Board determined that the G&amp;W offer represented the superior proposal. (p. 32)</t>
-        </is>
-      </c>
-      <c r="R51" s="2" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
+          <t>requested that the Company commit that it would not enter into an agreement with another bidder during its 30-day due diligence period (p. 30)</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="n"/>
       <c r="S51" s="2" t="n"/>
       <c r="T51" s="3" t="n">
-        <v>42594</v>
+        <v>42584</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>42594</v>
-      </c>
-      <c r="V51" s="3" t="n">
-        <v>42594</v>
-      </c>
+        <v>42583</v>
+      </c>
+      <c r="V51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -3996,22 +3936,22 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>by 08/12/2016</t>
+          <t>after 08/01/2016 (reported with 08/02 events)</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Party E</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Not selected at signing</t>
+          <t>Withdrew</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
@@ -4030,39 +3970,29 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>Terms or process</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="n"/>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>Inferred: last seen 08/02 with $21.26 confirmed (#42), then never mentioned; closed at signing with G&amp;W under the fallback rule.</t>
+          <t>After the Company refused the commitment, Party D said it would not proceed with further due diligence "at that time"; standing offer $24.00 (#46).</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>Party E withdrew its revised proposal on August 2, 2016 (but confirmed its original proposal of $21.26 per share) (p. 30)</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
+          <t>at which point Party D indicated that it would not proceed with further due diligence at that time (p. 30)</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="n"/>
       <c r="S52" s="2" t="n"/>
       <c r="T52" s="3" t="n">
-        <v>42594</v>
+        <v>42584</v>
       </c>
       <c r="U52" s="3" t="n">
-        <v>42584</v>
-      </c>
-      <c r="V52" s="3" t="n">
-        <v>42594</v>
-      </c>
+        <v>42583</v>
+      </c>
+      <c r="V52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -4070,27 +4000,25 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>08/15/2016</t>
+          <t>08/04/2016</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Providence and Worcester Railroad (target)</t>
         </is>
       </c>
       <c r="D53" s="2" t="n"/>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Merger announced</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
+      <c r="G53" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="H53" s="2" t="n"/>
       <c r="I53" s="2" t="n"/>
@@ -4102,28 +4030,672 @@
       <c r="O53" s="2" t="n"/>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>Press release before market open on Monday 08/15/2016.</t>
+          <t>Preferred bidder: the Committee kept diligence and negotiations going with both G&amp;W and Party B but, given Party B's higher price, told advisers to prioritize Party B and complete its merger agreement.</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>The Company issued a press release publicly announcing the transaction on Monday, August 15, 2016 prior to the opening of trading (p. 32)</t>
+          <t>given the higher price offered by Party B, to prioritize Party B and proceed to complete the negotiation of the merger agreement with Party B (p. 31)</t>
         </is>
       </c>
       <c r="R53" s="2" t="n"/>
       <c r="S53" s="2" t="n"/>
       <c r="T53" s="3" t="n">
+        <v>42586</v>
+      </c>
+      <c r="U53" s="3" t="n">
+        <v>42586</v>
+      </c>
+      <c r="V53" s="3" t="n">
+        <v>42586</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2016</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Party B</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Bid reaffirmed</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" s="2" t="n"/>
+      <c r="O54" s="2" t="n"/>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>Diligence still open (on-site to 08/11) under its expedited-review condition. Carried from #30: Party B's counsel returned a revised draft merger agreement while the Company finalized terms with it; its price stood $1.00 below G&amp;W on 08/12.</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>On August 4, 2016, legal counsel for Party B provided a revised draft of the merger agreement (p. 31)</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="n"/>
+      <c r="T54" s="3" t="n">
+        <v>42586</v>
+      </c>
+      <c r="U54" s="3" t="n">
+        <v>42586</v>
+      </c>
+      <c r="V54" s="3" t="n">
+        <v>42586</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2016</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Providence and Worcester Railroad (target)</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n"/>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Other material event</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H55" s="2" t="n"/>
+      <c r="I55" s="2" t="n"/>
+      <c r="J55" s="2" t="n"/>
+      <c r="K55" s="2" t="n"/>
+      <c r="L55" s="2" t="n"/>
+      <c r="M55" s="2" t="n"/>
+      <c r="N55" s="2" t="n"/>
+      <c r="O55" s="2" t="n"/>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>Target told G&amp;W it intended to sign with another bidder; G&amp;W's request to continue diligence (physical diligence 08/10–08/11) "to potentially facilitate an improved offer" was granted. Board meetings set for 08/12 to approve a Party B deal.</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>the Transaction Committee directed representatives of BMO to inform G&amp;W that the Company intended to enter into a merger agreement with another bidder (p. 31)</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="n"/>
+      <c r="S55" s="2" t="n"/>
+      <c r="T55" s="3" t="n">
+        <v>42591</v>
+      </c>
+      <c r="U55" s="3" t="n">
+        <v>42591</v>
+      </c>
+      <c r="V55" s="3" t="n">
+        <v>42591</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>08/10/2016</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Adviser</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H56" s="2" t="n"/>
+      <c r="I56" s="2" t="n"/>
+      <c r="J56" s="2" t="n"/>
+      <c r="K56" s="2" t="n"/>
+      <c r="L56" s="2" t="n"/>
+      <c r="M56" s="2" t="n"/>
+      <c r="N56" s="2" t="n"/>
+      <c r="O56" s="2" t="n"/>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>G&amp;W's legal counsel; first shown acting 08/10/2016, discussing the draft merger and voting agreements with Hinckley Allen; finalized the documents at signing.</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>Simpson Thacher &amp; Bartlett LLP (which we refer to as “Simpson Thacher”), G&amp;W’s legal counsel (p. 31)</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="n"/>
+      <c r="S56" s="2" t="n"/>
+      <c r="T56" s="3" t="n">
+        <v>42592</v>
+      </c>
+      <c r="U56" s="3" t="n">
+        <v>42592</v>
+      </c>
+      <c r="V56" s="3" t="n">
+        <v>42592</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>08/12/2016 (morning)</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>G&amp;W</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" s="2" t="n"/>
+      <c r="O57" s="2" t="n"/>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>Ready to sign: physical diligence completed 08/11; no financing condition, G&amp;W represented sufficient funds (pp. 34, A-§4.5). Mark-ups of merger and voting agreements; CVR dropped; offer to expire 6:00 p.m. 08/13. Signalled 08/11.</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>G&amp;W submitted a revised LOI to acquire the Company for a price of $25.00 per share in cash, which excluded the previously proposed CVR (p. 31)</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="n"/>
+      <c r="S57" s="2" t="n"/>
+      <c r="T57" s="3" t="n">
+        <v>42594</v>
+      </c>
+      <c r="U57" s="3" t="n">
+        <v>42594</v>
+      </c>
+      <c r="V57" s="3" t="n">
+        <v>42594</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>08/12/2016</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Providence and Worcester Railroad (target)</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Other material event</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H58" s="2" t="n"/>
+      <c r="I58" s="2" t="n"/>
+      <c r="J58" s="2" t="n"/>
+      <c r="K58" s="2" t="n"/>
+      <c r="L58" s="2" t="n"/>
+      <c r="M58" s="2" t="n"/>
+      <c r="N58" s="2" t="n"/>
+      <c r="O58" s="2" t="n"/>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>Price feedback to Party B: at 10:30 a.m. the Committee had BMO tell Party B a rival had submitted a higher revised LOI; that afternoon, at the Board's request, BMO asked Party B whether it would raise its price (#60).</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>the Transaction Committee directed representatives of BMO to inform Party B that another party had submitted a revised LOI at a higher price (p. 31)</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="n"/>
+      <c r="S58" s="2" t="n"/>
+      <c r="T58" s="3" t="n">
+        <v>42594</v>
+      </c>
+      <c r="U58" s="3" t="n">
+        <v>42594</v>
+      </c>
+      <c r="V58" s="3" t="n">
+        <v>42594</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>08/12/2016</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Company STB counsel (unnamed)</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n"/>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Adviser</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H59" s="2" t="n"/>
+      <c r="I59" s="2" t="n"/>
+      <c r="J59" s="2" t="n"/>
+      <c r="K59" s="2" t="n"/>
+      <c r="L59" s="2" t="n"/>
+      <c r="M59" s="2" t="n"/>
+      <c r="N59" s="2" t="n"/>
+      <c r="O59" s="2" t="n"/>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>Target's regulatory (Surface Transportation Board) counsel; advised the Board on 08/12/2016 that approval timing and likelihood were not materially different for G&amp;W and Party B.</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>The Board arranged a telephone call with the Company’s STB counsel to discuss the process for obtaining the required regulatory approval or exemption for the transaction (p. 32)</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="n"/>
+      <c r="S59" s="2" t="n"/>
+      <c r="T59" s="3" t="n">
+        <v>42594</v>
+      </c>
+      <c r="U59" s="3" t="n">
+        <v>42594</v>
+      </c>
+      <c r="V59" s="3" t="n">
+        <v>42594</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>08/12/2016</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>G&amp;W</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Merger agreement signed</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H60" s="2" t="n"/>
+      <c r="I60" s="2" t="n"/>
+      <c r="J60" s="2" t="n"/>
+      <c r="K60" s="2" t="n"/>
+      <c r="L60" s="2" t="n"/>
+      <c r="M60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N60" s="2" t="n"/>
+      <c r="O60" s="2" t="n"/>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>Board (Smith recused) found G&amp;W superior; BMO fairness opinion. $25.00 cash per common share, preferred converted 100:1; 3% fee ($3.785m, cut from 3.85%); Eder Trusts voting agreement. Ref: $16.30 close 08/12/2016; 53% premium.</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>Shortly thereafter, Hinckley Allen and Simpson Thacher finalized the transaction documents and the Company and G&amp;W executed the merger agreement (p. 32)</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="n"/>
+      <c r="S60" s="2" t="n"/>
+      <c r="T60" s="3" t="n">
+        <v>42594</v>
+      </c>
+      <c r="U60" s="3" t="n">
+        <v>42594</v>
+      </c>
+      <c r="V60" s="3" t="n">
+        <v>42594</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>08/12/2016</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Party B</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Not selected at signing</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H61" s="2" t="n"/>
+      <c r="I61" s="2" t="n"/>
+      <c r="J61" s="2" t="n"/>
+      <c r="K61" s="2" t="n"/>
+      <c r="L61" s="2" t="n"/>
+      <c r="M61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>Would not improve earlier offer</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="n"/>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>Asked at the Board's request whether it would raise its $24.00 offer (#53), Party B declined; Board chose G&amp;W's $25.00. Party B's draft carried a 3% fee plus expenses up to 1%.</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>Party B indicated that it would not increase its price. (p. 32)</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="n"/>
+      <c r="S61" s="2" t="n"/>
+      <c r="T61" s="3" t="n">
+        <v>42594</v>
+      </c>
+      <c r="U61" s="3" t="n">
+        <v>42594</v>
+      </c>
+      <c r="V61" s="3" t="n">
+        <v>42594</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>by 08/12/2016</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Party E</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Not selected at signing</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H62" s="2" t="n"/>
+      <c r="I62" s="2" t="n"/>
+      <c r="J62" s="2" t="n"/>
+      <c r="K62" s="2" t="n"/>
+      <c r="L62" s="2" t="n"/>
+      <c r="M62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>Inferred: last reported confirming its $21.26 LOI on 08/02 (#49) and not mentioned again; closed at signing with G&amp;W.</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>Party E withdrew its revised proposal on August 2, 2016 (but confirmed its original proposal of $21.26 per share) (p. 30)</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="n"/>
+      <c r="T62" s="3" t="n">
+        <v>42594</v>
+      </c>
+      <c r="U62" s="3" t="n">
+        <v>42584</v>
+      </c>
+      <c r="V62" s="3" t="n">
+        <v>42594</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>08/15/2016</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Providence and Worcester Railroad; G&amp;W</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n"/>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Merger announced</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="n"/>
+      <c r="I63" s="2" t="n"/>
+      <c r="J63" s="2" t="n"/>
+      <c r="K63" s="2" t="n"/>
+      <c r="L63" s="2" t="n"/>
+      <c r="M63" s="2" t="n"/>
+      <c r="N63" s="2" t="n"/>
+      <c r="O63" s="2" t="n"/>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>Company press release announcing the G&amp;W merger before NASDAQ opened on Monday 08/15/2016.</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>The Company issued a press release publicly announcing the transaction on Monday, August 15, 2016 prior to the opening of trading (p. 32)</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="n"/>
+      <c r="S63" s="2" t="n"/>
+      <c r="T63" s="3" t="n">
         <v>42597</v>
       </c>
-      <c r="U53" s="3" t="n">
+      <c r="U63" s="3" t="n">
         <v>42597</v>
       </c>
-      <c r="V53" s="3" t="n">
+      <c r="V63" s="3" t="n">
         <v>42597</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V53"/>
+  <autoFilter ref="A1:V63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4140,10 +4712,10 @@
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="50" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
@@ -4209,26 +4781,26 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>42460</v>
+        <v>42453</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>GHF outreach wave, week of 03/28/2016, on the Transaction Committee's 03/24 authorization: 11 strategic and 18 financial buyers contacted (#5–7).</t>
+          <t>Transaction Committee authorized GHF outreach (#5); GHF contacted 11 strategic and 18 financial buyers week of 03/28/2016.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>25 NDA signers (#8–9): 11 strategic (incl. Party A, G&amp;W; Parties B, E, F assumed) and 14 financial (incl. Party D, assumed).</t>
+          <t>Count: 25–27 NDA signers: 11 strategic incl. Party A; 14 financial; G&amp;W and Party B (strategic) unless among the 11. Filing total: 25 (p. 33).</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>05/10/2016 (superseded before arrival; revision date not reported) → 05/19/2016</t>
+          <t>05/10/2016 (superseded before arrival; inferred) → 05/19/2016</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Unclear</t>
+          <t>Late bids accepted</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -4238,12 +4810,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>9 IOIs, $17.93–$26.50 as a group (#14): G&amp;W, Parties B, D, E, F and 4 unnamed.</t>
+          <t>9 IOI bidders ($17.93–$26.50), inferred to include G&amp;W and Parties B, D, E, F; others unnamed.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>seven advanced; two low bidders excluded; sixteen did not submit (#15–17)</t>
+          <t>seven advanced, two low bidders dropped, 16–18 NDA signers did not submit</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4831,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Committee advanced seven IOI bidders to management presentations, data room and further diligence; mid-June request for LOIs with document mark-ups (#17–18).</t>
+          <t>Committee advanced the seven remaining IOI bidders to management presentations and the data site (#21); LOIs requested mid-June.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>7 admitted: 5 strategic (G&amp;W, Parties B, E, F, unnamed strategic buyer 1) and 2 financial (Party D, unnamed financial buyer 1); plus late entrant Party C (strategic), admitted to data room and management presentation 07/12–07/14 (#20–22).</t>
+          <t>7 admitted (5 strategic: G&amp;W, Parties B, E, F, one unnamed; 2 financial: Party D, one unnamed); Party C (strategic) admitted 07/12–07/14/2016 after its IOI.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -4284,12 +4856,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>6 LOIs: Party B $24.00; G&amp;W $21.15 → $22.15; Party E $21.26; Party D $21.00; Party C $19.30; Party F $19.20. Party C also bid $21.00 by IOI 07/12.</t>
+          <t>6: Party B $24.00; G&amp;W $21.15, revised $22.15; Party E $21.26; Party D $21.00; Party C $19.30 (IOI $21.00 on 07/12); Party F $19.20.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>two advanced (G&amp;W, Party B); four dropped (Parties C, D, E, F); two did not submit (#29–30, #33–34)</t>
+          <t>two advanced (G&amp;W, Party B), four dropped (Parties C, D, E, F), two did not submit</t>
         </is>
       </c>
     </row>
@@ -4305,17 +4877,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Committee chose G&amp;W and Party B for confirmatory diligence and merger-agreement negotiations (#35).</t>
+          <t>Committee chose confirmatory diligence and negotiation with G&amp;W and Party B only (#43).</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2 strategic: G&amp;W, Party B. Parties D (financial) and E (strategic): still being received, not admitted (re-engaged 07/29, revised LOIs 08/01).</t>
+          <t>2 strategic: G&amp;W, Party B. Party D (financial) and Party E (strategic): re-engaged 07/29/2016, still being received, not admitted.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>none stated</t>
+          <t>none stated (G&amp;W's own offer expiry of 6:00 p.m. 08/13/2016 is not a target due date)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4330,12 +4902,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4: G&amp;W $25.00 (#47); Party B $24.00 reaffirmed (#44, #48); Party D $24.00 (#38); Party E $23.81 then back to $21.26 (#39, #42).</t>
+          <t>4: G&amp;W $25.00 cash; Party B reaffirmed $24.00; Party D $24.00; Party E $23.81 then $21.26.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>signing with G&amp;W at $25.00; Party B would not raise and was not selected; Party E not selected; Party D withdrew</t>
+          <t>signing with G&amp;W at $25.00; Party D withdrew; Parties B and E not selected</t>
         </is>
       </c>
     </row>
@@ -4351,16 +4923,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4408,27 +4980,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Process and round map: one process with rounds 0–3?</t>
+          <t>Is Party A's Q4 2015 approach a Bidder interest in acquiring the Company, or an approach about a minority equity stake?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Yes. Process 1: round 0 (#1–4); round 1 opens with the 03/28-week outreach (#5); round 2 opens at the seven-bidder advancement (#17); round 3 (Inferred final) opens at the 07/27 G&amp;W/Party B selection (#35).</t>
+          <t>Keep as Bidder interest, round 0, with no price. It is the approach the board answered by hiring bankers for "possible negotiations with Party A", and Party A was carried into the auction.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Party A's equity interest (Q4 2015) led directly to the banker hire and the 03/14 process, which kept Party A in view (pp. 27–28). Gaps of about two months or more: Q4 2015 Party A meeting (10/01–12/31/2015, uncertain) to 03/22/2016 Party A meetings, i.e. 2.7–5.7 months. C7: (a) fails, since Party A was carried forward; (b) uncertain; (c) met. So there is no new process. No other gap of two months or more.</t>
+          <t>Party A "expressed some interest in acquiring equity" alongside joint-venture ideas (p. 27); the board then weighed change in control options.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>#1, #3, #5, #17, #18, #35</t>
+          <t>#1</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Most plausible alternative: round 2 opens at the mid-June LOI instruction (#18), not at the advancement decision, so #17 becomes a round-1 selection step. Another reading would open round 1 at the 03/24 authorization; nothing moves. Party A's interest in buying equity could instead be read as an other-scope approach; it has no row effect.</t>
+          <t>If read as a stake approach it becomes an Other material event; Initiation in Deal facts would move from mixed to target-led.</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -4441,27 +5013,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>How many parties signed confidentiality agreements, and who is in the outreach cohorts?</t>
+          <t>Process and round map: one process; round 0 (#1–#4); round 1 from 03/24/2016 (IOIs); round 2 from 05/23–06/01/2016 (seven advanced; LOIs); round 3 from 07/27/2016 (definitive negotiation with G&amp;W and Party B); post (#62).</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>26 parties: 25 from the March wave (11 strategic, 14 financial) plus Party C. Assume Parties B, E, F and G&amp;W were among the 11 strategic buyers, Party D among the 14 financial buyers, and the two “additional” Class I railroads outside the 11 and not signing.</t>
+          <t>Accept. Alternatives: open round 1 at the 03/14 decision (#3) or at the 03/28 outreach; open round 2 at the mid-June LOI request (#22), which moves only the opening date; treat Party D/E's 08/01 bids (#44–#47) as round-2 bargaining, which is unsupported because round 2 had closed at #39–#42.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>p. 28 gives 11 + 14 = 25 signers from the wave; p. 29 adds Party C's agreement; p. 33 says “25 of whom entered into confidentiality agreements”, which leaves out Party C or counts differently. Party B was first met 04/21 as “another potential strategic buyer” (p. 28).</t>
+          <t>E5: (a) fails, since Party A was kept in view (p. 27); (b) the only contact gap of about two months or more is Party A's Q4 2015 meeting to the 03/22/2016 meeting (about 2.7–5.7 months), with no reported end of the effort; (c) the 03/14/2016 decision is a fresh start. So there is one process.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>#6, #7, #8, #9, #10, #15, #20</t>
+          <t>#5, #21, #25, #43, #44, #45, #46, #47</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>If Party B was outside the 11, it needs its own Contact/NDA row and the non-submitter residual (#15) becomes 17. If the two railroads signed, the totals rise. The auction screen stays Met under every reading.</t>
+          <t>Round membership and live counts; a second process would reclassify #1 and add Process markers.</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -4474,27 +5046,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Deadline outcomes for each round.</t>
+          <t>How many parties signed confidentiality agreements? The background gives 11 strategic + 14 financial (p. 28) plus Party C in July (p. 29); the reasons section says 25 (p. 33). G&amp;W and Party B might or might not be among the 11.</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Round 1: 05/10 superseded before arrival, no outcome; 05/19 Unclear. Round 2: 07/20 Late bids accepted. Round 3: No deadline stated.</t>
+          <t>Keep the stated cohorts (11, 14) and give G&amp;W, Party B and Party C their own rows: 25–28 signers, with 26 the most likely (G&amp;W and B inside the 11; p. 33 omits Party C).</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>The 05/10 date was “subsequently postponed” to 05/19; the revision date is not reported (p. 29). The IOIs arrived “between May 19, 2016 and June 1, 2016” (p. 29), with no per-bid days. G&amp;W's LOI was dated 07/21, a day after the 07/20 due date, and was considered (p. 29). G&amp;W's 08/12 offer expiry is not a bid deadline (p. 31).</t>
+          <t>The filing never places G&amp;W, Party B or the two Class I railroads (#11) in the 11 contacted in week of 03/28 (p. 28); Party C "had not previously been part of the process" (p. 29).</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>#11, #12, #13, #14, #18, #23, #31</t>
+          <t>#6, #8, #9, #10, #11, #13, #14, #15, #19, #24</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>If 05/10 arrived before the postponement, it gets a Deadline row and the outcome Extended. If some IOIs are shown to have arrived after 05/19, round 1 becomes Late bids accepted; if all arrived on 05/19, Enforced.</t>
+          <t>Round-1 live count 25–27 and the non-submitter range at #19 (16–18); the auction screen stays Met either way.</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -4507,27 +5079,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Party B late-reconfirmation sequence: are #44 and #48 correct Bid reaffirmed rows?</t>
+          <t>Round 1 deadline outcomes: was 05/10/2016 superseded before it arrived, and what followed 05/19/2016?</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Yes. #44 is reaffirmed by returned draft (08/04): the Committee decided to complete the agreement with B (#43), B's latest priced row (#24) sits in round 2, which was Not final, and B's counsel returned a revised draft. #48 is by price confirmation (08/12).</t>
+          <t>05/10: superseded before arrival, so no Deadline row. 05/19: Late bids accepted, because IOIs arrived "between May 19 and June 1" and all nine were considered on 06/01.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>p. 31: “legal counsel for Party B provided a revised draft of the merger agreement” on 08/04, after the prioritize-B decision. p. 32: B “indicated that it would not increase its price”. Conditions went from Light (expedited diligence still open) to Light (only final documentation left).</t>
+          <t>The postponement was made "to ensure the potential buyers had sufficient time" (p. 29), which implies it came before 05/10; the receipt window runs to 06/01 (p. 29).</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>#24, #43, #44, #48, #50</t>
+          <t>#12, #16, #17, #18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>If “would not increase” is not an express confirmation, delete #48 and keep the fact in #50's Note. B's formality is unchanged either way (#24 is already Formal on its mark-up).</t>
+          <t>If all IOIs arrived 05/19 the outcome is Enforced; if the postponement came after 05/10, add a Deadline row with outcome Extended.</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -4540,27 +5112,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Is Party E's LOI Informal although it came with an issues list on the agreements?</t>
+          <t>Should the nine IOIs be one cohort Bid row, or individual inferred rows for G&amp;W and Parties B, D, E, F plus a four-bidder remainder?</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Yes, Informal. It came with a summary of material issues, not a mark-up.</t>
+          <t>Keep one nine-bidder cohort carrying the stated $17.93–$26.50 range, with inferred members named in the Note. Splitting would leave the stated range on no row.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>p. 29: Parties B, G&amp;W and D “provided mark-ups”, while Party E “provided a summary of material issues and proposed changes”. Under C13 an issues list alone is not a returned mark-up. The 60-day exclusivity condition keeps it Heavy either way.</t>
+          <t>The seven advanced are "the remaining seven" of nine (p. 29); only Party C is described as new at the LOI stage (p. 29), so the five named LOI bidders were IOI bidders. Their IOI prices are not given.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>#25, #39, #42</t>
+          <t>#18, #21</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>If Formal, round 2 has four Formal LOIs instead of three, and E's continuing proposals (#39, #42) become Formal.</t>
+          <t>Individual rows would give G&amp;W and Parties B, D, E, F round-1 bids with blank prices, and entries by bid for G&amp;W and Party B.</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -4573,33 +5145,132 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Parties D and E after their 07/27 exclusion: were they live, in which round, and how did they leave?</t>
+          <t>Round 2 deadline outcome for 07/20/2016.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Record Re-entered on 07/29, with their 08/01 bids in round 3 as “still being received, not admitted”. D Withdrew (“at that time”); E is Not selected at signing (inferred).</t>
+          <t>Late bids accepted: G&amp;W's LOI is dated 07/21/2016 and was reviewed with the others on 07/22 and 07/27. The other five came "in late July", arrival days unstated.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>p. 30: D and E “expressed interest in reengaging” after being told they were out; the Committee considered and clarified their 08/01 LOIs; D stopped diligence “at that time” when refused a no-other-agreement commitment; E is not mentioned after 08/02.</t>
+          <t>LOIs were due 07/20 (p. 29); G&amp;W "submitted an LOI on July 21, 2016" (p. 29); the Committee reviewed the LOIs on 07/22 and 07/27 (p. 30).</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>#33, #34, #36, #37, #38, #39, #40, #41, #42, #51</t>
+          <t>#22, #27, #36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>If their approaches are not treated as re-entry, drop #36–37 and treat #38–42 as post-exit proposals; live units in round 3 would be 2, not up to 4. E could instead be read as dropped by the target by 08/04 (#43).</t>
+          <t>If G&amp;W's LOI is treated as timely, the outcome would be Enforced.</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Are G&amp;W's 07/26 revised LOI and Party D's 08/01 revised LOI Formal, when neither is reported with a new mark-up?</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Formal: each revises a priced LOI the bidder had supported with its own mark-up of the merger agreement weeks earlier, and those mark-ups stayed on the table. G&amp;W's 07/26 Conditions: Unclear.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>G&amp;W, Party B and Party D "provided mark-ups of the draft merger agreement" with their LOIs (p. 29); the revisions are described only as price changes (pp. 29–30).</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>#38, #46</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>If Informal, the formal-bid set in rounds 2–3 shrinks and Party D's $24.00 becomes an informal exit price.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Party E: is 08/02 a withdrawal (exit) or a reversion to its $21.26 bid, and how does its participation end?</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Reversion: a Bid row at $21.26 (#49), then an inferred Not selected at signing on 08/12, since Party E "confirmed its original proposal" and is never mentioned again.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>"Party E withdrew its revised proposal on August 2, 2016 (but confirmed its original proposal of $21.26 per share)" (p. 30).</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>#49, #61</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>If treated as Withdrew on 08/02, Party E leaves before round 3's end and its $21.26 no longer counts as a live standing offer at signing.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Party B Bid reaffirmed on 08/04/2016 at $24.00 (carried from #30).</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Keep. Party B's counsel returned its own revised draft merger agreement while the Company was finalizing with it; its latest priced row sits in round 2 (Not final). Conditions Light: expedited diligence was still under way.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Party B's counsel "provided a revised draft of the merger agreement" on 08/04 (p. 31); on 08/12 G&amp;W's price "was $1.00 more per share" (p. 32), confirming $24.00 stood.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>#53</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Without it, Party B's last formal price sits only in a non-final round and its round-3 standing is unrecorded.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G7"/>
+  <autoFilter ref="A1:G10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4613,8 +5284,8 @@
   <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4637,7 +5308,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Providence and Worcester Railroad Company (PWRR)</t>
+          <t>Providence and Worcester Railroad Company (PWRR; NASDAQ: PWX), regional freight railroad, Rhode Island corporation</t>
         </is>
       </c>
     </row>
@@ -4649,7 +5320,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Genesee &amp; Wyoming Inc. (G&amp;W), through Pullman Acquisition Sub Inc.</t>
+          <t>Genesee &amp; Wyoming Inc. (G&amp;W; NYSE: GWR), via Pullman Acquisition Sub Inc.</t>
         </is>
       </c>
     </row>
@@ -4661,7 +5332,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Strategic: G&amp;W owns or leases 121 freight railroads (p. 21)</t>
+          <t>Strategic (owner/operator of 121 freight railroads, p. 1)</t>
         </is>
       </c>
     </row>
@@ -4673,7 +5344,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>$25.00 per share in cash, without interest; each preferred share converts into 100 common shares first (p. 27). No CVR. Termination fee $3.785 million.</t>
+          <t>$25.00 in cash per common share; each preferred share converts to 100 common shares first. No financing condition. Termination fee $3.785m (about 3%). Ref: $16.30 close 08/12/2016; 53% premium (p. 33).</t>
         </is>
       </c>
     </row>
@@ -4709,7 +5380,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DEFM14A definitive proxy statement dated 09/19/2016, filed 09/20/2016</t>
+          <t>DEFM14A; proxy statement dated 09/19/2016 (file name gives 2016-09-20)</t>
         </is>
       </c>
     </row>
@@ -4721,7 +5392,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>pp. 27–32</t>
+          <t>27–32</t>
         </is>
       </c>
     </row>
@@ -4733,7 +5404,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Mixed: Party A's unsolicited interest in acquiring equity (Q4 2015) prompted the banker search; the Company then ran a target-led auction (pp. 27–28).</t>
+          <t>mixed: Party A's Q4 2015 expression of interest prompted the board to hire GHF, and the target then ran a broad auction</t>
         </is>
       </c>
     </row>
@@ -4757,7 +5428,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>None reported</t>
+          <t>None reported apart from Party A's Q4 2015 approach, recorded as round 0 (#1)</t>
         </is>
       </c>
     </row>
@@ -4769,7 +5440,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Met (process 1): 26 parties: 25 confidentiality agreements from the March 2016 outreach (11 strategic, 14 financial, one per party) plus Party C (July 2016). Page 33 states a total of 25 parties. No post-signing additions.</t>
+          <t>Met (process 1): 25–28 parties (25 stated at p. 33; background supports at least 26 including Party C; see Q3)</t>
         </is>
       </c>
     </row>
@@ -4793,7 +5464,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>US dollars per share of common stock, assuming conversion of preferred into common; some bids also stated as implied equity value</t>
+          <t>US dollars per common share, assuming conversion of preferred into common (as bidders were instructed). G&amp;W's July LOIs included a $1.13 CVR, entered at total package value.</t>
         </is>
       </c>
     </row>
@@ -4805,7 +5476,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Greene Holcomb &amp; Fisher LLC (GHF), whose business BMO Capital Markets Corp. acquired on 08/01/2016; sole financial adviser; fairness opinion 08/12/2016. A BMO affiliate's roughly 5% participation in G&amp;W's credit facility was disclosed after signing and judged not material on 09/06/2016 (pp. 32, 41).</t>
+          <t>Greene Holcomb &amp; Fisher LLC (GHF), whose business BMO Capital Markets Corp. acquired on 08/01/2016; BMO gave the fairness opinion</t>
         </is>
       </c>
     </row>
@@ -4817,7 +5488,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Hinckley, Allen &amp; Snyder LLP; also unnamed STB counsel. G&amp;W's counsel: Simpson Thacher &amp; Bartlett LLP.</t>
+          <t>Hinckley, Allen &amp; Snyder LLP; unnamed STB (regulatory) counsel</t>
         </is>
       </c>
     </row>
@@ -4829,7 +5500,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>After Party A, a Class I rail partner, showed interest in acquiring equity in late 2015, PWRR hired GHF and in March 2016 decided to solicit buyers broadly. GHF contacted 29 parties; 25 signed confidentiality agreements, and nine submitted IOIs of $17.93–$26.50 per share. Seven advanced to management presentations and diligence, late entrant Party C joined, and six LOIs arrived in late July at $19.20–$24.00. The Transaction Committee chose Party B ($24.00, with mark-ups) and G&amp;W ($22.15 with a CVR) for confirmatory diligence. Parties D and E briefly returned with higher bids but fell away. On 08/12/2016 G&amp;W raised to $25.00 all cash, Party B declined to improve, and PWRR signed with G&amp;W that day.</t>
+          <t>After Party A, a Class I rail partner, expressed interest in taking equity in late 2015, PWRR hired GHF and in March 2016 authorized a broad auction. GHF contacted 29 buyers; 25 signed confidentiality agreements, and nine submitted IOIs of $17.93–$26.50 by 06/01/2016. The seven highest bidders got management presentations and the data site; late entrant Party C joined in July. Six non-binding LOIs arrived in late July, and the committee kept only Party B ($24.00) and G&amp;W ($22.15). Parties D and E briefly re-engaged in August but fell away over diligence and exclusivity terms. When PWRR was about to sign with Party B, G&amp;W bid $25.00 in cash with a one-day expiry; Party B would not raise its price, and PWRR signed with G&amp;W on 08/12/2016.</t>
         </is>
       </c>
     </row>

--- a/extraction/providence-worcester.xlsx
+++ b/extraction/providence-worcester.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal facts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rounds'!$A$1:$J$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deal facts'!$A$1:$B$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,14 +439,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V63"/>
+  <dimension ref="A1:V64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
@@ -455,12 +455,12 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
@@ -620,19 +620,15 @@
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>First contact. At a meeting on joint commercial opportunities, Party A (a Class I rail partner) floated joint ventures and "some interest in acquiring equity"; no price, scope (stake or whole company) unstated. Board then formed a subcommittee to interview bankers for possible negotiations with Party A.</t>
+          <t>First contact: at a commercial meeting with CEO Eder and CCO Rogers, Class I rail partner Party A floated joint ventures and "some interest in acquiring equity"; stake size or control not stated, no price. The Board then formed a subcommittee to interview bankers.</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Party A suggested possible joint venture arrangements and expressed some interest in acquiring equity in the Company to further develop strategic opportunities and enhance regional connectivity (p. 27)</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“Party A suggested possible joint venture arrangements and expressed some interest in acquiring equity in the Company to further develop strategic opportunities and enhance regional connectivity” (p. 27)</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="n"/>
       <c r="S2" s="2" t="n"/>
       <c r="T2" s="3" t="n">
         <v>42323</v>
@@ -655,7 +651,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Greene Holcomb &amp; Fisher LLC (GHF), later BMO Capital Markets Corp.</t>
+          <t>Greene Holcomb &amp; Fisher LLC (GHF; from 08/01/2016 BMO Capital Markets Corp.)</t>
         </is>
       </c>
       <c r="D3" s="2" t="n"/>
@@ -680,12 +676,12 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Target's financial adviser, recommended by the board subcommittee after interviewing several banks; engaged at the 01/27/2016 meeting. BMO acquired GHF's business on 08/01/2016 and continued the mandate; BMO gave the 08/12/2016 fairness opinion.</t>
+          <t>Target's financial adviser, engaged on the subcommittee's recommendation; said it would not represent any buyer or buyer financing source. BMO acquired GHF's business on 08/01/2016, continued the role and gave the 08/12/2016 fairness opinion; fee about $2.52 million.</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Following this presentation, the Board approved the subcommittee’s recommendation and the Company engaged GHF. (p. 27)</t>
+          <t>“Following this presentation, the Board approved the subcommittee’s recommendation and the Company engaged GHF.” (p. 27)</t>
         </is>
       </c>
       <c r="R3" s="2" t="n"/>
@@ -711,7 +707,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Providence and Worcester Railroad (target)</t>
+          <t>PWRR (target)</t>
         </is>
       </c>
       <c r="D4" s="2" t="n"/>
@@ -736,12 +732,12 @@
       <c r="O4" s="2" t="n"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Board accepted GHF's proposed process: continue discussions with Party A and solicit other parties' interest in a change in control transaction. Appointed a Transaction Committee (Barrett, Anderson, Garvey) to oversee it; only the full Board could approve a deal. Management met Party A 03/22–03/23.</t>
+          <t>Board adopts GHF's proposed process: continue discussions with Party A and solicit other third parties for a change-in-control transaction; appoints a Transaction Committee (Barrett, Anderson, Garvey) to supervise and recommend, without authority to approve a deal.</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>the Company would proceed with discussions with Party A and also solicit interest from other potential third parties regarding a change in control transaction (p. 27)</t>
+          <t>“the Company would proceed with discussions with Party A and also solicit interest from other potential third parties regarding a change in control transaction” (p. 27)</t>
         </is>
       </c>
       <c r="R4" s="2" t="n"/>
@@ -792,12 +788,12 @@
       <c r="O5" s="2" t="n"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Target's legal counsel; first shown acting at the 03/24/2016 Transaction Committee meeting and attended all its meetings; negotiated the merger documents with Party B's counsel and Simpson Thacher.</t>
+          <t>Target's legal counsel; first shown acting at the 03/24/2016 Transaction Committee meeting, attended all committee meetings, and negotiated the merger documents with bidders' counsel.</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>the Company’s legal counsel, Hinckley, Allen &amp; Snyder LLP (which we refer to as “Hinckley Allen”), participated in all meetings of the Transaction Committee (p. 28)</t>
+          <t>“the Company’s legal counsel, Hinckley, Allen &amp; Snyder LLP (which we refer to as “Hinckley Allen”), participated in all meetings of the Transaction Committee” (p. 28)</t>
         </is>
       </c>
       <c r="R5" s="2" t="n"/>
@@ -818,12 +814,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>03/24/2016</t>
+          <t>week of 03/28/2016</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Providence and Worcester Railroad (target)</t>
+          <t>PWRR (target)</t>
         </is>
       </c>
       <c r="D6" s="2" t="n"/>
@@ -848,28 +844,28 @@
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Transaction Committee authorized GHF to contact Party A and other potential buyers about a change in control transaction; GHF carried this out in the week of 03/28/2016 (#6–#7). Round opened at the authorizing decision (E6).</t>
+          <t>GHF outreach wave, executing the Transaction Committee's 03/24/2016 authorization to contact Party A and other potential buyers. Management had met Party A on 03/22-03/23/2016 and told it of GHF's engagement. NDAs carried no standstill.</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>The Transaction Committee authorized GHF to contact Party A as well as other potential buyers to determine their level of interest in a change in control transaction. (p. 28)</t>
+          <t>“During the week of March 28, 2016, in accordance with the Transaction Committee’s directives, representatives of GHF contacted 11 potential strategic buyers (including Party A) and 18 potential financial buyers.” (p. 28)</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S6" s="2" t="n"/>
       <c r="T6" s="3" t="n">
-        <v>42453</v>
+        <v>42460</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>42453</v>
+        <v>42457</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>42453</v>
+        <v>42463</v>
       </c>
     </row>
     <row r="7">
@@ -914,17 +910,17 @@
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated outreach by GHF. Filing total: 11 strategic buyers contacted, including Party A (first contact at #1). Whether G&amp;W (#10, #14), Party B (#13, #15) or the two Class I railroads (#11) are among the 11 is not stated.</t>
+          <t>Target-initiated (GHF). Filing total: 11 strategic buyers including Party A, whose first contact is #1. Whether G&amp;W or Party B was among them is not stated.</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>representatives of GHF contacted 11 potential strategic buyers (including Party A) and 18 potential financial buyers (p. 28)</t>
+          <t>“representatives of GHF contacted 11 potential strategic buyers (including Party A) and 18 potential financial buyers” (p. 28)</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S7" s="2" t="n"/>
@@ -980,12 +976,12 @@
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated outreach by GHF. 14 of the 18 later signed confidentiality agreements (#9); the other 4 never entered.</t>
+          <t>Target-initiated (GHF). Filing total 18 financial buyers contacted; 14 later signed confidentiality agreements (#9).</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>representatives of GHF contacted 11 potential strategic buyers (including Party A) and 18 potential financial buyers (p. 28)</t>
+          <t>“representatives of GHF contacted 11 potential strategic buyers (including Party A) and 18 potential financial buyers” (p. 28)</t>
         </is>
       </c>
       <c r="R8" s="2" t="n"/>
@@ -1011,7 +1007,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11 potential strategic buyers (incl. Party A)</t>
+          <t>Strategic NDA signers from the March outreach (incl. Party A)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1035,24 +1031,22 @@
       <c r="J9" s="2" t="n"/>
       <c r="K9" s="2" t="n"/>
       <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2" t="n">
-        <v>11</v>
-      </c>
+      <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>All 11 contacted strategic buyers, including Party A, signed; no standstill. Execution dates not given. G&amp;W and Party B (#14, #15) may be among the 11: not established. NDA signers received the Company memorandum.</t>
+          <t>Count: 9-11. All 11 strategic buyers contacted (incl. Party A) signed; G&amp;W (#10) and Party B (#13) have own rows and may be among the 11. Party E and Party F presumably members. Memorandum later sent to all signers.</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Each of the potential strategic buyers and 14 potential financial buyers subsequently executed confidentiality agreements. (p. 28)</t>
+          <t>“Each of the potential strategic buyers and 14 potential financial buyers subsequently executed confidentiality agreements.” (p. 28)</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S9" s="2" t="n"/>
@@ -1075,7 +1069,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>14 potential financial buyers</t>
+          <t>14 financial NDA signers</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1106,17 +1100,17 @@
       <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>No standstill; undated. The filing later says 25 parties signed confidentiality agreements (p. 33), which equals 11 + 14 and leaves no room for Party C (#24) or for G&amp;W and Party B outside #8.</t>
+          <t>14 of the 18 financial buyers contacted signed confidentiality agreements without standstills; the other 4 are not mentioned again. Party D, the only named financial bidder, is presumably a member. Memorandum later sent to all signers.</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Each of the potential strategic buyers and 14 potential financial buyers subsequently executed confidentiality agreements. (p. 28)</t>
+          <t>“Each of the potential strategic buyers and 14 potential financial buyers subsequently executed confidentiality agreements.” (p. 28)</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S10" s="2" t="n"/>
@@ -1134,12 +1128,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>04/03/2016–04/06/2016</t>
+          <t>04/03/2016</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5 potential strategic buyers (incl. G&amp;W)</t>
+          <t>Genesee &amp; Wyoming Inc. (G&amp;W)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1149,7 +1143,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -1164,34 +1158,34 @@
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
       <c r="M11" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N11" s="2" t="n"/>
       <c r="O11" s="2" t="n"/>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Introductory meetings held by GHF and management at the 2016 Connections Convention. First contact for G&amp;W unless it was among the 11 contacted at #6; overlap with #6 not stated. On 04/07 GHF was told to confirm these five parties' continuing interest.</t>
+          <t>Confidentiality agreement dated 04/03/2016, per the merger agreement's definitions (outside the background). G&amp;W met GHF and management at the Connections Convention 04/03-04/06/2016. Whether G&amp;W was one of the 11 strategic contacts is not stated.</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>held a series of introductory meetings with five potential strategic buyers (including G&amp;W) at the American Short Line and Regional Railroad Association’s 2016 Connections Convention (p. 28)</t>
+          <t>“the Confidentiality Agreement between the Company and Parent dated April 3, 2016” (p. A-48)</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S11" s="2" t="n"/>
       <c r="T11" s="3" t="n">
-        <v>42464</v>
+        <v>42463</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>42463</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>42466</v>
+        <v>42463</v>
       </c>
     </row>
     <row r="12">
@@ -1205,7 +1199,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2 additional Class I railroads</t>
+          <t>2 additional Class I railroads (unnamed)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1236,17 +1230,17 @@
       <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated: management approached two further Class I railroads about a possible transaction, reported 04/07/2016. Whether they are among the 11 at #6 or later signed NDAs is not stated; not mentioned again.</t>
+          <t>Target-initiated: management approached them to gauge interest, reported by CFO Noreck on 04/07/2016. Whether they were among the 11 strategic contacts, or signed NDAs, is not stated; no later role reported.</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>the Company had also approached two additional Class I railroads to determine their interest in a possible transaction (p. 28)</t>
+          <t>“Mr. Noreck reported that the Company had also approached two additional Class I railroads to determine their interest in a possible transaction.” (p. 28)</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S12" s="2" t="n"/>
@@ -1264,18 +1258,22 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>by 04/27/2016</t>
+          <t>04/21/2016</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Providence and Worcester Railroad (target)</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n"/>
+          <t>Party B</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Deadline set</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -1289,33 +1287,35 @@
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="n"/>
-      <c r="M13" s="2" t="n"/>
+      <c r="M13" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N13" s="2" t="n"/>
       <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Each potential buyer told to submit a non-binding indication of interest by 05/10/2016. Communication date not stated; reported at the 04/27/2016 board executive session. Window starts at the outreach.</t>
+          <t>First reported contact: introductory meeting of the Company and GHF with "another potential strategic buyer". Whether Party B was among the 11 strategic buyers contacted in the week of 03/28 is not stated.</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>each potential buyer had been advised to submit a non-binding indication of interest by May 10, 2016 (p. 29)</t>
+          <t>“on April 21, 2016, the Company and representatives of GHF held an introductory meeting with another potential strategic buyer (“Party B”).” (p. 28)</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S13" s="2" t="n"/>
       <c r="T13" s="3" t="n">
-        <v>42472</v>
+        <v>42481</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>42457</v>
+        <v>42481</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>42487</v>
+        <v>42481</v>
       </c>
     </row>
     <row r="14">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>04/21/2016</t>
+          <t>undated (reported after 04/21/2016)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -1360,29 +1360,25 @@
       <c r="O14" s="2" t="n"/>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Introductory meeting of the Company and GHF with "another potential strategic buyer". Whether Party B was among the 11 contacted at #6 is not stated.</t>
+          <t>Execution undated: the filing lists Party B among buyers that "had executed confidentiality agreements" and received the memorandum. Placed after #12 in the filing's sequence; Sort date is that of the preceding row.</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>on April 21, 2016, the Company and representatives of GHF held an introductory meeting with another potential strategic buyer (“Party B”). (p. 28)</t>
+          <t>“which was distributed to the potential buyers, including Party A, Party B and G&amp;W, that had executed confidentiality agreements” (p. 28)</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S14" s="2" t="n"/>
       <c r="T14" s="3" t="n">
         <v>42481</v>
       </c>
-      <c r="U14" s="3" t="n">
-        <v>42481</v>
-      </c>
-      <c r="V14" s="3" t="n">
-        <v>42481</v>
-      </c>
+      <c r="U14" s="2" t="n"/>
+      <c r="V14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1390,22 +1386,18 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>undated; by memorandum distribution</t>
+          <t>by 04/27/2016</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>G&amp;W (Genesee &amp; Wyoming Inc.)</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>PWRR (target)</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Deadline set</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -1419,19 +1411,17 @@
       <c r="J15" s="2" t="n"/>
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
-      <c r="M15" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M15" s="2" t="n"/>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>G&amp;W had signed a confidentiality agreement and received the Company memorandum; execution date not given. Kept outside the 11 at #8 because membership is not established; if inside, the NDA total falls by one.</t>
+          <t>GHF advised each potential buyer to submit a non-binding indication of interest by 05/10/2016; reported to the Board's 04/27/2016 executive session.</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>which was distributed to the potential buyers, including Party A, Party B and G&amp;W, that had executed confidentiality agreements (p. 28)</t>
+          <t>“each potential buyer had been advised to submit a non-binding indication of interest by May 10, 2016” (p. 29)</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
@@ -1441,12 +1431,12 @@
       </c>
       <c r="S15" s="2" t="n"/>
       <c r="T15" s="3" t="n">
-        <v>42481</v>
-      </c>
-      <c r="U15" s="3" t="n">
-        <v>42457</v>
-      </c>
-      <c r="V15" s="2" t="n"/>
+        <v>42487</v>
+      </c>
+      <c r="U15" s="2" t="n"/>
+      <c r="V15" s="3" t="n">
+        <v>42487</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1454,22 +1444,18 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>undated; by memorandum distribution</t>
+          <t>after 04/27/2016 (undated)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>PWRR (target)</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Deadline revised</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -1483,19 +1469,17 @@
       <c r="J16" s="2" t="n"/>
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
-      <c r="M16" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M16" s="2" t="n"/>
       <c r="N16" s="2" t="n"/>
       <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Party B had signed a confidentiality agreement and received the Company memorandum; execution date not given. Kept outside the 11 at #8 because membership is not established; if inside, the NDA total falls by one.</t>
+          <t>IOI due date postponed from 05/10 to 05/19/2016 so buyers could "formulate their most compelling offers"; postponement undated, treated as before 05/10 (superseded before arrival).</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>which was distributed to the potential buyers, including Party A, Party B and G&amp;W, that had executed confidentiality agreements (p. 28)</t>
+          <t>“which deadline was subsequently postponed to May 19, 2016 to ensure the potential buyers had sufficient time to formulate their most compelling offers” (p. 29)</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
@@ -1505,12 +1489,12 @@
       </c>
       <c r="S16" s="2" t="n"/>
       <c r="T16" s="3" t="n">
-        <v>42481</v>
-      </c>
-      <c r="U16" s="3" t="n">
-        <v>42457</v>
-      </c>
-      <c r="V16" s="2" t="n"/>
+        <v>42487</v>
+      </c>
+      <c r="U16" s="2" t="n"/>
+      <c r="V16" s="3" t="n">
+        <v>42509</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1518,18 +1502,18 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>after 05/10 due date set; before 05/19/2016</t>
+          <t>05/19/2016</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Providence and Worcester Railroad (target)</t>
+          <t>PWRR (target)</t>
         </is>
       </c>
       <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Deadline revised</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -1548,25 +1532,25 @@
       <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>IOI due date postponed from 05/10 to 05/19/2016 so buyers had time "to formulate their most compelling offers". Revision date not stated; read as made before 05/10 arrived (inferred from the stated purpose).</t>
+          <t>Revised IOI due date reached. Nine IOIs arrived between 05/19 and 06/01/2016 (#17); whether any arrived after 05/19 is not stated.</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>which deadline was subsequently postponed to May 19, 2016 to ensure the potential buyers had sufficient time to formulate their most compelling offers (p. 29)</t>
+          <t>“Between May 19, 2016 and June 1, 2016, the Company received nine written indications of interest (“IOIs”) from potential buyers” (p. 29)</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S17" s="2" t="n"/>
       <c r="T17" s="3" t="n">
-        <v>42483</v>
+        <v>42509</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>42457</v>
+        <v>42509</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>42509</v>
@@ -1578,18 +1562,22 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>05/19/2016</t>
+          <t>05/19/2016-06/01/2016</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Providence and Worcester Railroad (target)</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n"/>
+          <t>9 IOI bidders (unnamed)</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
@@ -1598,27 +1586,45 @@
       <c r="G18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="M18" s="2" t="n"/>
+      <c r="H18" s="4" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="N18" s="2" t="n"/>
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Operative IOI due date. IOIs arrived between 05/19 and 06/01/2016 and were considered by the Transaction Committee on 05/23 and 06/01 (#18).</t>
+          <t>Conditions not reported. Nine written non-binding IOIs, range for the group assuming preferred conversion (equity $90m-$134m). Members unnamed; Party B, G&amp;W, Party D, Party E and Party F presumably among them, as later LOI bidders. Mixed types.</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>which deadline was subsequently postponed to May 19, 2016 (p. 29)</t>
+          <t>“with offer prices per share ranging from $17.93 to $26.50 (assuming the conversion of preferred stock into common stock), implying equity values of $90 million to $134 million” (p. 29)</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q3; Q4</t>
         </is>
       </c>
       <c r="S18" s="2" t="n"/>
@@ -1629,7 +1635,7 @@
         <v>42509</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>42509</v>
+        <v>42522</v>
       </c>
     </row>
     <row r="19">
@@ -1638,12 +1644,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>05/19/2016–06/01/2016</t>
+          <t>by 06/01/2016 (IOIs due 05/19/2016)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9 IOI bidders</t>
+          <t>NDA signers submitting no IOI (unnamed)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1653,7 +1659,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Did not submit</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
@@ -1662,54 +1668,42 @@
       <c r="G19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="4" t="n">
-        <v>17.93</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="N19" s="2" t="n"/>
-      <c r="O19" s="2" t="n"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Conditions not reported (cohort). Non-binding written IOIs; per share assuming preferred converted to common; equity values $90m–$134m. Inferred members: G&amp;W and Parties B, D, E, F (all later LOI bidders except Party C), two later non-LOI bidders (#28–#29) and two low bidders (#20). Party A unknown.</t>
+          <t>Count: 15-18. Signers before July: 25-27 (11 strategic + 14 financial, plus G&amp;W and Party B if outside the 11) − 9 IOIs = 16-18; 15 if p. 33's total of 25 includes Party C. Party A may be here. None reappears.</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>the Company received nine written indications of interest (“IOIs”) from potential buyers, with offer prices per share ranging from $17.93 to $26.50 (p. 29)</t>
+          <t>“Between May 19, 2016 and June 1, 2016, the Company received nine written indications of interest” (p. 29)</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>Q4; Q5</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S19" s="2" t="n"/>
       <c r="T19" s="3" t="n">
-        <v>42509</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>42509</v>
-      </c>
+        <v>42522</v>
+      </c>
+      <c r="U19" s="2" t="n"/>
       <c r="V19" s="3" t="n">
         <v>42522</v>
       </c>
@@ -1720,12 +1714,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>by 05/19/2016</t>
+          <t>05/23/2016-06/01/2016</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>NDA signers not submitting IOIs</t>
+          <t>2 lowest IOI bidders (unnamed)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1735,7 +1729,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Did not submit</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
@@ -1749,39 +1743,35 @@
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="n"/>
+      <c r="M20" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>Lower offer than rivals</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Count: 16–18. 25 signers (#8–#9) plus 0–2 for G&amp;W and Party B if outside #8, less 9 IOI bidders (#18). May include Party A. The filing's 25 total (p. 33) conflicts with Party C's later NDA (Q3).</t>
+          <t>Transaction Committee (meetings 05/23 and 06/01) excluded "the two low bidders" from management presentations, citing the management time required. Identities and prices not given; Party A may be one.</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Between May 19, 2016 and June 1, 2016, the Company received nine written indications of interest (“IOIs”) from potential buyers (p. 29)</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+          <t>“the Transaction Committee concluded that the two low bidders should be excluded from that process” (p. 29)</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="n"/>
       <c r="S20" s="2" t="n"/>
       <c r="T20" s="3" t="n">
-        <v>42509</v>
-      </c>
-      <c r="U20" s="2" t="n"/>
+        <v>42522</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>42513</v>
+      </c>
       <c r="V20" s="3" t="n">
-        <v>42509</v>
+        <v>42522</v>
       </c>
     </row>
     <row r="21">
@@ -1790,58 +1780,52 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>05/23/2016–06/01/2016</t>
+          <t>05/23/2016-06/01/2016</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2 low IOI bidders</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+          <t>PWRR (target)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="n"/>
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
-      <c r="M21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>Lower offer than rivals</t>
-        </is>
-      </c>
+      <c r="M21" s="2" t="n"/>
+      <c r="N21" s="2" t="n"/>
       <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Transaction Committee excluded "the two low bidders" from management presentations, citing the management time presentations would take. Identities and prices not disclosed.</t>
+          <t>Committee advances the remaining seven IOI bidders to in-person management presentations and further diligence, with internet data-site access given alike to all seven. LOI instructions followed in mid-June (#21).</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>the Transaction Committee concluded that the two low bidders should be excluded from that process (p. 29)</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="n"/>
+          <t>“The Transaction Committee authorized representatives of GHF to schedule in-person management presentations with the remaining seven potential buyers and allow these parties to conduct additional due diligence.” (p. 29)</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>Q1; Q4</t>
+        </is>
+      </c>
       <c r="S21" s="2" t="n"/>
       <c r="T21" s="3" t="n">
-        <v>42517</v>
+        <v>42522</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>42513</v>
@@ -1856,18 +1840,18 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>05/23/2016–06/01/2016</t>
+          <t>mid-June 2016</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Providence and Worcester Railroad (target)</t>
+          <t>PWRR (target)</t>
         </is>
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Deadline set</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -1886,28 +1870,24 @@
       <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Transaction Committee advanced the remaining seven IOI bidders to in-person management presentations, further diligence and data-site access, given alike to all seven. Inferred members: G&amp;W, Parties B, D, E, F, one unnamed strategic, one unnamed financial.</t>
+          <t>GHF, at the committee's direction, asks for non-binding LOIs by 07/20/2016 with mark-ups of draft merger agreement, disclosure letter and voting agreement (drafts posted 06/29-07/11), priced per share for 100% of common, preferred converted.</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>The Transaction Committee authorized representatives of GHF to schedule in-person management presentations with the remaining seven potential buyers and allow these parties to conduct additional due diligence. (p. 29)</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>Q2; Q5</t>
-        </is>
-      </c>
+          <t>“representatives of GHF instructed all potential buyers to submit non-binding letters of intent (“LOIs”) by July 20, 2016, together with mark-ups of the forms of merger agreement” (p. 29)</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="n"/>
       <c r="S22" s="2" t="n"/>
       <c r="T22" s="3" t="n">
-        <v>42517</v>
+        <v>42536</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>42513</v>
+        <v>42532</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>42522</v>
+        <v>42540</v>
       </c>
     </row>
     <row r="23">
@@ -1916,18 +1896,22 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>mid-June 2016</t>
+          <t>early July 2016</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Providence and Worcester Railroad (target)</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n"/>
+          <t>Party C</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Deadline set</t>
+          <t>Bidder interest</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -1941,33 +1925,31 @@
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
-      <c r="M23" s="2" t="n"/>
+      <c r="M23" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N23" s="2" t="n"/>
       <c r="O23" s="2" t="n"/>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>GHF told all potential buyers to submit non-binding LOIs by 07/20/2016 with mark-ups of the merger agreement, disclosure letter and voting agreement, pricing 100% of common per share (preferred converted). Drafts posted 06/29, 06/30 and 07/11/2016.</t>
+          <t>First contact: Party C, a strategic buyer new to the process, approached management unsolicited and expressed interest in acquiring the Company; no price.</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>representatives of GHF instructed all potential buyers to submit non-binding letters of intent (“LOIs”) by July 20, 2016, together with mark-ups of the forms of merger agreement (p. 29)</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
+          <t>“a potential strategic buyer that had not previously been part of the process (“Party C”) approached the Company’s management and expressed interest in acquiring the Company” (p. 29)</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="n"/>
       <c r="S23" s="2" t="n"/>
       <c r="T23" s="3" t="n">
-        <v>42536</v>
+        <v>42556</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>42532</v>
+        <v>42552</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>42540</v>
+        <v>42561</v>
       </c>
     </row>
     <row r="24">
@@ -1976,7 +1958,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>early July 2016</t>
+          <t>early July 2016 (before 07/12/2016)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1991,7 +1973,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Bidder interest</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -2012,24 +1994,24 @@
       <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>First contact. A strategic buyer not previously part of the process approached management unprompted and expressed interest in acquiring the Company; no price.</t>
+          <t>Party C executed a confidentiality agreement after its approach and then received the same memorandum the other buyers had (catch-up information).</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>a potential strategic buyer that had not previously been part of the process (“Party C”) approached the Company’s management and expressed interest in acquiring the Company (p. 29)</t>
+          <t>“After executing a confidentiality agreement, Party C was provided the memorandum concerning the Company provided to the other potential buyers.” (p. 29)</t>
         </is>
       </c>
       <c r="R24" s="2" t="n"/>
       <c r="S24" s="2" t="n"/>
       <c r="T24" s="3" t="n">
-        <v>42556</v>
+        <v>42557</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>42552</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>42561</v>
+        <v>42563</v>
       </c>
     </row>
     <row r="25">
@@ -2038,7 +2020,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>early July 2016 (before 07/12/2016)</t>
+          <t>07/12/2016</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2053,7 +2035,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -2062,11 +2044,27 @@
       <c r="G25" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="n"/>
-      <c r="J25" s="2" t="n"/>
-      <c r="K25" s="2" t="n"/>
-      <c r="L25" s="2" t="n"/>
+      <c r="H25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M25" s="2" t="n">
         <v>1</v>
       </c>
@@ -2074,25 +2072,25 @@
       <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>Party C signed a confidentiality agreement, then received the Company memorandum given to other buyers. Not covered by the 25-party total implied by #8–#9 (Q3).</t>
+          <t>Conditions not stated. Unsolicited IOI after reading the memorandum; implied equity $108 million. Made outside the round-1 solicitation; recorded in the round current at receipt.</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>After executing a confidentiality agreement, Party C was provided the memorandum concerning the Company provided to the other potential buyers. (p. 29)</t>
+          <t>“On July 12, 2016, Party C submitted an IOI with an offer price per share of $21.00 (implying an equity value of $108 million).” (p. 29)</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S25" s="2" t="n"/>
       <c r="T25" s="3" t="n">
-        <v>42557</v>
+        <v>42563</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>42552</v>
+        <v>42563</v>
       </c>
       <c r="V25" s="3" t="n">
         <v>42563</v>
@@ -2104,7 +2102,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>07/12/2016</t>
+          <t>07/12/2016-07/14/2016</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2119,7 +2117,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -2128,27 +2126,11 @@
       <c r="G26" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H26" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
       <c r="M26" s="2" t="n">
         <v>1</v>
       </c>
@@ -2156,28 +2138,24 @@
       <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Conditions not reported. IOI, equity value $108m. A late entrant's catch-up IOI submitted while round-2 LOIs were pending; placed in round 2.</t>
+          <t>Target admits Party C to round 2 with catch-up access: internet data site after its IOI and a telephone management presentation on 07/14/2016, which the other seven had had since June.</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>On July 12, 2016, Party C submitted an IOI with an offer price per share of $21.00 (implying an equity value of $108 million). (p. 29)</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
+          <t>“Subsequently, Party C was provided access to the internet data site and the Company’s management held a management presentation with Party C by telephone on July 14, 2016.” (p. 29)</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="n"/>
       <c r="S26" s="2" t="n"/>
       <c r="T26" s="3" t="n">
-        <v>42563</v>
+        <v>42565</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>42563</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>42563</v>
+        <v>42565</v>
       </c>
     </row>
     <row r="27">
@@ -2186,22 +2164,18 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>07/12/2016–07/14/2016</t>
+          <t>07/20/2016</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>PWRR (target)</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -2215,31 +2189,33 @@
       <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="n"/>
-      <c r="M27" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M27" s="2" t="n"/>
       <c r="N27" s="2" t="n"/>
       <c r="O27" s="2" t="n"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Admitted with catch-up access: after its IOI, Party C got data-site access and a telephone management presentation on 07/14/2016, joining the other bidders' diligence six days before LOIs were due.</t>
+          <t>LOI due date reached. Six LOIs arrived "in late July", G&amp;W's on 07/21 (#34); all reviewed on 07/22 and 07/27. LOIs used differing assumptions on transaction expenses and change-in-control payments.</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>Subsequently, Party C was provided access to the internet data site and the Company’s management held a management presentation with Party C by telephone on July 14, 2016. (p. 29)</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="n"/>
+          <t>“In late July 2016, the Company received six LOIs with offer prices per share ranging from $19.20 to $24.00 (implying equity values of $96 million to $121 million).” (p. 29)</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
       <c r="S27" s="2" t="n"/>
       <c r="T27" s="3" t="n">
-        <v>42564</v>
+        <v>42571</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>42563</v>
+        <v>42571</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>42565</v>
+        <v>42571</v>
       </c>
     </row>
     <row r="28">
@@ -2248,18 +2224,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>07/20/2016</t>
+          <t>late July 2016</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Providence and Worcester Railroad (target)</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n"/>
+          <t>Party B</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -2268,22 +2248,40 @@
       <c r="G28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="n"/>
-      <c r="J28" s="2" t="n"/>
-      <c r="K28" s="2" t="n"/>
-      <c r="L28" s="2" t="n"/>
-      <c r="M28" s="2" t="n"/>
+      <c r="H28" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N28" s="2" t="n"/>
       <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>LOI due date. Six LOIs arrived in late July, G&amp;W's on 07/21 (#36); the Transaction Committee reviewed them on 07/22 and 07/27/2016.</t>
+          <t>Light: subject to an expedited diligence review. LOI (non-binding in name) came with Party B's mark-ups of the draft merger and voting agreements, hence Formal. Highest LOI.</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>submit non-binding letters of intent (“LOIs”) by July 20, 2016 (p. 29)</t>
+          <t>“Party B submitted an LOI to acquire the Company for a price of $24.00 per share (subject to an expedited diligence review).” (p. 29)</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
@@ -2299,7 +2297,7 @@
         <v>42571</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>42571</v>
+        <v>42578</v>
       </c>
     </row>
     <row r="29">
@@ -2308,12 +2306,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>by 07/20/2016</t>
+          <t>late July 2016</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Unnamed strategic bidder (non-LOI)</t>
+          <t>Party E</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2323,7 +2321,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Did not submit</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -2332,28 +2330,40 @@
       <c r="G29" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="n"/>
-      <c r="J29" s="2" t="n"/>
-      <c r="K29" s="2" t="n"/>
-      <c r="L29" s="2" t="n"/>
+      <c r="H29" s="4" t="n">
+        <v>21.26</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>21.26</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="M29" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
+      <c r="N29" s="2" t="n"/>
       <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Reported: one strategic buyer among those invited "elected not to submit an LOI"; identity and IOI price not given. Could be Party A if Party A was among the seven advanced.</t>
+          <t>Heavy: 60-day exclusivity period for due diligence and negotiation of definitive documents. Party E sent only a summary of issues on the merger and voting agreements, not a mark-up, so Informal.</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>One strategic buyer and one financial buyer elected not to submit an LOI. (p. 30)</t>
+          <t>“Party E (a strategic buyer) submitted an LOI to acquire the Company for a price of $21.26 per share (subject to a 60-day exclusivity period” (p. 30)</t>
         </is>
       </c>
       <c r="R29" s="2" t="n"/>
@@ -2361,9 +2371,11 @@
       <c r="T29" s="3" t="n">
         <v>42571</v>
       </c>
-      <c r="U29" s="2" t="n"/>
+      <c r="U29" s="3" t="n">
+        <v>42571</v>
+      </c>
       <c r="V29" s="3" t="n">
-        <v>42571</v>
+        <v>42578</v>
       </c>
     </row>
     <row r="30">
@@ -2372,12 +2384,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>by 07/20/2016</t>
+          <t>late July 2016</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Unnamed financial bidder (non-LOI)</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2387,7 +2399,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Did not submit</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
@@ -2396,38 +2408,56 @@
       <c r="G30" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="n"/>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" s="2" t="n"/>
-      <c r="L30" s="2" t="n"/>
+      <c r="H30" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="M30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
+      <c r="N30" s="2" t="n"/>
       <c r="O30" s="2" t="n"/>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Reported: one financial buyer among those invited "elected not to submit an LOI"; identity and IOI price not given.</t>
+          <t>Heavy: four-week diligence period. With Party D's mark-ups of the draft merger and voting agreements, hence Formal.</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>One strategic buyer and one financial buyer elected not to submit an LOI. (p. 30)</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="n"/>
+          <t>“Party D (a financial buyer) submitted an LOI to acquire the Company for a price of $21.00 per share (subject to a four-week diligence period).” (p. 30)</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
       <c r="S30" s="2" t="n"/>
       <c r="T30" s="3" t="n">
         <v>42571</v>
       </c>
-      <c r="U30" s="2" t="n"/>
+      <c r="U30" s="3" t="n">
+        <v>42571</v>
+      </c>
       <c r="V30" s="3" t="n">
-        <v>42571</v>
+        <v>42578</v>
       </c>
     </row>
     <row r="31">
@@ -2441,7 +2471,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>Party C</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2461,10 +2491,10 @@
         <v>2</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>24</v>
+        <v>19.3</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>24</v>
+        <v>19.3</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2473,12 +2503,12 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Formal</t>
+          <t>Informal</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Heavy</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
@@ -2488,12 +2518,12 @@
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>Subject to an expedited diligence review. Non-binding LOI with mark-ups of the merger and voting agreements (Formal, E11). Highest LOI. Prices rested on differing assumptions about transaction expenses and change-in-control payments.</t>
+          <t>Heavy: 30-day diligence period. No mark-up reported. Below its own 07/12 IOI of $21.00 (#24).</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>Party B submitted an LOI to acquire the Company for a price of $24.00 per share (subject to an expedited diligence review). (p. 29)</t>
+          <t>“Party C submitted an LOI to acquire the Company for a price of $19.30 per share (subject to a 30-day diligence period).” (p. 30)</t>
         </is>
       </c>
       <c r="R31" s="2" t="n"/>
@@ -2519,7 +2549,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Party E</t>
+          <t>Party F</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2539,10 +2569,10 @@
         <v>2</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>21.26</v>
+        <v>19.2</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>21.26</v>
+        <v>19.2</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2566,12 +2596,12 @@
       <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Subject to a 60-day exclusivity period for diligence and documentation. Gave only a summary of material issues on the merger and voting agreements, not a mark-up (Informal).</t>
+          <t>Heavy: 30-day due diligence period. No mark-up reported. Lowest LOI.</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>Party E (a strategic buyer) submitted an LOI to acquire the Company for a price of $21.26 per share (subject to a 60-day exclusivity period for due diligence (p. 30)</t>
+          <t>“Party F (a strategic buyer) submitted an LOI to acquire the Company for a price of $19.20 per share (subject to a 30-day due diligence period).” (p. 30)</t>
         </is>
       </c>
       <c r="R32" s="2" t="n"/>
@@ -2592,12 +2622,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>late July 2016</t>
+          <t>late July 2016 (LOIs due 07/20/2016)</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Party E</t>
+          <t>Unnamed strategic round-2 bidder</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2607,7 +2637,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Exclusivity changed</t>
+          <t>Did not submit</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -2624,16 +2654,20 @@
       <c r="M33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N33" s="2" t="n"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Requested: Party E's LOI asked for a 60-day exclusivity period for due diligence and negotiation of definitive documentation. Not granted.</t>
+          <t>One of the seven advanced IOI bidders "elected not to submit an LOI"; no reason given, not mentioned again. Party A may be this bidder (not stated).</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>subject to a 60-day exclusivity period for due diligence and negotiation of definitive documentation (p. 30)</t>
+          <t>“One strategic buyer and one financial buyer elected not to submit an LOI.” (p. 30)</t>
         </is>
       </c>
       <c r="R33" s="2" t="n"/>
@@ -2654,12 +2688,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>late July 2016</t>
+          <t>late July 2016 (LOIs due 07/20/2016)</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>Unnamed financial round-2 bidder</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2669,7 +2703,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Did not submit</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
@@ -2678,40 +2712,28 @@
       <c r="G34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H34" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="I34" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" s="2" t="n"/>
       <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Subject to a four-week diligence period. LOI with mark-ups of the draft merger and voting agreements (Formal, E11).</t>
+          <t>One of the seven advanced IOI bidders "elected not to submit an LOI"; no reason given, not mentioned again.</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>Party D (a financial buyer) submitted an LOI to acquire the Company for a price of $21.00 per share (subject to a four-week diligence period). (p. 30)</t>
+          <t>“One strategic buyer and one financial buyer elected not to submit an LOI.” (p. 30)</t>
         </is>
       </c>
       <c r="R34" s="2" t="n"/>
@@ -2732,12 +2754,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>late July 2016</t>
+          <t>07/21/2016</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>G&amp;W</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2757,10 +2779,10 @@
         <v>2</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>19.3</v>
+        <v>21.15</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>19.3</v>
+        <v>21.15</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -2769,7 +2791,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Informal</t>
+          <t>Formal</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -2784,24 +2806,28 @@
       <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>Subject to a 30-day diligence period. LOI; no mark-up reported. Down from its $21.00 IOI (#25).</t>
+          <t>Heavy: three-week exclusive diligence period. $20.02 cash at closing plus $1.13 CVR tied to a later sale of the South Quay property (CVR payment form not stated). With mark-ups of merger and voting agreements and disclosure letter: Formal. One day after the due date.</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>Party C submitted an LOI to acquire the Company for a price of $19.30 per share (subject to a 30-day diligence period). (p. 30)</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="n"/>
+          <t>“G&amp;W submitted an LOI on July 21, 2016 to acquire the Company for a price of $21.15 per share (subject to a three-week exclusive diligence period).” (p. 29)</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>Q5; Q6</t>
+        </is>
+      </c>
       <c r="S35" s="2" t="n"/>
       <c r="T35" s="3" t="n">
-        <v>42571</v>
+        <v>42572</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>42571</v>
+        <v>42572</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>42578</v>
+        <v>42572</v>
       </c>
     </row>
     <row r="36">
@@ -2810,12 +2836,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>late July 2016</t>
+          <t>07/21/2016-07/26/2016</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Party F</t>
+          <t>G&amp;W</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2825,7 +2851,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
@@ -2834,27 +2860,11 @@
       <c r="G36" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H36" s="4" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="I36" s="4" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
       <c r="M36" s="2" t="n">
         <v>1</v>
       </c>
@@ -2862,24 +2872,24 @@
       <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Subject to a 30-day due diligence period. LOI; no mark-up reported. Lowest LOI.</t>
+          <t>Price signal: GHF tells G&amp;W its price and CVR structure are not competitive. No such feedback is reported to other bidders.</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>Party F (a strategic buyer) submitted an LOI to acquire the Company for a price of $19.20 per share (subject to a 30-day due diligence period). (p. 30)</t>
+          <t>“in response to feedback from representatives of GHF indicating its price and CVR structure were not competitive” (p. 29)</t>
         </is>
       </c>
       <c r="R36" s="2" t="n"/>
       <c r="S36" s="2" t="n"/>
       <c r="T36" s="3" t="n">
-        <v>42571</v>
+        <v>42574</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>42571</v>
+        <v>42572</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>42578</v>
+        <v>42577</v>
       </c>
     </row>
     <row r="37">
@@ -2888,7 +2898,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>07/21/2016</t>
+          <t>07/26/2016</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2913,10 +2923,10 @@
         <v>2</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>21.15</v>
+        <v>22.15</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>21.15</v>
+        <v>22.15</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -2930,7 +2940,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Heavy</t>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
@@ -2940,12 +2950,12 @@
       <c r="O37" s="2" t="n"/>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>Subject to a three-week exclusive diligence period. $20.02 cash at closing plus $1.13 CVR tied to a later sale of the South Quay property (CVR payment form not stated). Mark-ups of merger, voting agreement and disclosure letter (Formal). One day after the due date.</t>
+          <t>Unclear: revised LOI states no conditions while diligence stays open (on-site diligence to 08/11). $21.02 cash plus $1.13 CVR. Formal as a revision resting on G&amp;W's mark-ups (#34).</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>G&amp;W submitted an LOI on July 21, 2016 to acquire the Company for a price of $21.15 per share (subject to a three-week exclusive diligence period). (p. 29)</t>
+          <t>“G&amp;W submitted a revised LOI, which increased its offer to $22.15 per share (including $21.02 in cash and $1.13 CVR).” (p. 29)</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
@@ -2955,13 +2965,13 @@
       </c>
       <c r="S37" s="2" t="n"/>
       <c r="T37" s="3" t="n">
-        <v>42572</v>
+        <v>42577</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>42572</v>
+        <v>42577</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>42572</v>
+        <v>42577</v>
       </c>
     </row>
     <row r="38">
@@ -2970,60 +2980,58 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>07/21/2016</t>
+          <t>07/27/2016 (committee meetings 07/22 and 07/27)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>G&amp;W</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>PWRR (target)</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Exclusivity changed</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H38" s="2" t="n"/>
       <c r="I38" s="2" t="n"/>
       <c r="J38" s="2" t="n"/>
       <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="n"/>
-      <c r="M38" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M38" s="2" t="n"/>
       <c r="N38" s="2" t="n"/>
       <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Requested: G&amp;W's LOI was conditioned on a three-week exclusive diligence period. Not granted.</t>
+          <t>Move to definitive negotiation with selected bidders G&amp;W and Party B. Decision dated 07/27: on 07/22 G&amp;W ($21.15) trailed Party E. Both got on-site diligence 07/27-08/11 incl. hi-rail trips. Committee also cited multi-party on-site diligence delays and confidentiality.</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>subject to a three-week exclusive diligence period (p. 29)</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="n"/>
+          <t>“the Company should proceed with confirmatory due diligence and negotiations with G&amp;W and Party B because of the higher offers made by each of G&amp;W and Party B” (p. 30)</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S38" s="2" t="n"/>
       <c r="T38" s="3" t="n">
-        <v>42572</v>
+        <v>42578</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>42572</v>
+        <v>42573</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>42572</v>
+        <v>42578</v>
       </c>
     </row>
     <row r="39">
@@ -3032,12 +3040,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/26/2016</t>
+          <t>late July 2016 (after the committee decision, before 07/29/2016)</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>G&amp;W</t>
+          <t>Party C</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3047,7 +3055,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
@@ -3056,56 +3064,40 @@
       <c r="G39" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H39" s="4" t="n">
-        <v>22.15</v>
-      </c>
-      <c r="I39" s="4" t="n">
-        <v>22.15</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+      <c r="H39" s="2" t="n"/>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39" s="2" t="n"/>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="n"/>
       <c r="M39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N39" s="2" t="n"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>Lower offer than rivals</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Conditions not restated; whether #36's exclusive-diligence condition still applied is not said. Raised after GHF said its price and CVR structure were not competitive: $21.02 cash plus $1.13 CVR. Formal via #36's mark-ups (Q7).</t>
+          <t>Not selected for round 3 (#37) against the higher G&amp;W ($22.15) and Party B ($24.00) offers; its LOI was $19.30. GHF then told the remaining bidders they were out.</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>G&amp;W submitted a revised LOI, which increased its offer to $22.15 per share (including $21.02 in cash and $1.13 CVR). (p. 29)</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t>Q7</t>
-        </is>
-      </c>
+          <t>“representatives of GHF subsequently contacted the remaining bidders to inform them that they were no longer involved in the process” (p. 30)</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="n"/>
       <c r="S39" s="2" t="n"/>
       <c r="T39" s="3" t="n">
-        <v>42577</v>
+        <v>42578</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>42577</v>
+        <v>42573</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>42577</v>
+        <v>42580</v>
       </c>
     </row>
     <row r="40">
@@ -3114,17 +3106,17 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>07/27/2016 (decision; told subsequently)</t>
+          <t>late July 2016 (after the committee decision, before 07/29/2016)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -3154,12 +3146,12 @@
       <c r="O40" s="2" t="n"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Transaction Committee kept only G&amp;W and Party B "because of the higher offers"; GHF then told the other bidders they were out. Party C's LOI: $19.30. Decision dated 07/27: it relies on G&amp;W's 07/26 revision (#38).</t>
+          <t>Not selected for round 3 (#37) against the higher G&amp;W ($22.15) and Party B ($24.00) offers; its LOI was $21.00. GHF then told the remaining bidders they were out.</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>representatives of GHF subsequently contacted the remaining bidders to inform them that they were no longer involved in the process (p. 30)</t>
+          <t>“representatives of GHF subsequently contacted the remaining bidders to inform them that they were no longer involved in the process” (p. 30)</t>
         </is>
       </c>
       <c r="R40" s="2" t="n"/>
@@ -3168,10 +3160,10 @@
         <v>42578</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>42578</v>
+        <v>42573</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>42578</v>
+        <v>42580</v>
       </c>
     </row>
     <row r="41">
@@ -3180,17 +3172,17 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>07/27/2016 (decision; told subsequently)</t>
+          <t>late July 2016 (after the committee decision, before 07/29/2016)</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>Party E</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -3220,12 +3212,12 @@
       <c r="O41" s="2" t="n"/>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Transaction Committee kept only G&amp;W and Party B "because of the higher offers"; GHF then told the other bidders they were out. Party D's LOI: $21.00. Decision dated 07/27: it relies on G&amp;W's 07/26 revision (#38).</t>
+          <t>Not selected for round 3 (#37) against the higher G&amp;W ($22.15) and Party B ($24.00) offers; its LOI was $21.26. GHF then told the remaining bidders they were out.</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>representatives of GHF subsequently contacted the remaining bidders to inform them that they were no longer involved in the process (p. 30)</t>
+          <t>“representatives of GHF subsequently contacted the remaining bidders to inform them that they were no longer involved in the process” (p. 30)</t>
         </is>
       </c>
       <c r="R41" s="2" t="n"/>
@@ -3234,10 +3226,10 @@
         <v>42578</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>42578</v>
+        <v>42573</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>42578</v>
+        <v>42580</v>
       </c>
     </row>
     <row r="42">
@@ -3246,12 +3238,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>07/27/2016 (decision; told subsequently)</t>
+          <t>late July 2016 (after the committee decision, before 07/29/2016)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Party E</t>
+          <t>Party F</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -3286,12 +3278,12 @@
       <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Transaction Committee kept only G&amp;W and Party B "because of the higher offers"; GHF then told the other bidders they were out. Party E's LOI: $21.26. Decision dated 07/27: it relies on G&amp;W's 07/26 revision (#38).</t>
+          <t>Not selected for round 3 (#37) against the higher G&amp;W ($22.15) and Party B ($24.00) offers; its LOI was $19.20. GHF then told the remaining bidders they were out.</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>representatives of GHF subsequently contacted the remaining bidders to inform them that they were no longer involved in the process (p. 30)</t>
+          <t>“representatives of GHF subsequently contacted the remaining bidders to inform them that they were no longer involved in the process” (p. 30)</t>
         </is>
       </c>
       <c r="R42" s="2" t="n"/>
@@ -3300,10 +3292,10 @@
         <v>42578</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>42578</v>
+        <v>42573</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>42578</v>
+        <v>42580</v>
       </c>
     </row>
     <row r="43">
@@ -3312,29 +3304,29 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>07/27/2016 (decision; told subsequently)</t>
+          <t>07/29/2016</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Party F</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Re-entered</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H43" s="2" t="n"/>
       <c r="I43" s="2" t="n"/>
@@ -3344,32 +3336,28 @@
       <c r="M43" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>Lower offer than rivals</t>
-        </is>
-      </c>
+      <c r="N43" s="2" t="n"/>
       <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>Transaction Committee kept only G&amp;W and Party B "because of the higher offers"; GHF then told the other bidders they were out. Party F's LOI: $19.20. Decision dated 07/27: it relies on G&amp;W's 07/26 revision (#38).</t>
+          <t>On calls with GHF after being dropped (#39), Party D expressed interest in re-engaging and raising its offer. Not admitted to round 3's on-site diligence; its bids are still received.</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>representatives of GHF subsequently contacted the remaining bidders to inform them that they were no longer involved in the process (p. 30)</t>
+          <t>“During those calls, Party D and Party E both expressed interest in reengaging and enhancing their offers.” (p. 30)</t>
         </is>
       </c>
       <c r="R43" s="2" t="n"/>
       <c r="S43" s="2" t="n"/>
       <c r="T43" s="3" t="n">
-        <v>42578</v>
+        <v>42580</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>42578</v>
+        <v>42580</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>42578</v>
+        <v>42580</v>
       </c>
     </row>
     <row r="44">
@@ -3378,18 +3366,22 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>07/27/2016</t>
+          <t>07/29/2016</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Providence and Worcester Railroad (target)</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="n"/>
+          <t>Party E</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Re-entered</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
@@ -3403,33 +3395,31 @@
       <c r="J44" s="2" t="n"/>
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="n"/>
-      <c r="M44" s="2" t="n"/>
+      <c r="M44" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N44" s="2" t="n"/>
       <c r="O44" s="2" t="n"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Transaction Committee moved to confirmatory diligence and negotiations with G&amp;W and Party B only (definitive negotiation with selected bidders, no final-bid request). Both did on-site diligence 07/27–08/11. Dated 07/27, the meeting after G&amp;W's 07/26 revision.</t>
+          <t>On calls with GHF after being dropped (#40), Party E expressed interest in re-engaging and raising its offer. Not admitted to round 3's on-site diligence; its bids are still received.</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>The Transaction Committee concluded that the Company should proceed with confirmatory due diligence and negotiations with G&amp;W and Party B because of the higher offers (p. 30)</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
+          <t>“During those calls, Party D and Party E both expressed interest in reengaging and enhancing their offers.” (p. 30)</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="n"/>
       <c r="S44" s="2" t="n"/>
       <c r="T44" s="3" t="n">
-        <v>42578</v>
+        <v>42580</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>42578</v>
+        <v>42580</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>42578</v>
+        <v>42580</v>
       </c>
     </row>
     <row r="45">
@@ -3438,7 +3428,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>07/29/2016</t>
+          <t>08/01/2016</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3453,7 +3443,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Re-entered</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
@@ -3462,11 +3452,27 @@
       <c r="G45" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H45" s="2" t="n"/>
-      <c r="I45" s="2" t="n"/>
-      <c r="J45" s="2" t="n"/>
-      <c r="K45" s="2" t="n"/>
-      <c r="L45" s="2" t="n"/>
+      <c r="H45" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="M45" s="2" t="n">
         <v>1</v>
       </c>
@@ -3474,28 +3480,28 @@
       <c r="O45" s="2" t="n"/>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>On calls with GHF, Party D expressed interest in reengaging and enhancing its offer after being told it was out (#40). Not admitted to round 3; its revised proposal was still received.</t>
+          <t>Heavy: 30-day due diligence period. Revised LOI raising $21.00 (#29) to $24.00, level with Party B. No new mark-up reported; Formal as resting on its July mark-ups.</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>During those calls, Party D and Party E both expressed interest in reengaging and enhancing their offers. (p. 30)</t>
+          <t>“On August 1, 2016, Party D submitted a revised LOI at a price of $24.00 per share” (p. 30)</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="S45" s="2" t="n"/>
       <c r="T45" s="3" t="n">
-        <v>42580</v>
+        <v>42583</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>42580</v>
+        <v>42583</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>42580</v>
+        <v>42583</v>
       </c>
     </row>
     <row r="46">
@@ -3504,7 +3510,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>07/29/2016</t>
+          <t>08/01/2016</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3519,7 +3525,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Re-entered</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
@@ -3528,11 +3534,27 @@
       <c r="G46" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H46" s="2" t="n"/>
-      <c r="I46" s="2" t="n"/>
-      <c r="J46" s="2" t="n"/>
-      <c r="K46" s="2" t="n"/>
-      <c r="L46" s="2" t="n"/>
+      <c r="H46" s="4" t="n">
+        <v>23.81</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>23.81</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="M46" s="2" t="n">
         <v>1</v>
       </c>
@@ -3540,28 +3562,24 @@
       <c r="O46" s="2" t="n"/>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>On calls with GHF, Party E expressed interest in reengaging and enhancing its offer after being told it was out (#41). Not admitted to round 3; its revised proposal was still received.</t>
+          <t>Heavy: 30-day due diligence period. Revised LOI raising $21.26 (#28) to $23.81, backed by financing support from Party F (#46). No mark-up reported.</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>During those calls, Party D and Party E both expressed interest in reengaging and enhancing their offers. (p. 30)</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
+          <t>“Party E submitted a revised LOI, along with financing support, from Party F, at a price of $23.81 per share. Both revised proposals contained a 30-day due diligence period.” (p. 30)</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="n"/>
       <c r="S46" s="2" t="n"/>
       <c r="T46" s="3" t="n">
-        <v>42580</v>
+        <v>42583</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>42580</v>
+        <v>42583</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>42580</v>
+        <v>42583</v>
       </c>
     </row>
     <row r="47">
@@ -3575,17 +3593,17 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
+          <t>Party F</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
@@ -3594,27 +3612,11 @@
       <c r="G47" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H47" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="I47" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
+      <c r="H47" s="2" t="n"/>
+      <c r="I47" s="2" t="n"/>
+      <c r="J47" s="2" t="n"/>
+      <c r="K47" s="2" t="n"/>
+      <c r="L47" s="2" t="n"/>
       <c r="M47" s="2" t="n">
         <v>1</v>
       </c>
@@ -3622,19 +3624,15 @@
       <c r="O47" s="2" t="n"/>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>Subject to a 30-day due diligence period. Revised LOI up from $21.00 (#33); matched Party B's $24.00. No new mark-up reported; Formal via its July mark-ups (Q7).</t>
+          <t>Financing support: Party F, dropped on 07/27 (#41), backs Party E's revised LOI. Under the conventions this is not a bidding group; Party E keeps its identity and Party F does not re-enter.</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>On August 1, 2016, Party D submitted a revised LOI at a price of $24.00 per share (p. 30)</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>Q2; Q7</t>
-        </is>
-      </c>
+          <t>“Party E submitted a revised LOI, along with financing support, from Party F” (p. 30)</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="n"/>
       <c r="S47" s="2" t="n"/>
       <c r="T47" s="3" t="n">
         <v>42583</v>
@@ -3657,17 +3655,13 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Party E</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>PWRR (target)</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
@@ -3676,47 +3670,25 @@
       <c r="G48" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H48" s="4" t="n">
-        <v>23.81</v>
-      </c>
-      <c r="I48" s="4" t="n">
-        <v>23.81</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H48" s="2" t="n"/>
+      <c r="I48" s="2" t="n"/>
+      <c r="J48" s="2" t="n"/>
+      <c r="K48" s="2" t="n"/>
+      <c r="L48" s="2" t="n"/>
+      <c r="M48" s="2" t="n"/>
       <c r="N48" s="2" t="n"/>
       <c r="O48" s="2" t="n"/>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>Subject to a 30-day due diligence period. Revised LOI up from $21.26 (#31), with financing support from Party F (#48). Committee had BMO clarify terms and diligence needs.</t>
+          <t>Target engages the re-entered bidders: after reviewing Party D's and Party E's revised LOIs, the committee has BMO (GHF's successor from 08/01) clarify their terms and diligence requirements.</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>Party E submitted a revised LOI, along with financing support, from Party F, at a price of $23.81 per share. (p. 30)</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
+          <t>“subsequently directed representatives of BMO (which acquired the business of GHF on August 1, 2016) to clarify certain elements of the revised proposals and the bidders’ respective due diligence requirements” (p. 30)</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="n"/>
       <c r="S48" s="2" t="n"/>
       <c r="T48" s="3" t="n">
         <v>42583</v>
@@ -3734,12 +3706,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>08/01/2016</t>
+          <t>08/02/2016</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Party F (supporting Party E)</t>
+          <t>Party E</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3749,7 +3721,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
@@ -3758,34 +3730,52 @@
       <c r="G49" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H49" s="2" t="n"/>
-      <c r="I49" s="2" t="n"/>
-      <c r="J49" s="2" t="n"/>
-      <c r="K49" s="2" t="n"/>
-      <c r="L49" s="2" t="n"/>
-      <c r="M49" s="2" t="n"/>
+      <c r="H49" s="4" t="n">
+        <v>21.26</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>21.26</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N49" s="2" t="n"/>
       <c r="O49" s="2" t="n"/>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>Financing support: Party F, dropped at #42, backed Party E's revised LOI. Not a bidding group (E4); Party F does not re-enter.</t>
+          <t>Heavy: reverts to its original terms (#28), which carried a 60-day exclusivity period for diligence and documentation. Party E withdrew its $23.81 revised proposal and confirmed $21.26.</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>Party E submitted a revised LOI, along with financing support, from Party F (p. 30)</t>
+          <t>“Party E withdrew its revised proposal on August 2, 2016 (but confirmed its original proposal of $21.26 per share)” (p. 30)</t>
         </is>
       </c>
       <c r="R49" s="2" t="n"/>
       <c r="S49" s="2" t="n"/>
       <c r="T49" s="3" t="n">
-        <v>42583</v>
+        <v>42584</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>42583</v>
+        <v>42584</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>42583</v>
+        <v>42584</v>
       </c>
     </row>
     <row r="50">
@@ -3794,22 +3784,22 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>08/02/2016</t>
+          <t>early August 2016 (after 08/01, by 08/04/2016)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Party E</t>
+          <t>Party D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Exclusivity changed</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
@@ -3818,27 +3808,11 @@
       <c r="G50" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H50" s="4" t="n">
-        <v>21.26</v>
-      </c>
-      <c r="I50" s="4" t="n">
-        <v>21.26</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
+      <c r="H50" s="2" t="n"/>
+      <c r="I50" s="2" t="n"/>
+      <c r="J50" s="2" t="n"/>
+      <c r="K50" s="2" t="n"/>
+      <c r="L50" s="2" t="n"/>
       <c r="M50" s="2" t="n">
         <v>1</v>
       </c>
@@ -3846,28 +3820,24 @@
       <c r="O50" s="2" t="n"/>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>Reversion: withdrew the 08/01 $23.81 proposal but confirmed its original $21.26 LOI (#31), whose terms included a 60-day exclusivity for diligence and documentation.</t>
+          <t>Requested and refused: Party D would not shorten its 30-day diligence and asked the Company not to sign with anyone else meanwhile; the Company declined, citing Party B's and G&amp;W's active interest. Upper bound: the 08/04 meeting continued only with G&amp;W and Party B.</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>Party E withdrew its revised proposal on August 2, 2016 (but confirmed its original proposal of $21.26 per share) (p. 30)</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>Q8</t>
-        </is>
-      </c>
+          <t>“Party D declined to shorten its due diligence period and requested that the Company commit that it would not enter into an agreement with another bidder” (p. 30)</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="n"/>
       <c r="S50" s="2" t="n"/>
       <c r="T50" s="3" t="n">
         <v>42584</v>
       </c>
       <c r="U50" s="3" t="n">
-        <v>42584</v>
+        <v>42583</v>
       </c>
       <c r="V50" s="3" t="n">
-        <v>42584</v>
+        <v>42586</v>
       </c>
     </row>
     <row r="51">
@@ -3876,7 +3846,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>after 08/01/2016 (reported with 08/02 events)</t>
+          <t>early August 2016 (after 08/01, by 08/04/2016)</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3891,7 +3861,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Exclusivity changed</t>
+          <t>Withdrew</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
@@ -3908,19 +3878,27 @@
       <c r="M51" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N51" s="2" t="n"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>Terms or process</t>
+        </is>
+      </c>
       <c r="O51" s="2" t="n"/>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>Requested: Party D refused to shorten its 30-day diligence and asked the Company to commit not to sign with another bidder during it. The Company declined, citing Party B's and G&amp;W's active interest.</t>
+          <t>After the refusal (#49), Party D said it would not proceed with further diligence "at that time"; its $24.00 bid (#44) lapsed.</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>requested that the Company commit that it would not enter into an agreement with another bidder during its 30-day due diligence period (p. 30)</t>
-        </is>
-      </c>
-      <c r="R51" s="2" t="n"/>
+          <t>“the Company declined to make such a commitment, at which point Party D indicated that it would not proceed with further due diligence at that time” (p. 30)</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
       <c r="S51" s="2" t="n"/>
       <c r="T51" s="3" t="n">
         <v>42584</v>
@@ -3928,7 +3906,9 @@
       <c r="U51" s="3" t="n">
         <v>42583</v>
       </c>
-      <c r="V51" s="2" t="n"/>
+      <c r="V51" s="3" t="n">
+        <v>42586</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -3936,22 +3916,18 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>after 08/01/2016 (reported with 08/02 events)</t>
+          <t>08/04/2016</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Party D</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>PWRR (target)</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n"/>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Withdrew</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
@@ -3965,34 +3941,30 @@
       <c r="J52" s="2" t="n"/>
       <c r="K52" s="2" t="n"/>
       <c r="L52" s="2" t="n"/>
-      <c r="M52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>Terms or process</t>
-        </is>
-      </c>
+      <c r="M52" s="2" t="n"/>
+      <c r="N52" s="2" t="n"/>
       <c r="O52" s="2" t="n"/>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>After the Company refused the commitment, Party D said it would not proceed with further due diligence "at that time"; standing offer $24.00 (#46).</t>
+          <t>Preferred bidder: committee keeps diligence and negotiation going with G&amp;W and Party B but, given Party B's higher price, tells advisers to prioritize Party B and complete its merger agreement.</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>at which point Party D indicated that it would not proceed with further due diligence at that time (p. 30)</t>
+          <t>“given the higher price offered by Party B, to prioritize Party B and proceed to complete the negotiation of the merger agreement with Party B” (p. 31)</t>
         </is>
       </c>
       <c r="R52" s="2" t="n"/>
       <c r="S52" s="2" t="n"/>
       <c r="T52" s="3" t="n">
-        <v>42584</v>
+        <v>42586</v>
       </c>
       <c r="U52" s="3" t="n">
-        <v>42583</v>
-      </c>
-      <c r="V52" s="2" t="n"/>
+        <v>42586</v>
+      </c>
+      <c r="V52" s="3" t="n">
+        <v>42586</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -4000,18 +3972,22 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>08/04/2016</t>
+          <t>by 08/04/2016</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Providence and Worcester Railroad (target)</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="n"/>
+          <t>Party E</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
@@ -4025,26 +4001,40 @@
       <c r="J53" s="2" t="n"/>
       <c r="K53" s="2" t="n"/>
       <c r="L53" s="2" t="n"/>
-      <c r="M53" s="2" t="n"/>
-      <c r="N53" s="2" t="n"/>
-      <c r="O53" s="2" t="n"/>
+      <c r="M53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>Preferred bidder: the Committee kept diligence and negotiations going with both G&amp;W and Party B but, given Party B's higher price, told advisers to prioritize Party B and complete its merger agreement.</t>
+          <t>Inferred: the 08/04 direction names only G&amp;W and Party B as continuing; Party E's reconfirmed $21.26 bid (#48) is never mentioned again.</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>given the higher price offered by Party B, to prioritize Party B and proceed to complete the negotiation of the merger agreement with Party B (p. 31)</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="n"/>
+          <t>“the Transaction Committee directed the management team and representatives of each of BMO and Hinckley Allen to continue diligence and negotiations with both G&amp;W and Party B” (p. 31)</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
       <c r="S53" s="2" t="n"/>
       <c r="T53" s="3" t="n">
         <v>42586</v>
       </c>
       <c r="U53" s="3" t="n">
-        <v>42586</v>
+        <v>42584</v>
       </c>
       <c r="V53" s="3" t="n">
         <v>42586</v>
@@ -4108,17 +4098,17 @@
       <c r="O54" s="2" t="n"/>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>Diligence still open (on-site to 08/11) under its expedited-review condition. Carried from #30: Party B's counsel returned a revised draft merger agreement while the Company finalized terms with it; its price stood $1.00 below G&amp;W on 08/12.</t>
+          <t>Light: expedited diligence per its LOI, on-site diligence continuing to 08/11. Carried from #27: after Hinckley Allen sent a revised merger agreement (08/01) and the Company chose to complete it with Party B, Party B's counsel returned its own revised draft.</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>On August 4, 2016, legal counsel for Party B provided a revised draft of the merger agreement (p. 31)</t>
+          <t>“On August 4, 2016, legal counsel for Party B provided a revised draft of the merger agreement” (p. 31)</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="S54" s="2" t="n"/>
@@ -4143,10 +4133,14 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Providence and Worcester Railroad (target)</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="n"/>
+          <t>G&amp;W</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Other material event</t>
@@ -4163,17 +4157,19 @@
       <c r="J55" s="2" t="n"/>
       <c r="K55" s="2" t="n"/>
       <c r="L55" s="2" t="n"/>
-      <c r="M55" s="2" t="n"/>
+      <c r="M55" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N55" s="2" t="n"/>
       <c r="O55" s="2" t="n"/>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>Target told G&amp;W it intended to sign with another bidder; G&amp;W's request to continue diligence (physical diligence 08/10–08/11) "to potentially facilitate an improved offer" was granted. Board meetings set for 08/12 to approve a Party B deal.</t>
+          <t>Target tells G&amp;W, via BMO, that it intends to sign with another bidder. Board and committee meetings were set for 08/12 to approve a Party B deal.</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>the Transaction Committee directed representatives of BMO to inform G&amp;W that the Company intended to enter into a merger agreement with another bidder (p. 31)</t>
+          <t>“the Transaction Committee directed representatives of BMO to inform G&amp;W that the Company intended to enter into a merger agreement with another bidder” (p. 31)</t>
         </is>
       </c>
       <c r="R55" s="2" t="n"/>
@@ -4194,18 +4190,22 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>08/10/2016</t>
+          <t>08/09/2016-08/10/2016</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="n"/>
+          <t>G&amp;W</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
@@ -4219,26 +4219,28 @@
       <c r="J56" s="2" t="n"/>
       <c r="K56" s="2" t="n"/>
       <c r="L56" s="2" t="n"/>
-      <c r="M56" s="2" t="n"/>
+      <c r="M56" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N56" s="2" t="n"/>
       <c r="O56" s="2" t="n"/>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>G&amp;W's legal counsel; first shown acting 08/10/2016, discussing the draft merger and voting agreements with Hinckley Allen; finalized the documents at signing.</t>
+          <t>Target grants G&amp;W's request to keep doing diligence, incl. physical diligence on 08/10-08/11, "to potentially facilitate an improved offer". On 08/11 G&amp;W signalled a possible revised LOI for 08/12.</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>Simpson Thacher &amp; Bartlett LLP (which we refer to as “Simpson Thacher”), G&amp;W’s legal counsel (p. 31)</t>
+          <t>“including physical due diligence on August 10 and August 11, 2016, to potentially facilitate an improved offer, which request was granted” (p. 31)</t>
         </is>
       </c>
       <c r="R56" s="2" t="n"/>
       <c r="S56" s="2" t="n"/>
       <c r="T56" s="3" t="n">
-        <v>42592</v>
+        <v>42591</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>42592</v>
+        <v>42591</v>
       </c>
       <c r="V56" s="3" t="n">
         <v>42592</v>
@@ -4250,22 +4252,18 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>08/12/2016 (morning)</t>
+          <t>08/10/2016</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>G&amp;W</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Simpson Thacher &amp; Bartlett LLP</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
@@ -4274,52 +4272,34 @@
       <c r="G57" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H57" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="I57" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="H57" s="2" t="n"/>
+      <c r="I57" s="2" t="n"/>
+      <c r="J57" s="2" t="n"/>
+      <c r="K57" s="2" t="n"/>
+      <c r="L57" s="2" t="n"/>
+      <c r="M57" s="2" t="n"/>
       <c r="N57" s="2" t="n"/>
       <c r="O57" s="2" t="n"/>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>Ready to sign: physical diligence completed 08/11; no financing condition, G&amp;W represented sufficient funds (pp. 34, A-§4.5). Mark-ups of merger and voting agreements; CVR dropped; offer to expire 6:00 p.m. 08/13. Signalled 08/11.</t>
+          <t>G&amp;W's legal counsel; first shown acting on 08/10/2016, discussing the draft merger and voting agreements with Hinckley Allen; finalized the documents at signing.</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>G&amp;W submitted a revised LOI to acquire the Company for a price of $25.00 per share in cash, which excluded the previously proposed CVR (p. 31)</t>
+          <t>“Simpson Thacher &amp; Bartlett LLP (which we refer to as “Simpson Thacher”), G&amp;W’s legal counsel” (p. 31)</t>
         </is>
       </c>
       <c r="R57" s="2" t="n"/>
       <c r="S57" s="2" t="n"/>
       <c r="T57" s="3" t="n">
-        <v>42594</v>
+        <v>42592</v>
       </c>
       <c r="U57" s="3" t="n">
-        <v>42594</v>
+        <v>42592</v>
       </c>
       <c r="V57" s="3" t="n">
-        <v>42594</v>
+        <v>42592</v>
       </c>
     </row>
     <row r="58">
@@ -4328,18 +4308,22 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>08/12/2016</t>
+          <t>08/12/2016 (morning)</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Providence and Worcester Railroad (target)</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="n"/>
+          <t>G&amp;W</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
@@ -4348,22 +4332,40 @@
       <c r="G58" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H58" s="2" t="n"/>
-      <c r="I58" s="2" t="n"/>
-      <c r="J58" s="2" t="n"/>
-      <c r="K58" s="2" t="n"/>
-      <c r="L58" s="2" t="n"/>
-      <c r="M58" s="2" t="n"/>
+      <c r="H58" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N58" s="2" t="n"/>
       <c r="O58" s="2" t="n"/>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>Price feedback to Party B: at 10:30 a.m. the Committee had BMO tell Party B a rival had submitted a higher revised LOI; that afternoon, at the Board's request, BMO asked Party B whether it would raise its price (#60).</t>
+          <t>None: physical diligence just completed and the signed agreement had no financing condition (p. 34). All cash, CVR dropped, with mark-ups of merger and voting agreements; offer to expire 6:00 p.m. next day. Signed same day.</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>the Transaction Committee directed representatives of BMO to inform Party B that another party had submitted a revised LOI at a higher price (p. 31)</t>
+          <t>“G&amp;W submitted a revised LOI to acquire the Company for a price of $25.00 per share in cash, which excluded the previously proposed CVR” (p. 31)</t>
         </is>
       </c>
       <c r="R58" s="2" t="n"/>
@@ -4384,18 +4386,22 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>08/12/2016</t>
+          <t>08/12/2016 (10:30 a.m. meeting)</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Company STB counsel (unnamed)</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="n"/>
+          <t>Party B</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
@@ -4409,17 +4415,19 @@
       <c r="J59" s="2" t="n"/>
       <c r="K59" s="2" t="n"/>
       <c r="L59" s="2" t="n"/>
-      <c r="M59" s="2" t="n"/>
+      <c r="M59" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N59" s="2" t="n"/>
       <c r="O59" s="2" t="n"/>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>Target's regulatory (Surface Transportation Board) counsel; advised the Board on 08/12/2016 that approval timing and likelihood were not materially different for G&amp;W and Party B.</t>
+          <t>Target tells Party B, via BMO, that another party has submitted a revised LOI at a higher price.</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>The Board arranged a telephone call with the Company’s STB counsel to discuss the process for obtaining the required regulatory approval or exemption for the transaction (p. 32)</t>
+          <t>“the Transaction Committee directed representatives of BMO to inform Party B that another party had submitted a revised LOI at a higher price” (p. 31)</t>
         </is>
       </c>
       <c r="R59" s="2" t="n"/>
@@ -4445,17 +4453,13 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>G&amp;W</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Company's STB counsel (unnamed)</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Merger agreement signed</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
@@ -4469,19 +4473,17 @@
       <c r="J60" s="2" t="n"/>
       <c r="K60" s="2" t="n"/>
       <c r="L60" s="2" t="n"/>
-      <c r="M60" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M60" s="2" t="n"/>
       <c r="N60" s="2" t="n"/>
       <c r="O60" s="2" t="n"/>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>Board (Smith recused) found G&amp;W superior; BMO fairness opinion. $25.00 cash per common share, preferred converted 100:1; 3% fee ($3.785m, cut from 3.85%); Eder Trusts voting agreement. Ref: $16.30 close 08/12/2016; 53% premium.</t>
+          <t>Target's regulatory counsel; advised the Board on STB approval or exemption, a voting trust and timing. The Board found regulatory timing and likelihood not materially different for G&amp;W and Party B.</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>Shortly thereafter, Hinckley Allen and Simpson Thacher finalized the transaction documents and the Company and G&amp;W executed the merger agreement (p. 32)</t>
+          <t>“The Board arranged a telephone call with the Company’s STB counsel to discuss the process for obtaining the required regulatory approval or exemption for the transaction” (p. 32)</t>
         </is>
       </c>
       <c r="R60" s="2" t="n"/>
@@ -4502,7 +4504,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>08/12/2016</t>
+          <t>08/12/2016 (afternoon)</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4517,7 +4519,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Not selected at signing</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
@@ -4534,20 +4536,16 @@
       <c r="M61" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>Would not improve earlier offer</t>
-        </is>
-      </c>
+      <c r="N61" s="2" t="n"/>
       <c r="O61" s="2" t="n"/>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>Asked at the Board's request whether it would raise its $24.00 offer (#53), Party B declined; Board chose G&amp;W's $25.00. Party B's draft carried a 3% fee plus expenses up to 1%.</t>
+          <t>Price request: at the Board's request BMO asks Party B whether it would raise its $24.00 offer; Party B says it will not.</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>Party B indicated that it would not increase its price. (p. 32)</t>
+          <t>“representatives of BMO then contacted Party B to determine if it would increase its offer price. Party B indicated that it would not increase its price.” (p. 32)</t>
         </is>
       </c>
       <c r="R61" s="2" t="n"/>
@@ -4568,12 +4566,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>by 08/12/2016</t>
+          <t>08/12/2016</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Party E</t>
+          <t>G&amp;W</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -4583,7 +4581,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Not selected at signing</t>
+          <t>Merger agreement signed</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
@@ -4600,37 +4598,25 @@
       <c r="M62" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O62" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="N62" s="2" t="n"/>
+      <c r="O62" s="2" t="n"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>Inferred: last reported confirming its $21.26 LOI on 08/02 (#49) and not mentioned again; closed at signing with G&amp;W.</t>
+          <t>$25.00 cash per common share; preferred converts to 100 common each. Board (Smith recused) chose G&amp;W over Party B: $1.00 more, lower break fee (3%, cut from 3.85%, $3.785m). BMO fairness opinion; Eder Trusts signed a voting agreement.</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>Party E withdrew its revised proposal on August 2, 2016 (but confirmed its original proposal of $21.26 per share) (p. 30)</t>
-        </is>
-      </c>
-      <c r="R62" s="2" t="inlineStr">
-        <is>
-          <t>Q8</t>
-        </is>
-      </c>
+          <t>“Shortly thereafter, Hinckley Allen and Simpson Thacher finalized the transaction documents and the Company and G&amp;W executed the merger agreement” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="n"/>
       <c r="S62" s="2" t="n"/>
       <c r="T62" s="3" t="n">
         <v>42594</v>
       </c>
       <c r="U62" s="3" t="n">
-        <v>42584</v>
+        <v>42594</v>
       </c>
       <c r="V62" s="3" t="n">
         <v>42594</v>
@@ -4642,60 +4628,130 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>08/15/2016</t>
+          <t>08/12/2016</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Providence and Worcester Railroad; G&amp;W</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="n"/>
+          <t>Party B</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Merger announced</t>
+          <t>Not selected at signing</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
+      <c r="G63" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="H63" s="2" t="n"/>
       <c r="I63" s="2" t="n"/>
       <c r="J63" s="2" t="n"/>
       <c r="K63" s="2" t="n"/>
       <c r="L63" s="2" t="n"/>
-      <c r="M63" s="2" t="n"/>
-      <c r="N63" s="2" t="n"/>
+      <c r="M63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>Would not improve earlier offer</t>
+        </is>
+      </c>
       <c r="O63" s="2" t="n"/>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>Company press release announcing the G&amp;W merger before NASDAQ opened on Monday 08/15/2016.</t>
+          <t>Still negotiating a near-final agreement at $24.00 when the Board signed with G&amp;W at $25.00; had declined to raise its price (#60).</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>The Company issued a press release publicly announcing the transaction on Monday, August 15, 2016 prior to the opening of trading (p. 32)</t>
-        </is>
-      </c>
-      <c r="R63" s="2" t="n"/>
+          <t>“The Board determined that the G&amp;W offer represented the superior proposal.” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
       <c r="S63" s="2" t="n"/>
       <c r="T63" s="3" t="n">
+        <v>42594</v>
+      </c>
+      <c r="U63" s="3" t="n">
+        <v>42594</v>
+      </c>
+      <c r="V63" s="3" t="n">
+        <v>42594</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>08/15/2016</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>PWRR (target)</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n"/>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Merger announced</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="n"/>
+      <c r="I64" s="2" t="n"/>
+      <c r="J64" s="2" t="n"/>
+      <c r="K64" s="2" t="n"/>
+      <c r="L64" s="2" t="n"/>
+      <c r="M64" s="2" t="n"/>
+      <c r="N64" s="2" t="n"/>
+      <c r="O64" s="2" t="n"/>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>Press release before the NASDAQ open. Ref: $16.30 close on 08/12/2016; 53% premium (p. 33).</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>“The Company issued a press release publicly announcing the transaction on Monday, August 15, 2016 prior to the opening of trading of the Company’s common stock on the NASDAQ.” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="n"/>
+      <c r="S64" s="2" t="n"/>
+      <c r="T64" s="3" t="n">
         <v>42597</v>
       </c>
-      <c r="U63" s="3" t="n">
+      <c r="U64" s="3" t="n">
         <v>42597</v>
       </c>
-      <c r="V63" s="3" t="n">
+      <c r="V64" s="3" t="n">
         <v>42597</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V63"/>
+  <autoFilter ref="A1:V64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4712,12 +4768,12 @@
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -4781,26 +4837,26 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>42453</v>
+        <v>42460</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Transaction Committee authorized GHF outreach (#5); GHF contacted 11 strategic and 18 financial buyers week of 03/28/2016.</t>
+          <t>GHF outreach to 11 strategic and 18 financial buyers, week of 03/28/2016 (#5), after the committee's 03/24 authorization.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Count: 25–27 NDA signers: 11 strategic incl. Party A; 14 financial; G&amp;W and Party B (strategic) unless among the 11. Filing total: 25 (p. 33).</t>
+          <t>NDA signers, at least 25: 11 strategic incl. Party A (G&amp;W and Party B may be among them or additional) and 14 financial. Named: Party A, G&amp;W, Party B (strategic). Party D (financial), Party E and Party F (strategic) presumably inside the cohorts. Two further Class I railroads were approached; NDA status unknown.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>05/10/2016 (superseded before arrival; inferred) → 05/19/2016</t>
+          <t>05/10/2016 (superseded before arrival) → 05/19/2016</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Late bids accepted</t>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -4810,12 +4866,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>9 IOI bidders ($17.93–$26.50), inferred to include G&amp;W and Parties B, D, E, F; others unnamed.</t>
+          <t>9 bidders (unnamed; presumably incl. Party B, G&amp;W, Party D, Party E, Party F), $17.93-$26.50</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>seven advanced, two low bidders dropped, 16–18 NDA signers did not submit</t>
+          <t>Seven advanced; two low bidders dropped; 15-18 NDA signers did not submit.</t>
         </is>
       </c>
     </row>
@@ -4827,16 +4883,16 @@
         <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>42517</v>
+        <v>42522</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Committee advanced the seven remaining IOI bidders to management presentations and the data site (#21); LOIs requested mid-June.</t>
+          <t>Committee advanced seven IOI bidders to management presentations and data-site diligence (#20); LOIs with agreement mark-ups requested mid-June.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>7 admitted (5 strategic: G&amp;W, Parties B, E, F, one unnamed; 2 financial: Party D, one unnamed); Party C (strategic) admitted 07/12–07/14/2016 after its IOI.</t>
+          <t>8: 6 strategic (Party B, G&amp;W, Party E, Party F, one unnamed; Party C admitted 07/12-07/14 after its unsolicited IOI) and 2 financial (Party D, one unnamed).</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -4856,12 +4912,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>6: Party B $24.00; G&amp;W $21.15, revised $22.15; Party E $21.26; Party D $21.00; Party C $19.30 (IOI $21.00 on 07/12); Party F $19.20.</t>
+          <t>6 bidders: Party B $24.00; G&amp;W $21.15 then $22.15; Party E $21.26; Party D $21.00; Party C $19.30 (after a $21.00 IOI); Party F $19.20</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>two advanced (G&amp;W, Party B), four dropped (Parties C, D, E, F), two did not submit</t>
+          <t>Two advanced (G&amp;W, Party B); four dropped (Party C, Party D, Party E, Party F); two did not submit.</t>
         </is>
       </c>
     </row>
@@ -4877,17 +4933,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Committee chose confirmatory diligence and negotiation with G&amp;W and Party B only (#43).</t>
+          <t>Committee chose G&amp;W and Party B for confirmatory diligence and definitive negotiation (#37).</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2 strategic: G&amp;W, Party B. Party D (financial) and Party E (strategic): re-engaged 07/29/2016, still being received, not admitted.</t>
+          <t>2 strategic: G&amp;W, Party B. Party D (financial) and Party E (strategic) re-entered on 07/29: still being received, not admitted.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>none stated (G&amp;W's own offer expiry of 6:00 p.m. 08/13/2016 is not a target due date)</t>
+          <t>none stated</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4902,12 +4958,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4: G&amp;W $25.00 cash; Party B reaffirmed $24.00; Party D $24.00; Party E $23.81 then $21.26.</t>
+          <t>4 bidders: G&amp;W $25.00 (08/12); Party B $24.00 reaffirmed (08/04); Party D $24.00 (08/01); Party E $23.81 (08/01), reverting to $21.26 (08/02)</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>signing with G&amp;W at $25.00; Party D withdrew; Parties B and E not selected</t>
+          <t>Signing with G&amp;W on 08/12/2016; Party B not selected; Party D withdrew; Party E dropped.</t>
         </is>
       </c>
     </row>
@@ -4923,15 +4979,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -4980,27 +5036,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Is Party A's Q4 2015 approach a Bidder interest in acquiring the Company, or an approach about a minority equity stake?</t>
+          <t>Process and round map: one process with three rounds (IOIs; LOIs; definitive negotiation with G&amp;W and Party B)?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Keep as Bidder interest, round 0, with no price. It is the approach the board answered by hiring bankers for "possible negotiations with Party A", and Party A was carried into the auction.</t>
+          <t>Keep. Round 1 opens with the week-of-03/28 outreach wave; round 2 with the 05/23-06/01 selection of seven bidders; round 3 with the 07/27 move to definitive negotiation. Party C's unsolicited 07/12 IOI sits in round 2, where Party C was admitted.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Party A "expressed some interest in acquiring equity" alongside joint-venture ideas (p. 27); the board then weighed change in control options.</t>
+          <t>E5 tests: (a) not met, as the 03/14 plan kept Party A in view (p. 27); (b) possibly met, since the only ~2-month gap is Q4 2015 (10/01-12/31/2015) to 03/22/2016 (pp. 27-28); (c) met (03/14 decision). All three are needed, so one process.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>#1</t>
+          <t>#5, #20, #24, #37</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>If read as a stake approach it becomes an Other material event; Initiation in Deal facts would move from mixed to target-led.</t>
+          <t>Alternative boundaries: open round 1 at the 03/24 authorization (only the date changes), or fold round 3 into round 2 (the round-3 rows become round 2 and round 2 becomes Inferred final).</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -5013,27 +5069,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Process and round map: one process; round 0 (#1–#4); round 1 from 03/24/2016 (IOIs); round 2 from 05/23–06/01/2016 (seven advanced; LOIs); round 3 from 07/27/2016 (definitive negotiation with G&amp;W and Party B); post (#62).</t>
+          <t>How many parties signed confidentiality agreements, and were G&amp;W and Party B among the 11 strategic signers?</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Accept. Alternatives: open round 1 at the 03/14 decision (#3) or at the 03/28 outreach; open round 2 at the mid-June LOI request (#22), which moves only the opening date; treat Party D/E's 08/01 bids (#44–#47) as round-2 bargaining, which is unsupported because round 2 had closed at #39–#42.</t>
+          <t>Keep G&amp;W and Party B as separate rows, leave the strategic cohort Count blank (9-11), and treat the auction screen as Met with at least 25.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>E5: (a) fails, since Party A was kept in view (p. 27); (b) the only contact gap of about two months or more is Party A's Q4 2015 meeting to the 03/22/2016 meeting (about 2.7–5.7 months), with no reported end of the effort; (c) the 03/14/2016 decision is a fresh start. So there is one process.</t>
+          <t>P. 28 says 11 strategic (incl. Party A) and 14 financial signed. Party C signed in July (p. 29), making at least 26. P. 33 says 25 in total. G&amp;W's NDA date (04/03, p. A-48) falls in the outreach week. Party B was met on 04/21 as "another" strategic buyer.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>#5, #21, #25, #43, #44, #45, #46, #47</t>
+          <t>#6, #8, #9, #10, #11, #12, #13, #18</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Round membership and live counts; a second process would reclassify #1 and add Process markers.</t>
+          <t>If G&amp;W and Party B were among the 11, the cohort Count is 9 and the round-1 non-submitters number 16. If both were outside, the cohort is 11 and there are 18 non-submitters. The p. 33 total would imply 15.</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -5046,27 +5102,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>How many parties signed confidentiality agreements? The background gives 11 strategic + 14 financial (p. 28) plus Party C in July (p. 29); the reasons section says 25 (p. 33). G&amp;W and Party B might or might not be among the 11.</t>
+          <t>Round 1 deadline outcomes: was the 05/10 date superseded before arrival, and what followed the 05/19 date?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Keep the stated cohorts (11, 14) and give G&amp;W, Party B and Party C their own rows: 25–28 signers, with 26 the most likely (G&amp;W and B inside the 11; p. 33 omits Party C).</t>
+          <t>Treat 05/10 as superseded (no outcome); record 05/19 as Unclear.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>The filing never places G&amp;W, Party B or the two Class I railroads (#11) in the 11 contacted in week of 03/28 (p. 28); Party C "had not previously been part of the process" (p. 29).</t>
+          <t>P. 29 says only that the 05/10 date "was subsequently postponed" to 05/19. IOIs arrived "Between May 19, 2016 and June 1, 2016", and the committee met on 05/23 and 06/01 to consider them. No IOI is dated, so a late arrival is not established.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>#6, #8, #9, #10, #11, #13, #14, #15, #19, #24</t>
+          <t>#14, #15, #16, #17</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Round-1 live count 25–27 and the non-submitter range at #19 (16–18); the auction screen stays Met either way.</t>
+          <t>If any IOI arrived after 05/19, the outcome becomes Late bids accepted. If the postponement came after 05/10, that date needs a Deadline row and an Extended outcome.</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -5079,27 +5135,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Round 1 deadline outcomes: was 05/10/2016 superseded before it arrived, and what followed 05/19/2016?</t>
+          <t>Were Party B, G&amp;W, Party D, Party E and Party F among the nine IOI bidders and the seven advanced to round 2?</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>05/10: superseded before arrival, so no Deadline row. 05/19: Late bids accepted, because IOIs arrived "between May 19 and June 1" and all nine were considered on 06/01.</t>
+          <t>Yes, by inference; keep them inside the unnamed IOI cohort, with no individual IOI rows.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>The postponement was made "to ensure the potential buyers had sufficient time" (p. 29), which implies it came before 05/10; the receipt window runs to 06/01 (p. 29).</t>
+          <t>Six LOIs came from Party B, G&amp;W, Party D, Party E, Party C and Party F. Party C was the only new entrant, and two of the seven did not submit (pp. 29-30): 5 + 2 = 7. No IOI is attributed to a named party.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>#12, #16, #17, #18</t>
+          <t>#17, #20</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>If all IOIs arrived 05/19 the outcome is Enforced; if the postponement came after 05/10, add a Deadline row with outcome Extended.</t>
+          <t>If any of them entered after the IOI stage, round 2 would have fewer than five named members from round 1, and the Rounds sheet's admitted list and live counts would change.</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -5112,27 +5168,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Should the nine IOIs be one cohort Bid row, or individual inferred rows for G&amp;W and Parties B, D, E, F plus a four-bidder remainder?</t>
+          <t>Round 2 deadline outcome for the 07/20/2016 LOI due date.</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Keep one nine-bidder cohort carrying the stated $17.93–$26.50 range, with inferred members named in the Note. Splitting would leave the stated range on no row.</t>
+          <t>Late bids accepted.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>The seven advanced are "the remaining seven" of nine (p. 29); only Party C is described as new at the LOI stage (p. 29), so the five named LOI bidders were IOI bidders. Their IOI prices are not given.</t>
+          <t>G&amp;W's LOI is dated 07/21/2016, one day after the 07/20 due date, and the committee reviewed it with the others on 07/22 and 07/27 (pp. 29-30). The other LOIs are dated only "late July".</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>#18, #21</t>
+          <t>#26, #34</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Individual rows would give G&amp;W and Parties B, D, E, F round-1 bids with blank prices, and entries by bid for G&amp;W and Party B.</t>
+          <t>If G&amp;W's one-day slip were read as within an informal grace period, the outcome would be Enforced: the committee took its next step on the bids in hand.</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -5145,27 +5201,27 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Round 2 deadline outcome for 07/20/2016.</t>
+          <t>Formality and conditions of LOIs that came with agreement mark-ups (Party B, Party D, G&amp;W) and of the revisions that rested on them.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Late bids accepted: G&amp;W's LOI is dated 07/21/2016 and was reviewed with the others on 07/22 and 07/27. The other five came "in late July", arrival days unstated.</t>
+          <t>Formal for #27, #29, #34, #36, #44. Conditions record the diligence terms, and #36 is Unclear.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>LOIs were due 07/20 (p. 29); G&amp;W "submitted an LOI on July 21, 2016" (p. 29); the Committee reviewed the LOIs on 07/22 and 07/27 (p. 30).</t>
+          <t>E11(1): a priced proposal with a mark-up of the acquisition agreement is Formal even when the filing calls it a non-binding LOI (p. 29). Party E gave only an issues summary, so Informal. Neither revision restates its mark-ups or conditions (pp. 29-30).</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>#22, #27, #36</t>
+          <t>#27, #29, #34, #36, #44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>If G&amp;W's LOI is treated as timely, the outcome would be Enforced.</t>
+          <t>Treating the revisions as Informal would lower G&amp;W's and Party D's standing bids before round 3. Recording #36 as Heavy would carry over the three-week exclusive-diligence condition.</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -5178,27 +5234,27 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Are G&amp;W's 07/26 revised LOI and Party D's 08/01 revised LOI Formal, when neither is reported with a new mark-up?</t>
+          <t>Exit labels for Party D and Party E after they re-entered.</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Formal: each revises a priced LOI the bidder had supported with its own mark-up of the merger agreement weeks earlier, and those mark-ups stayed on the table. G&amp;W's 07/26 Conditions: Unclear.</t>
+          <t>Party D: Withdrew (Terms or process). Party E: Dropped by target, inferred, by 08/04.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>G&amp;W, Party B and Party D "provided mark-ups of the draft merger agreement" with their LOIs (p. 29); the revisions are described only as price changes (pp. 29–30).</t>
+          <t>Party D said it would not proceed "at that time" after the Company refused a no-sign commitment (p. 30). Party E is last seen confirming $21.26 on 08/02, and on 08/04 the committee named only G&amp;W and Party B as continuing (p. 31).</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>#38, #46</t>
+          <t>#50, #52</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>If Informal, the formal-bid set in rounds 2–3 shrinks and Party D's $24.00 becomes an informal exit price.</t>
+          <t>Party D could be Dropped by target, since the refusal was the target's decision. Party E could be Not selected at signing on 08/12, which keeps it live in round 3 until signing.</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -5211,66 +5267,33 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Party E: is 08/02 a withdrawal (exit) or a reversion to its $21.26 bid, and how does its participation end?</t>
+          <t>Should Party B's 08/04 return of its revised merger-agreement draft be recorded as Bid reaffirmed at $24.00?</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Reversion: a Bid row at $21.26 (#49), then an inferred Not selected at signing on 08/12, since Party E "confirmed its original proposal" and is never mentioned again.</t>
+          <t>Yes. Keep the row as Formal and Light.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>"Party E withdrew its revised proposal on August 2, 2016 (but confirmed its original proposal of $21.26 per share)" (p. 30).</t>
+          <t>On 08/04 the committee chose to complete the merger agreement with Party B, and Party B's counsel returned a revised draft that day (p. 31). Its last priced row (#27) sits in round 2, which was Not final. On 08/12 it would not raise its price (p. 32).</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>#49, #61</t>
+          <t>#53, #62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>If treated as Withdrew on 08/02, Party E leaves before round 3's end and its $21.26 no longer counts as a live standing offer at signing.</t>
+          <t>Without the row, Party B's last priced offer stays in a Not-final round, and its $24.00 is not recorded as a standing offer in round 3.</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Q9</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Party B Bid reaffirmed on 08/04/2016 at $24.00 (carried from #30).</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Keep. Party B's counsel returned its own revised draft merger agreement while the Company was finalizing with it; its latest priced row sits in round 2 (Not final). Conditions Light: expedited diligence was still under way.</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Party B's counsel "provided a revised draft of the merger agreement" on 08/04 (p. 31); on 08/12 G&amp;W's price "was $1.00 more per share" (p. 32), confirming $24.00 stood.</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>#53</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Without it, Party B's last formal price sits only in a non-final round and its round-3 standing is unrecorded.</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5284,8 +5307,8 @@
   <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5308,7 +5331,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Providence and Worcester Railroad Company (PWRR; NASDAQ: PWX), regional freight railroad, Rhode Island corporation</t>
+          <t>Providence and Worcester Railroad Company (PWRR; NASDAQ: PWX), a Rhode Island regional freight railroad</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5343,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Genesee &amp; Wyoming Inc. (G&amp;W; NYSE: GWR), via Pullman Acquisition Sub Inc.</t>
+          <t>Genesee &amp; Wyoming Inc. (G&amp;W), through its wholly owned subsidiary Pullman Acquisition Sub Inc.</t>
         </is>
       </c>
     </row>
@@ -5332,7 +5355,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Strategic (owner/operator of 121 freight railroads, p. 1)</t>
+          <t>Strategic: G&amp;W owns or leases 121 freight railroads worldwide (p. 21)</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5367,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>$25.00 in cash per common share; each preferred share converts to 100 common shares first. No financing condition. Termination fee $3.785m (about 3%). Ref: $16.30 close 08/12/2016; 53% premium (p. 33).</t>
+          <t>$25.00 per share of common stock in cash, without interest; each preferred share converts into 100 common shares first. No financing condition. Termination fee $3.785 million (about 3%). Eder Trusts voting agreement.</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5391,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>08/15/2016 (press release before market open)</t>
+          <t>08/15/2016 (press release before the NASDAQ open)</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5403,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DEFM14A; proxy statement dated 09/19/2016 (file name gives 2016-09-20)</t>
+          <t>DEFM14A (definitive proxy statement), filed 09/20/2016; proxy statement dated 09/19/2016</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5415,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>27–32</t>
+          <t>27-32</t>
         </is>
       </c>
     </row>
@@ -5404,7 +5427,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>mixed: Party A's Q4 2015 expression of interest prompted the board to hire GHF, and the target then ran a broad auction</t>
+          <t>mixed: Party A's Q4 2015 unsolicited interest in an equity investment prompted the Board to hire GHF, then the target ran a broad auction</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5451,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>None reported apart from Party A's Q4 2015 approach, recorded as round 0 (#1)</t>
+          <t>None reported (Party A's Q4 2015 interest is round 0 of process 1)</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5463,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Met (process 1): 25–28 parties (25 stated at p. 33; background supports at least 26 including Party C; see Q3)</t>
+          <t>Met (process 1): at least 25 parties (11 strategic + 14 financial on p. 28, plus Party C on p. 29; 25 on p. 33)</t>
         </is>
       </c>
     </row>
@@ -5464,7 +5487,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>US dollars per common share, assuming conversion of preferred into common (as bidders were instructed). G&amp;W's July LOIs included a $1.13 CVR, entered at total package value.</t>
+          <t>US dollars per share of common stock, assuming preferred converts to common (100 per preferred share). G&amp;W's July LOIs combined cash with a $1.13 CVR.</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5523,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>After Party A, a Class I rail partner, expressed interest in taking equity in late 2015, PWRR hired GHF and in March 2016 authorized a broad auction. GHF contacted 29 buyers; 25 signed confidentiality agreements, and nine submitted IOIs of $17.93–$26.50 by 06/01/2016. The seven highest bidders got management presentations and the data site; late entrant Party C joined in July. Six non-binding LOIs arrived in late July, and the committee kept only Party B ($24.00) and G&amp;W ($22.15). Parties D and E briefly re-engaged in August but fell away over diligence and exclusivity terms. When PWRR was about to sign with Party B, G&amp;W bid $25.00 in cash with a one-day expiry; Party B would not raise its price, and PWRR signed with G&amp;W on 08/12/2016.</t>
+          <t>In Q4 2015 Class I rail partner Party A expressed interest in taking equity, and the Board hired GHF in January 2016. In March 2016 the Board decided to solicit change-in-control interest: GHF contacted 29 buyers, and at least 25 signed confidentiality agreements. Nine non-binding IOIs ($17.93-$26.50) arrived by 06/01; the two lowest bidders were cut and seven got management presentations, joined in July by the unsolicited Party C. Six LOIs arrived in late July, led by Party B at $24.00; the committee chose Party B and G&amp;W for definitive negotiation and prioritized Party B, while re-engaged Parties D and E fell away. G&amp;W, told it was losing, raised its bid on 08/12 to $25.00 all cash; Party B would not match, and the Board signed with G&amp;W that day.</t>
         </is>
       </c>
     </row>
